--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -397,1103 +397,1387 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:I47"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="70.83203125" customWidth="1"/>
-    <col min="7" max="7" width="45.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="50.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="65.83203125" customWidth="1"/>
+    <col min="9" max="9" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
         <v>Domaine</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>Fonctionnalité</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Description</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Priorité</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Statut</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>Prédécesseurs</v>
+      </c>
+      <c r="H1" t="str">
         <v>Directives d'implémentation</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>Notes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>REQ-001</v>
+      </c>
+      <c r="B2" t="str">
         <v>Cœur métier</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>Workflow complet d'audit</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>Phase 1.1 Préparation → 1.2 Entretiens → 1.3 Scoring → 1.4 Rapports</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>P0</v>
       </c>
-      <c r="E2" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F2" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G2" t="str">
+        <v>-</v>
+      </c>
+      <c r="H2" t="str">
         <v>Chaque phase est un mode d'affichage séparé dans App.tsx. État global gère la transition.</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>MVP complet, testé en production</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>REQ-002</v>
+      </c>
+      <c r="B3" t="str">
         <v>Cœur métier</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>Gestion des campagnes d'audit</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>Création, sélection, stockage des campagnes avec métadonnées</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>P0</v>
       </c>
-      <c r="E3" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F3" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G3" t="str">
+        <v>-</v>
+      </c>
+      <c r="H3" t="str">
         <v>Endpoints: POST /campaigns, GET /campaigns. Stockage lowdb en db.data.campaigns</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>ID UUID, timestamps, framework (ISO 19011/PASSI)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>REQ-003</v>
+      </c>
+      <c r="B4" t="str">
         <v>Cœur métier</v>
       </c>
-      <c r="B4" t="str">
+      <c r="C4" t="str">
         <v>Gestion des critères d'audit</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>Code, titre, thème pour chaque critère avec lien campagne</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>P0</v>
       </c>
-      <c r="E4" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F4" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G4" t="str">
+        <v>REQ-002</v>
+      </c>
+      <c r="H4" t="str">
         <v>POST /criteria, GET /criteria?campaignId=. Clé étrangère campaignId.</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>Critères liés à campagnes pour isolation des données</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>REQ-004</v>
+      </c>
+      <c r="B5" t="str">
         <v>Cœur métier</v>
       </c>
-      <c r="B5" t="str">
+      <c r="C5" t="str">
         <v>Génération de questions</v>
       </c>
-      <c r="C5" t="str">
+      <c r="D5" t="str">
         <v>Questions avec text, guidance, theme générées dynamiquement</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>P0</v>
       </c>
-      <c r="E5" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F5" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G5" t="str">
+        <v>REQ-003</v>
+      </c>
+      <c r="H5" t="str">
         <v>POST /question, GET /questions. Schéma Zod pour validation stricte.</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>Peut être depuis template ou IA (voir section IA)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>REQ-005</v>
+      </c>
+      <c r="B6" t="str">
         <v>IA &amp; Génération</v>
       </c>
-      <c r="B6" t="str">
+      <c r="C6" t="str">
         <v>Génération depuis référentiel</v>
       </c>
-      <c r="C6" t="str">
+      <c r="D6" t="str">
         <v>Parser PDF ou Excel, extraire texte, passer à IA pour générer questions</v>
       </c>
-      <c r="D6" t="str">
-        <v>P1</v>
-      </c>
       <c r="E6" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F6" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G6" t="str">
+        <v>REQ-003</v>
+      </c>
+      <c r="H6" t="str">
         <v>POST /generate-questions-from-referential. Multipart form. parseReferentialFile() en services/referentialParser.ts</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>Limite 50KB texte extrait pour perf API</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>REQ-006</v>
+      </c>
+      <c r="B7" t="str">
         <v>IA &amp; Génération</v>
       </c>
-      <c r="B7" t="str">
+      <c r="C7" t="str">
         <v>Dual AI strategy - OpenAI</v>
       </c>
-      <c r="C7" t="str">
+      <c r="D7" t="str">
         <v>Intégration GPT-4o pour génération rapide et haute qualité</v>
       </c>
-      <c r="D7" t="str">
-        <v>P1</v>
-      </c>
       <c r="E7" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F7" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G7" t="str">
+        <v>REQ-028</v>
+      </c>
+      <c r="H7" t="str">
         <v>generateQuestionsFromOpenAI() dans openai.ts. OpenAI client avec apiKey depuis .env</v>
       </c>
-      <c r="G7" t="str">
+      <c r="I7" t="str">
         <v>Fallback si OPENAI_API_KEY absent</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>REQ-007</v>
+      </c>
+      <c r="B8" t="str">
         <v>IA &amp; Génération</v>
       </c>
-      <c r="B8" t="str">
+      <c r="C8" t="str">
         <v>Dual AI strategy - Ollama local</v>
       </c>
-      <c r="C8" t="str">
+      <c r="D8" t="str">
         <v>Ollama + Mistral/Gemma3 pour mode offline-first sur éliteBook</v>
       </c>
-      <c r="D8" t="str">
-        <v>P1</v>
-      </c>
       <c r="E8" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F8" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G8" t="str">
+        <v>REQ-028</v>
+      </c>
+      <c r="H8" t="str">
         <v>generateQuestionsFromOllama() fetch to localhost:11434/api/generate. checkOllamaAvailable() avec timeout 2s</v>
       </c>
-      <c r="G8" t="str">
+      <c r="I8" t="str">
         <v>Auto-détection Ollama, fallback depuis OpenAI si non dispo</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>REQ-008</v>
+      </c>
+      <c r="B9" t="str">
         <v>IA &amp; Génération</v>
       </c>
-      <c r="B9" t="str">
+      <c r="C9" t="str">
         <v>Model switching UI</v>
       </c>
-      <c r="C9" t="str">
+      <c r="D9" t="str">
         <v>Permuter entre mistral et gemma3:4b directement dans l'appli</v>
       </c>
-      <c r="D9" t="str">
-        <v>P1</v>
-      </c>
       <c r="E9" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F9" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G9" t="str">
+        <v>REQ-006, REQ-007</v>
+      </c>
+      <c r="H9" t="str">
         <v>GET/POST /config endpoints. État currentOllamaModel dans server.ts. Boutons UI dans App.tsx 'Configuration IA'</v>
       </c>
-      <c r="G9" t="str">
+      <c r="I9" t="str">
         <v>Changement runtime, pas besoin restart API</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>REQ-009</v>
+      </c>
+      <c r="B10" t="str">
         <v>IA &amp; Génération</v>
       </c>
-      <c r="B10" t="str">
+      <c r="C10" t="str">
         <v>Parsing référentiel multi-format</v>
       </c>
-      <c r="C10" t="str">
+      <c r="D10" t="str">
         <v>Support PDF et Excel avec extraction de texte</v>
       </c>
-      <c r="D10" t="str">
-        <v>P1</v>
-      </c>
       <c r="E10" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F10" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G10" t="str">
+        <v>REQ-005</v>
+      </c>
+      <c r="H10" t="str">
         <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
       </c>
-      <c r="G10" t="str">
+      <c r="I10" t="str">
         <v>Gère encodages UTF-8, caractères spéciaux</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>REQ-010</v>
+      </c>
+      <c r="B11" t="str">
         <v>IA &amp; Génération</v>
       </c>
-      <c r="B11" t="str">
+      <c r="C11" t="str">
         <v>Prompt dynamique contextuel</v>
       </c>
-      <c r="C11" t="str">
+      <c r="D11" t="str">
         <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
       </c>
-      <c r="D11" t="str">
-        <v>P1</v>
-      </c>
       <c r="E11" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F11" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G11" t="str">
+        <v>REQ-005</v>
+      </c>
+      <c r="H11" t="str">
         <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
       </c>
-      <c r="G11" t="str">
+      <c r="I11" t="str">
         <v>Zod validation sur count (1-10), language (fr/en)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>REQ-011</v>
+      </c>
+      <c r="B12" t="str">
         <v>Structuration données</v>
       </c>
-      <c r="B12" t="str">
+      <c r="C12" t="str">
         <v>Modèle Document</v>
       </c>
-      <c r="C12" t="str">
+      <c r="D12" t="str">
         <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
       </c>
-      <c r="D12" t="str">
+      <c r="E12" t="str">
         <v>P0</v>
       </c>
-      <c r="E12" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F12" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G12" t="str">
+        <v>REQ-002</v>
+      </c>
+      <c r="H12" t="str">
         <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
       </c>
-      <c r="G12" t="str">
+      <c r="I12" t="str">
         <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v>REQ-012</v>
+      </c>
+      <c r="B13" t="str">
         <v>Structuration données</v>
       </c>
-      <c r="B13" t="str">
+      <c r="C13" t="str">
         <v>Modèle Interviewé</v>
       </c>
-      <c r="C13" t="str">
+      <c r="D13" t="str">
         <v>Nom complet, rôle, lié à campaign</v>
       </c>
-      <c r="D13" t="str">
+      <c r="E13" t="str">
         <v>P0</v>
       </c>
-      <c r="E13" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F13" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G13" t="str">
+        <v>REQ-002</v>
+      </c>
+      <c r="H13" t="str">
         <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
       </c>
-      <c r="G13" t="str">
+      <c r="I13" t="str">
         <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>REQ-013</v>
+      </c>
+      <c r="B14" t="str">
         <v>Structuration données</v>
       </c>
-      <c r="B14" t="str">
+      <c r="C14" t="str">
         <v>Modèle Note d'entretien</v>
       </c>
-      <c r="C14" t="str">
+      <c r="D14" t="str">
         <v>Contenu libre + scoring, lié à criterion et interviewé</v>
       </c>
-      <c r="D14" t="str">
+      <c r="E14" t="str">
         <v>P0</v>
       </c>
-      <c r="E14" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F14" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G14" t="str">
+        <v>REQ-003, REQ-012</v>
+      </c>
+      <c r="H14" t="str">
         <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
       </c>
-      <c r="G14" t="str">
+      <c r="I14" t="str">
         <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>REQ-014</v>
+      </c>
+      <c r="B15" t="str">
         <v>Structuration données</v>
       </c>
-      <c r="B15" t="str">
+      <c r="C15" t="str">
         <v>Matrice de conformité</v>
       </c>
-      <c r="C15" t="str">
+      <c r="D15" t="str">
         <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
       </c>
-      <c r="D15" t="str">
-        <v>P1</v>
-      </c>
       <c r="E15" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F15" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G15" t="str">
+        <v>REQ-013</v>
+      </c>
+      <c r="H15" t="str">
         <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
       </c>
-      <c r="G15" t="str">
+      <c r="I15" t="str">
         <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>REQ-015</v>
+      </c>
+      <c r="B16" t="str">
         <v>Structuration données</v>
       </c>
-      <c r="B16" t="str">
+      <c r="C16" t="str">
         <v>Configuration Métriques</v>
       </c>
-      <c r="C16" t="str">
+      <c r="D16" t="str">
         <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
       </c>
-      <c r="D16" t="str">
-        <v>P1</v>
-      </c>
       <c r="E16" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F16" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G16" t="str">
+        <v>REQ-002</v>
+      </c>
+      <c r="H16" t="str">
         <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
       </c>
-      <c r="G16" t="str">
+      <c r="I16" t="str">
         <v>Format texte (ex: '1-5') pour flexibilité</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v>REQ-016</v>
+      </c>
+      <c r="B17" t="str">
         <v>Audit &amp; Traçabilité</v>
       </c>
-      <c r="B17" t="str">
+      <c r="C17" t="str">
         <v>Audit Log complet</v>
       </c>
-      <c r="C17" t="str">
+      <c r="D17" t="str">
         <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
       </c>
-      <c r="D17" t="str">
-        <v>P1</v>
-      </c>
       <c r="E17" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F17" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G17" t="str">
+        <v>REQ-002, REQ-028</v>
+      </c>
+      <c r="H17" t="str">
         <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
       </c>
-      <c r="G17" t="str">
+      <c r="I17" t="str">
         <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v>REQ-017</v>
+      </c>
+      <c r="B18" t="str">
         <v>Audit &amp; Traçabilité</v>
       </c>
-      <c r="B18" t="str">
+      <c r="C18" t="str">
         <v>Filtrage logs par période</v>
       </c>
-      <c r="C18" t="str">
+      <c r="D18" t="str">
         <v>Vue 7j, 30j, tout (by date range filter)</v>
       </c>
-      <c r="D18" t="str">
-        <v>P1</v>
-      </c>
       <c r="E18" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F18" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G18" t="str">
+        <v>REQ-016</v>
+      </c>
+      <c r="H18" t="str">
         <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
       </c>
-      <c r="G18" t="str">
+      <c r="I18" t="str">
         <v>Filter UI: dropdown 3 options + affichage dynamique</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v>REQ-018</v>
+      </c>
+      <c r="B19" t="str">
         <v>Audit &amp; Traçabilité</v>
       </c>
-      <c r="B19" t="str">
+      <c r="C19" t="str">
         <v>Filtrage logs par action</v>
       </c>
-      <c r="C19" t="str">
+      <c r="D19" t="str">
         <v>Filter sur type d'action (campaign.created, etc.)</v>
       </c>
-      <c r="D19" t="str">
-        <v>P1</v>
-      </c>
       <c r="E19" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F19" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G19" t="str">
+        <v>REQ-016</v>
+      </c>
+      <c r="H19" t="str">
         <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
       </c>
-      <c r="G19" t="str">
+      <c r="I19" t="str">
         <v>Enum actions découvertes dynamiquement from logs</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
+        <v>REQ-019</v>
+      </c>
+      <c r="B20" t="str">
         <v>Rapports &amp; Exports</v>
       </c>
-      <c r="B20" t="str">
+      <c r="C20" t="str">
         <v>Export DOCX</v>
       </c>
-      <c r="C20" t="str">
+      <c r="D20" t="str">
         <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
       </c>
-      <c r="D20" t="str">
+      <c r="E20" t="str">
         <v>P2</v>
       </c>
-      <c r="E20" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F20" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G20" t="str">
+        <v>REQ-004, REQ-014</v>
+      </c>
+      <c r="H20" t="str">
         <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
       </c>
-      <c r="G20" t="str">
+      <c r="I20" t="str">
         <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
+        <v>REQ-020</v>
+      </c>
+      <c r="B21" t="str">
         <v>Rapports &amp; Exports</v>
       </c>
-      <c r="B21" t="str">
+      <c r="C21" t="str">
         <v>Export CSV</v>
       </c>
-      <c r="C21" t="str">
+      <c r="D21" t="str">
         <v>Audit logs + conformity matrix en CSV téléchargeable</v>
       </c>
-      <c r="D21" t="str">
+      <c r="E21" t="str">
         <v>P2</v>
       </c>
-      <c r="E21" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F21" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G21" t="str">
+        <v>REQ-014, REQ-016</v>
+      </c>
+      <c r="H21" t="str">
         <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
       </c>
-      <c r="G21" t="str">
+      <c r="I21" t="str">
         <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
+        <v>REQ-021</v>
+      </c>
+      <c r="B22" t="str">
         <v>Rapports &amp; Exports</v>
       </c>
-      <c r="B22" t="str">
+      <c r="C22" t="str">
         <v>Gestion des rapports</v>
       </c>
-      <c r="C22" t="str">
+      <c r="D22" t="str">
         <v>Stocker rapports générés avec titre, date gen, version</v>
       </c>
-      <c r="D22" t="str">
+      <c r="E22" t="str">
         <v>P2</v>
       </c>
-      <c r="E22" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F22" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G22" t="str">
+        <v>REQ-019, REQ-020</v>
+      </c>
+      <c r="H22" t="str">
         <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
       </c>
-      <c r="G22" t="str">
+      <c r="I22" t="str">
         <v>Récupérable dans UI, archivé pour traçabilité</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
+        <v>REQ-022</v>
+      </c>
+      <c r="B23" t="str">
         <v>Dashboard &amp; Visualisation</v>
       </c>
-      <c r="B23" t="str">
+      <c r="C23" t="str">
         <v>KPIs essentiels</v>
       </c>
-      <c r="C23" t="str">
+      <c r="D23" t="str">
         <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
       </c>
-      <c r="D23" t="str">
-        <v>P1</v>
-      </c>
       <c r="E23" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F23" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G23" t="str">
+        <v>REQ-011, REQ-012, REQ-013</v>
+      </c>
+      <c r="H23" t="str">
         <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
       </c>
-      <c r="G23" t="str">
+      <c r="I23" t="str">
         <v>Affiché en gros chiffres zone haute dashboard</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
+        <v>REQ-023</v>
+      </c>
+      <c r="B24" t="str">
         <v>Dashboard &amp; Visualisation</v>
       </c>
-      <c r="B24" t="str">
+      <c r="C24" t="str">
         <v>Matrice de conformité interactive</v>
       </c>
-      <c r="C24" t="str">
+      <c r="D24" t="str">
         <v>Tableau avec % conformité par criterion, tri/filtre</v>
       </c>
-      <c r="D24" t="str">
+      <c r="E24" t="str">
         <v>P2</v>
       </c>
-      <c r="E24" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F24" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G24" t="str">
+        <v>REQ-014</v>
+      </c>
+      <c r="H24" t="str">
         <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
       </c>
-      <c r="G24" t="str">
+      <c r="I24" t="str">
         <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>REQ-024</v>
+      </c>
+      <c r="B25" t="str">
         <v>Dashboard &amp; Visualisation</v>
       </c>
-      <c r="B25" t="str">
+      <c r="C25" t="str">
         <v>Graphiques optionnels (futur)</v>
       </c>
-      <c r="C25" t="str">
+      <c r="D25" t="str">
         <v>Tendances audit timeline, pie charts conformity domains</v>
       </c>
-      <c r="D25" t="str">
+      <c r="E25" t="str">
         <v>P3</v>
       </c>
-      <c r="E25" t="str">
+      <c r="F25" t="str">
         <v>Planifié</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
+        <v>REQ-022</v>
+      </c>
+      <c r="H25" t="str">
         <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
       </c>
-      <c r="G25" t="str">
+      <c r="I25" t="str">
         <v>MVP n'a pas graphiques, architecture prête pour.</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
+        <v>REQ-025</v>
+      </c>
+      <c r="B26" t="str">
         <v>Configuration &amp; Flexibilité</v>
       </c>
-      <c r="B26" t="str">
+      <c r="C26" t="str">
         <v>Support multilingue</v>
       </c>
-      <c r="C26" t="str">
+      <c r="D26" t="str">
         <v>FR et EN, sélection par campaign</v>
       </c>
-      <c r="D26" t="str">
-        <v>P1</v>
-      </c>
       <c r="E26" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F26" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G26" t="str">
+        <v>REQ-028</v>
+      </c>
+      <c r="H26" t="str">
         <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
       </c>
-      <c r="G26" t="str">
+      <c r="I26" t="str">
         <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
+        <v>REQ-026</v>
+      </c>
+      <c r="B27" t="str">
         <v>Configuration &amp; Flexibilité</v>
       </c>
-      <c r="B27" t="str">
+      <c r="C27" t="str">
         <v>Modèle Ollama configurable</v>
       </c>
-      <c r="C27" t="str">
+      <c r="D27" t="str">
         <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
       </c>
-      <c r="D27" t="str">
-        <v>P1</v>
-      </c>
       <c r="E27" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F27" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G27" t="str">
+        <v>REQ-007</v>
+      </c>
+      <c r="H27" t="str">
         <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
       </c>
-      <c r="G27" t="str">
+      <c r="I27" t="str">
         <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v>REQ-027</v>
+      </c>
+      <c r="B28" t="str">
         <v>Configuration &amp; Flexibilité</v>
       </c>
-      <c r="B28" t="str">
+      <c r="C28" t="str">
         <v>OpenAI optionnel</v>
       </c>
-      <c r="C28" t="str">
+      <c r="D28" t="str">
         <v>API key via .env, fallback auto Ollama si absent</v>
       </c>
-      <c r="D28" t="str">
-        <v>P1</v>
-      </c>
       <c r="E28" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F28" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G28" t="str">
+        <v>REQ-028</v>
+      </c>
+      <c r="H28" t="str">
         <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
       </c>
-      <c r="G28" t="str">
+      <c r="I28" t="str">
         <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
+        <v>REQ-028</v>
+      </c>
+      <c r="B29" t="str">
         <v>Configuration &amp; Flexibilité</v>
       </c>
-      <c r="B29" t="str">
+      <c r="C29" t="str">
         <v>Thèmes personnalisés</v>
       </c>
-      <c r="C29" t="str">
+      <c r="D29" t="str">
         <v>Texte libre pour documents et questions</v>
       </c>
-      <c r="D29" t="str">
+      <c r="E29" t="str">
         <v>P2</v>
       </c>
-      <c r="E29" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F29" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G29" t="str">
+        <v>-</v>
+      </c>
+      <c r="H29" t="str">
         <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
       </c>
-      <c r="G29" t="str">
+      <c r="I29" t="str">
         <v>Permet flexibilité sur domaines audit custom</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
+        <v>REQ-029</v>
+      </c>
+      <c r="B30" t="str">
         <v>Infrastructure &amp; Déploiement</v>
       </c>
-      <c r="B30" t="str">
+      <c r="C30" t="str">
         <v>Offline-first capability</v>
       </c>
-      <c r="C30" t="str">
+      <c r="D30" t="str">
         <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
       </c>
-      <c r="D30" t="str">
-        <v>P1</v>
-      </c>
       <c r="E30" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F30" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G30" t="str">
+        <v>-</v>
+      </c>
+      <c r="H30" t="str">
         <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
       </c>
-      <c r="G30" t="str">
+      <c r="I30" t="str">
         <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>REQ-030</v>
+      </c>
+      <c r="B31" t="str">
         <v>Infrastructure &amp; Déploiement</v>
       </c>
-      <c r="B31" t="str">
+      <c r="C31" t="str">
         <v>Automation PowerShell</v>
       </c>
-      <c r="C31" t="str">
+      <c r="D31" t="str">
         <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
       </c>
-      <c r="D31" t="str">
+      <c r="E31" t="str">
         <v>P2</v>
       </c>
-      <c r="E31" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F31" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G31" t="str">
+        <v>REQ-026, REQ-029</v>
+      </c>
+      <c r="H31" t="str">
         <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
       </c>
-      <c r="G31" t="str">
+      <c r="I31" t="str">
         <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
+        <v>REQ-031</v>
+      </c>
+      <c r="B32" t="str">
         <v>Infrastructure &amp; Déploiement</v>
       </c>
-      <c r="B32" t="str">
+      <c r="C32" t="str">
         <v>Versionning Git &amp; GitHub</v>
       </c>
-      <c r="C32" t="str">
+      <c r="D32" t="str">
         <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
       </c>
-      <c r="D32" t="str">
-        <v>P1</v>
-      </c>
       <c r="E32" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F32" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G32" t="str">
+        <v>REQ-005, REQ-029</v>
+      </c>
+      <c r="H32" t="str">
         <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
       </c>
-      <c r="G32" t="str">
+      <c r="I32" t="str">
         <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v>REQ-032</v>
+      </c>
+      <c r="B33" t="str">
         <v>Infrastructure &amp; Déploiement</v>
       </c>
-      <c r="B33" t="str">
+      <c r="C33" t="str">
         <v>API REST Fastify</v>
       </c>
-      <c r="C33" t="str">
+      <c r="D33" t="str">
         <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
       </c>
-      <c r="D33" t="str">
+      <c r="E33" t="str">
         <v>P0</v>
       </c>
-      <c r="E33" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F33" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G33" t="str">
+        <v>REQ-011, REQ-029</v>
+      </c>
+      <c r="H33" t="str">
         <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
       </c>
-      <c r="G33" t="str">
+      <c r="I33" t="str">
         <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
+        <v>REQ-033</v>
+      </c>
+      <c r="B34" t="str">
         <v>UI/UX</v>
       </c>
-      <c r="B34" t="str">
+      <c r="C34" t="str">
         <v>UI React + TypeScript + Vite</v>
       </c>
-      <c r="C34" t="str">
+      <c r="D34" t="str">
         <v>Bundling optimisé, HMR dev mode</v>
       </c>
-      <c r="D34" t="str">
-        <v>P1</v>
-      </c>
       <c r="E34" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F34" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G34" t="str">
+        <v>REQ-015, REQ-029</v>
+      </c>
+      <c r="H34" t="str">
         <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
       </c>
-      <c r="G34" t="str">
+      <c r="I34" t="str">
         <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
+        <v>REQ-034</v>
+      </c>
+      <c r="B35" t="str">
         <v>UI/UX</v>
       </c>
-      <c r="B35" t="str">
+      <c r="C35" t="str">
         <v>Configuration IA section</v>
       </c>
-      <c r="C35" t="str">
+      <c r="D35" t="str">
         <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
       </c>
-      <c r="D35" t="str">
-        <v>P1</v>
-      </c>
       <c r="E35" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F35" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G35" t="str">
+        <v>REQ-022, REQ-029</v>
+      </c>
+      <c r="H35" t="str">
         <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
       </c>
-      <c r="G35" t="str">
+      <c r="I35" t="str">
         <v>UX: clair et accessible, pas scroll nécessaire</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
+        <v>REQ-035</v>
+      </c>
+      <c r="B36" t="str">
         <v>UI/UX</v>
       </c>
-      <c r="B36" t="str">
+      <c r="C36" t="str">
         <v>Génération questions section</v>
       </c>
-      <c r="C36" t="str">
+      <c r="D36" t="str">
         <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
       </c>
-      <c r="D36" t="str">
-        <v>P1</v>
-      </c>
       <c r="E36" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F36" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G36" t="str">
+        <v>REQ-012, REQ-013, REQ-029</v>
+      </c>
+      <c r="H36" t="str">
         <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
       </c>
-      <c r="G36" t="str">
+      <c r="I36" t="str">
         <v>État uploadingReferential: loading indicator, disabled submit</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
+        <v>REQ-036</v>
+      </c>
+      <c r="B37" t="str">
         <v>UI/UX</v>
       </c>
-      <c r="B37" t="str">
+      <c r="C37" t="str">
         <v>Référentiel documentaire section</v>
       </c>
-      <c r="C37" t="str">
+      <c r="D37" t="str">
         <v>Ajouter document avec métas, liste affichée</v>
       </c>
-      <c r="D37" t="str">
-        <v>P1</v>
-      </c>
       <c r="E37" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F37" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G37" t="str">
+        <v>REQ-017, REQ-018, REQ-029</v>
+      </c>
+      <c r="H37" t="str">
         <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
       </c>
-      <c r="G37" t="str">
+      <c r="I37" t="str">
         <v>Erreurs affichées, success feedback, état documentS refresh</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
+        <v>REQ-037</v>
+      </c>
+      <c r="B38" t="str">
         <v>UI/UX</v>
       </c>
-      <c r="B38" t="str">
+      <c r="C38" t="str">
         <v>Échelles métriques config</v>
       </c>
-      <c r="C38" t="str">
+      <c r="D38" t="str">
         <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
       </c>
-      <c r="D38" t="str">
-        <v>P1</v>
-      </c>
       <c r="E38" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F38" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G38" t="str">
+        <v>REQ-019, REQ-020, REQ-029</v>
+      </c>
+      <c r="H38" t="str">
         <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
       </c>
-      <c r="G38" t="str">
+      <c r="I38" t="str">
         <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
+        <v>REQ-038</v>
+      </c>
+      <c r="B39" t="str">
         <v>UI/UX</v>
       </c>
-      <c r="B39" t="str">
+      <c r="C39" t="str">
         <v>Dashboard avec KPIs</v>
       </c>
-      <c r="C39" t="str">
+      <c r="D39" t="str">
         <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
       </c>
-      <c r="D39" t="str">
-        <v>P1</v>
-      </c>
       <c r="E39" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F39" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G39" t="str">
+        <v>-</v>
+      </c>
+      <c r="H39" t="str">
         <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
       </c>
-      <c r="G39" t="str">
+      <c r="I39" t="str">
         <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
+        <v>REQ-039</v>
+      </c>
+      <c r="B40" t="str">
         <v>UI/UX</v>
       </c>
-      <c r="B40" t="str">
+      <c r="C40" t="str">
         <v>Gestion entretiens</v>
       </c>
-      <c r="C40" t="str">
+      <c r="D40" t="str">
         <v>Interviewés, notes questions, scoring intégré</v>
       </c>
-      <c r="D40" t="str">
-        <v>P1</v>
-      </c>
       <c r="E40" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F40" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G40" t="str">
+        <v>-</v>
+      </c>
+      <c r="H40" t="str">
         <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
       </c>
-      <c r="G40" t="str">
+      <c r="I40" t="str">
         <v>Chaque note liée criterion + interviewee + score optionnel</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
+        <v>REQ-040</v>
+      </c>
+      <c r="B41" t="str">
         <v>UI/UX</v>
       </c>
-      <c r="B41" t="str">
+      <c r="C41" t="str">
         <v>Audit log viewer</v>
       </c>
-      <c r="C41" t="str">
+      <c r="D41" t="str">
         <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
       </c>
-      <c r="D41" t="str">
-        <v>P1</v>
-      </c>
       <c r="E41" t="str">
-        <v>Complété</v>
+        <v>P1</v>
       </c>
       <c r="F41" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G41" t="str">
+        <v>REQ-039</v>
+      </c>
+      <c r="H41" t="str">
         <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
       </c>
-      <c r="G41" t="str">
+      <c r="I41" t="str">
         <v>Sync knownActions dynamiquement depuis logs récupérés</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
+        <v>REQ-041</v>
+      </c>
+      <c r="B42" t="str">
         <v>UI/UX</v>
       </c>
-      <c r="B42" t="str">
+      <c r="C42" t="str">
         <v>Export buttons</v>
       </c>
-      <c r="C42" t="str">
+      <c r="D42" t="str">
         <v>Boutons DOCX et CSV téléchargement</v>
       </c>
-      <c r="D42" t="str">
+      <c r="E42" t="str">
         <v>P2</v>
       </c>
-      <c r="E42" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F42" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G42" t="str">
+        <v>-</v>
+      </c>
+      <c r="H42" t="str">
         <v>POST /export-report et /export-csv. browser Blob download.</v>
       </c>
-      <c r="G42" t="str">
+      <c r="I42" t="str">
         <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
+        <v>REQ-042</v>
+      </c>
+      <c r="B43" t="str">
         <v>Persévérance &amp; Facilité</v>
       </c>
-      <c r="B43" t="str">
+      <c r="C43" t="str">
         <v>Documentation complète</v>
       </c>
-      <c r="C43" t="str">
+      <c r="D43" t="str">
         <v>Setup guides, quickstart, git manual, examples références</v>
       </c>
-      <c r="D43" t="str">
+      <c r="E43" t="str">
         <v>P2</v>
       </c>
-      <c r="E43" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F43" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G43" t="str">
+        <v>-</v>
+      </c>
+      <c r="H43" t="str">
         <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
       </c>
-      <c r="G43" t="str">
+      <c r="I43" t="str">
         <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
       </c>
     </row>
     <row r="44" xml:space="preserve">
       <c r="A44" t="str">
+        <v>REQ-043</v>
+      </c>
+      <c r="B44" t="str">
         <v>Persévérance &amp; Facilité</v>
       </c>
-      <c r="B44" t="str">
+      <c r="C44" t="str">
         <v>One-command installation</v>
       </c>
-      <c r="C44" t="str">
+      <c r="D44" t="str">
         <v>Non-tech user peut installer Rubis complet en 1 commande</v>
       </c>
-      <c r="D44" t="str">
+      <c r="E44" t="str">
         <v>P2</v>
       </c>
-      <c r="E44" t="str">
-        <v>Complété</v>
-      </c>
-      <c r="F44" t="str" xml:space="preserve">
+      <c r="F44" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G44" t="str">
+        <v>-</v>
+      </c>
+      <c r="H44" t="str" xml:space="preserve">
         <v xml:space="preserve">.
  install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
       </c>
-      <c r="G44" t="str">
+      <c r="I44" t="str">
         <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
       </c>
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45" t="str">
+        <v>REQ-044</v>
+      </c>
+      <c r="B45" t="str">
         <v>Persévérance &amp; Facilité</v>
       </c>
-      <c r="B45" t="str">
+      <c r="C45" t="str">
         <v>One-command launch</v>
       </c>
-      <c r="C45" t="str" xml:space="preserve">
+      <c r="D45" t="str" xml:space="preserve">
         <v xml:space="preserve">npm run dev ou .
 start-rubis.ps1 pour lancer tout</v>
       </c>
-      <c r="D45" t="str">
+      <c r="E45" t="str">
         <v>P2</v>
       </c>
-      <c r="E45" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F45" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G45" t="str">
+        <v>-</v>
+      </c>
+      <c r="H45" t="str">
         <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
       </c>
-      <c r="G45" t="str">
+      <c r="I45" t="str">
         <v>Détection auto erreurs, log output lisible</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
+        <v>REQ-045</v>
+      </c>
+      <c r="B46" t="str">
         <v>Persévérance &amp; Facilité</v>
       </c>
-      <c r="B46" t="str">
+      <c r="C46" t="str">
         <v>Clear error messages</v>
       </c>
-      <c r="C46" t="str">
+      <c r="D46" t="str">
         <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
       </c>
-      <c r="D46" t="str">
+      <c r="E46" t="str">
         <v>P2</v>
       </c>
-      <c r="E46" t="str">
-        <v>Complété</v>
-      </c>
       <c r="F46" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G46" t="str">
+        <v>-</v>
+      </c>
+      <c r="H46" t="str">
         <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
       </c>
-      <c r="G46" t="str">
+      <c r="I46" t="str">
         <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
+        <v>REQ-046</v>
+      </c>
+      <c r="B47" t="str">
         <v>Persévérance &amp; Facilité</v>
       </c>
-      <c r="B47" t="str">
+      <c r="C47" t="str">
         <v>Roadmap versioning</v>
       </c>
-      <c r="C47" t="str">
+      <c r="D47" t="str">
         <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
       </c>
-      <c r="D47" t="str">
+      <c r="E47" t="str">
         <v>P2</v>
       </c>
-      <c r="E47" t="str">
+      <c r="F47" t="str">
         <v>Planifié</v>
       </c>
-      <c r="F47" t="str">
+      <c r="G47" t="str">
+        <v>-</v>
+      </c>
+      <c r="H47" t="str">
         <v>Créer ROADMAP.xlsx avec specs, priorités, statuts, directives implémentation.</v>
       </c>
-      <c r="G47" t="str">
+      <c r="I47" t="str">
         <v>À committé dans git, mis à jour post-MVP pour v2 features</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -502,16 +502,16 @@
         <v>REQ-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Cœur métier</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C4" t="str">
-        <v>Gestion des critères d'audit</v>
+        <v>Liste déroulante référentiels sécurité</v>
       </c>
       <c r="D4" t="str">
-        <v>Code, titre, thème pour chaque critère avec lien campagne</v>
+        <v>Select avec 25+ référentiels organisés par catégories (ISO, France, Luxembourg, EU, International)</v>
       </c>
       <c r="E4" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F4" t="str">
         <v>Complété</v>
@@ -520,10 +520,10 @@
         <v>REQ-002</v>
       </c>
       <c r="H4" t="str">
-        <v>POST /criteria, GET /criteria?campaignId=. Clé étrangère campaignId.</v>
+        <v>Select dropdown dans form création campagne. Optgroups: ISO27001/27002/27005/19011, PASSI/LPM/II901/ANSSI/HDS/RGS, CSSF, NIS2/GDPR/DORA, NIST/CIS/SOC2/PCI-DSS/COBIT, Custom</v>
       </c>
       <c r="I4" t="str">
-        <v>Critères liés à campagnes pour isolation des données</v>
+        <v>Remplace input texte libre. Améliore UX et standardise les noms de référentiels. ~$*.xlsx ajouté au .gitignore</v>
       </c>
     </row>
     <row r="5">
@@ -534,10 +534,10 @@
         <v>Cœur métier</v>
       </c>
       <c r="C5" t="str">
-        <v>Génération de questions</v>
+        <v>Gestion des critères d'audit</v>
       </c>
       <c r="D5" t="str">
-        <v>Questions avec text, guidance, theme générées dynamiquement</v>
+        <v>Code, titre, thème pour chaque critère avec lien campagne</v>
       </c>
       <c r="E5" t="str">
         <v>P0</v>
@@ -546,13 +546,13 @@
         <v>Complété</v>
       </c>
       <c r="G5" t="str">
-        <v>REQ-003</v>
+        <v>REQ-002</v>
       </c>
       <c r="H5" t="str">
-        <v>POST /question, GET /questions. Schéma Zod pour validation stricte.</v>
+        <v>POST /criteria, GET /criteria?campaignId=. Clé étrangère campaignId.</v>
       </c>
       <c r="I5" t="str">
-        <v>Peut être depuis template ou IA (voir section IA)</v>
+        <v>Critères liés à campagnes pour isolation des données</v>
       </c>
     </row>
     <row r="6">
@@ -560,28 +560,28 @@
         <v>REQ-005</v>
       </c>
       <c r="B6" t="str">
-        <v>IA &amp; Génération</v>
+        <v>Cœur métier</v>
       </c>
       <c r="C6" t="str">
-        <v>Génération depuis référentiel</v>
+        <v>Génération de questions</v>
       </c>
       <c r="D6" t="str">
-        <v>Parser PDF ou Excel, extraire texte, passer à IA pour générer questions</v>
+        <v>Questions avec text, guidance, theme générées dynamiquement</v>
       </c>
       <c r="E6" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F6" t="str">
         <v>Complété</v>
       </c>
       <c r="G6" t="str">
-        <v>REQ-003</v>
+        <v>REQ-004</v>
       </c>
       <c r="H6" t="str">
-        <v>POST /generate-questions-from-referential. Multipart form. parseReferentialFile() en services/referentialParser.ts</v>
+        <v>POST /question, GET /questions. Schéma Zod pour validation stricte.</v>
       </c>
       <c r="I6" t="str">
-        <v>Limite 50KB texte extrait pour perf API</v>
+        <v>Peut être depuis template ou IA (voir section IA)</v>
       </c>
     </row>
     <row r="7">
@@ -592,10 +592,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C7" t="str">
-        <v>Dual AI strategy - OpenAI</v>
+        <v>Génération depuis référentiel</v>
       </c>
       <c r="D7" t="str">
-        <v>Intégration GPT-4o pour génération rapide et haute qualité</v>
+        <v>Parser PDF ou Excel, extraire texte, passer à IA pour générer questions</v>
       </c>
       <c r="E7" t="str">
         <v>P1</v>
@@ -604,13 +604,13 @@
         <v>Complété</v>
       </c>
       <c r="G7" t="str">
-        <v>REQ-028</v>
+        <v>REQ-004</v>
       </c>
       <c r="H7" t="str">
-        <v>generateQuestionsFromOpenAI() dans openai.ts. OpenAI client avec apiKey depuis .env</v>
+        <v>POST /generate-questions-from-referential. Multipart form. parseReferentialFile() en services/referentialParser.ts</v>
       </c>
       <c r="I7" t="str">
-        <v>Fallback si OPENAI_API_KEY absent</v>
+        <v>Limite 50KB texte extrait pour perf API</v>
       </c>
     </row>
     <row r="8">
@@ -621,10 +621,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C8" t="str">
-        <v>Dual AI strategy - Ollama local</v>
+        <v>Dual AI strategy - OpenAI</v>
       </c>
       <c r="D8" t="str">
-        <v>Ollama + Mistral/Gemma3 pour mode offline-first sur éliteBook</v>
+        <v>Intégration GPT-4o pour génération rapide et haute qualité</v>
       </c>
       <c r="E8" t="str">
         <v>P1</v>
@@ -633,13 +633,13 @@
         <v>Complété</v>
       </c>
       <c r="G8" t="str">
-        <v>REQ-028</v>
+        <v>REQ-029</v>
       </c>
       <c r="H8" t="str">
-        <v>generateQuestionsFromOllama() fetch to localhost:11434/api/generate. checkOllamaAvailable() avec timeout 2s</v>
+        <v>generateQuestionsFromOpenAI() dans openai.ts. OpenAI client avec apiKey depuis .env</v>
       </c>
       <c r="I8" t="str">
-        <v>Auto-détection Ollama, fallback depuis OpenAI si non dispo</v>
+        <v>Fallback si OPENAI_API_KEY absent</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C9" t="str">
-        <v>Model switching UI</v>
+        <v>Dual AI strategy - Ollama local</v>
       </c>
       <c r="D9" t="str">
-        <v>Permuter entre mistral et gemma3:4b directement dans l'appli</v>
+        <v>Ollama + Mistral/Gemma3 pour mode offline-first sur éliteBook</v>
       </c>
       <c r="E9" t="str">
         <v>P1</v>
@@ -662,13 +662,13 @@
         <v>Complété</v>
       </c>
       <c r="G9" t="str">
-        <v>REQ-006, REQ-007</v>
+        <v>REQ-029</v>
       </c>
       <c r="H9" t="str">
-        <v>GET/POST /config endpoints. État currentOllamaModel dans server.ts. Boutons UI dans App.tsx 'Configuration IA'</v>
+        <v>generateQuestionsFromOllama() fetch to localhost:11434/api/generate. checkOllamaAvailable() avec timeout 2s</v>
       </c>
       <c r="I9" t="str">
-        <v>Changement runtime, pas besoin restart API</v>
+        <v>Auto-détection Ollama, fallback depuis OpenAI si non dispo</v>
       </c>
     </row>
     <row r="10">
@@ -679,10 +679,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C10" t="str">
-        <v>Parsing référentiel multi-format</v>
+        <v>Model switching UI</v>
       </c>
       <c r="D10" t="str">
-        <v>Support PDF et Excel avec extraction de texte</v>
+        <v>Permuter entre mistral et gemma3:4b directement dans l'appli</v>
       </c>
       <c r="E10" t="str">
         <v>P1</v>
@@ -691,13 +691,13 @@
         <v>Complété</v>
       </c>
       <c r="G10" t="str">
-        <v>REQ-005</v>
+        <v>REQ-007, REQ-008</v>
       </c>
       <c r="H10" t="str">
-        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
+        <v>GET/POST /config endpoints. État currentOllamaModel dans server.ts. Boutons UI dans App.tsx 'Configuration IA'</v>
       </c>
       <c r="I10" t="str">
-        <v>Gère encodages UTF-8, caractères spéciaux</v>
+        <v>Changement runtime, pas besoin restart API</v>
       </c>
     </row>
     <row r="11">
@@ -708,10 +708,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C11" t="str">
-        <v>Prompt dynamique contextuel</v>
+        <v>Parsing référentiel multi-format</v>
       </c>
       <c r="D11" t="str">
-        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
+        <v>Support PDF et Excel avec extraction de texte</v>
       </c>
       <c r="E11" t="str">
         <v>P1</v>
@@ -720,13 +720,13 @@
         <v>Complété</v>
       </c>
       <c r="G11" t="str">
-        <v>REQ-005</v>
+        <v>REQ-006</v>
       </c>
       <c r="H11" t="str">
-        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
+        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
       </c>
       <c r="I11" t="str">
-        <v>Zod validation sur count (1-10), language (fr/en)</v>
+        <v>Gère encodages UTF-8, caractères spéciaux</v>
       </c>
     </row>
     <row r="12">
@@ -734,28 +734,28 @@
         <v>REQ-011</v>
       </c>
       <c r="B12" t="str">
-        <v>Structuration données</v>
+        <v>IA &amp; Génération</v>
       </c>
       <c r="C12" t="str">
-        <v>Modèle Document</v>
+        <v>Prompt dynamique contextuel</v>
       </c>
       <c r="D12" t="str">
-        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
+        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
       </c>
       <c r="E12" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F12" t="str">
         <v>Complété</v>
       </c>
       <c r="G12" t="str">
-        <v>REQ-002</v>
+        <v>REQ-006</v>
       </c>
       <c r="H12" t="str">
-        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
+        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
       </c>
       <c r="I12" t="str">
-        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
+        <v>Zod validation sur count (1-10), language (fr/en)</v>
       </c>
     </row>
     <row r="13">
@@ -766,10 +766,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C13" t="str">
-        <v>Modèle Interviewé</v>
+        <v>Modèle Document</v>
       </c>
       <c r="D13" t="str">
-        <v>Nom complet, rôle, lié à campaign</v>
+        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
       </c>
       <c r="E13" t="str">
         <v>P0</v>
@@ -781,10 +781,10 @@
         <v>REQ-002</v>
       </c>
       <c r="H13" t="str">
-        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
+        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
       </c>
       <c r="I13" t="str">
-        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
+        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
       </c>
     </row>
     <row r="14">
@@ -795,10 +795,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C14" t="str">
-        <v>Modèle Note d'entretien</v>
+        <v>Modèle Interviewé</v>
       </c>
       <c r="D14" t="str">
-        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
+        <v>Nom complet, rôle, lié à campaign</v>
       </c>
       <c r="E14" t="str">
         <v>P0</v>
@@ -807,13 +807,13 @@
         <v>Complété</v>
       </c>
       <c r="G14" t="str">
-        <v>REQ-003, REQ-012</v>
+        <v>REQ-002</v>
       </c>
       <c r="H14" t="str">
-        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
+        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
       </c>
       <c r="I14" t="str">
-        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
+        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
       </c>
     </row>
     <row r="15">
@@ -824,25 +824,25 @@
         <v>Structuration données</v>
       </c>
       <c r="C15" t="str">
-        <v>Matrice de conformité</v>
+        <v>Modèle Note d'entretien</v>
       </c>
       <c r="D15" t="str">
-        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
+        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
       </c>
       <c r="E15" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F15" t="str">
         <v>Complété</v>
       </c>
       <c r="G15" t="str">
-        <v>REQ-013</v>
+        <v>REQ-004, REQ-013</v>
       </c>
       <c r="H15" t="str">
-        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
+        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
       </c>
       <c r="I15" t="str">
-        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
+        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
       </c>
     </row>
     <row r="16">
@@ -853,10 +853,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C16" t="str">
-        <v>Configuration Métriques</v>
+        <v>Matrice de conformité</v>
       </c>
       <c r="D16" t="str">
-        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
+        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
       </c>
       <c r="E16" t="str">
         <v>P1</v>
@@ -865,13 +865,13 @@
         <v>Complété</v>
       </c>
       <c r="G16" t="str">
-        <v>REQ-002</v>
+        <v>REQ-014</v>
       </c>
       <c r="H16" t="str">
-        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
+        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
       </c>
       <c r="I16" t="str">
-        <v>Format texte (ex: '1-5') pour flexibilité</v>
+        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
       </c>
     </row>
     <row r="17">
@@ -879,13 +879,13 @@
         <v>REQ-016</v>
       </c>
       <c r="B17" t="str">
-        <v>Audit &amp; Traçabilité</v>
+        <v>Structuration données</v>
       </c>
       <c r="C17" t="str">
-        <v>Audit Log complet</v>
+        <v>Configuration Métriques</v>
       </c>
       <c r="D17" t="str">
-        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
+        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
       </c>
       <c r="E17" t="str">
         <v>P1</v>
@@ -894,13 +894,13 @@
         <v>Complété</v>
       </c>
       <c r="G17" t="str">
-        <v>REQ-002, REQ-028</v>
+        <v>REQ-002</v>
       </c>
       <c r="H17" t="str">
-        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
+        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
       </c>
       <c r="I17" t="str">
-        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
+        <v>Format texte (ex: '1-5') pour flexibilité</v>
       </c>
     </row>
     <row r="18">
@@ -911,10 +911,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C18" t="str">
-        <v>Filtrage logs par période</v>
+        <v>Audit Log complet</v>
       </c>
       <c r="D18" t="str">
-        <v>Vue 7j, 30j, tout (by date range filter)</v>
+        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
       </c>
       <c r="E18" t="str">
         <v>P1</v>
@@ -923,13 +923,13 @@
         <v>Complété</v>
       </c>
       <c r="G18" t="str">
-        <v>REQ-016</v>
+        <v>REQ-002, REQ-029</v>
       </c>
       <c r="H18" t="str">
-        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
+        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
       </c>
       <c r="I18" t="str">
-        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
+        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
       </c>
     </row>
     <row r="19">
@@ -940,10 +940,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C19" t="str">
-        <v>Filtrage logs par action</v>
+        <v>Filtrage logs par période</v>
       </c>
       <c r="D19" t="str">
-        <v>Filter sur type d'action (campaign.created, etc.)</v>
+        <v>Vue 7j, 30j, tout (by date range filter)</v>
       </c>
       <c r="E19" t="str">
         <v>P1</v>
@@ -952,13 +952,13 @@
         <v>Complété</v>
       </c>
       <c r="G19" t="str">
-        <v>REQ-016</v>
+        <v>REQ-017</v>
       </c>
       <c r="H19" t="str">
-        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
+        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
       </c>
       <c r="I19" t="str">
-        <v>Enum actions découvertes dynamiquement from logs</v>
+        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
       </c>
     </row>
     <row r="20">
@@ -966,28 +966,28 @@
         <v>REQ-019</v>
       </c>
       <c r="B20" t="str">
-        <v>Rapports &amp; Exports</v>
+        <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C20" t="str">
-        <v>Export DOCX</v>
+        <v>Filtrage logs par action</v>
       </c>
       <c r="D20" t="str">
-        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
+        <v>Filter sur type d'action (campaign.created, etc.)</v>
       </c>
       <c r="E20" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F20" t="str">
         <v>Complété</v>
       </c>
       <c r="G20" t="str">
-        <v>REQ-004, REQ-014</v>
+        <v>REQ-017</v>
       </c>
       <c r="H20" t="str">
-        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
+        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
       </c>
       <c r="I20" t="str">
-        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
+        <v>Enum actions découvertes dynamiquement from logs</v>
       </c>
     </row>
     <row r="21">
@@ -998,10 +998,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C21" t="str">
-        <v>Export CSV</v>
+        <v>Export DOCX</v>
       </c>
       <c r="D21" t="str">
-        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
+        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
       </c>
       <c r="E21" t="str">
         <v>P2</v>
@@ -1010,13 +1010,13 @@
         <v>Complété</v>
       </c>
       <c r="G21" t="str">
-        <v>REQ-014, REQ-016</v>
+        <v>REQ-005, REQ-015</v>
       </c>
       <c r="H21" t="str">
-        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
+        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
       </c>
       <c r="I21" t="str">
-        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
+        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
       </c>
     </row>
     <row r="22">
@@ -1027,10 +1027,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C22" t="str">
-        <v>Gestion des rapports</v>
+        <v>Export CSV</v>
       </c>
       <c r="D22" t="str">
-        <v>Stocker rapports générés avec titre, date gen, version</v>
+        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
       </c>
       <c r="E22" t="str">
         <v>P2</v>
@@ -1039,13 +1039,13 @@
         <v>Complété</v>
       </c>
       <c r="G22" t="str">
-        <v>REQ-019, REQ-020</v>
+        <v>REQ-015, REQ-017</v>
       </c>
       <c r="H22" t="str">
-        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
+        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
       </c>
       <c r="I22" t="str">
-        <v>Récupérable dans UI, archivé pour traçabilité</v>
+        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
       </c>
     </row>
     <row r="23">
@@ -1053,28 +1053,28 @@
         <v>REQ-022</v>
       </c>
       <c r="B23" t="str">
-        <v>Dashboard &amp; Visualisation</v>
+        <v>Rapports &amp; Exports</v>
       </c>
       <c r="C23" t="str">
-        <v>KPIs essentiels</v>
+        <v>Gestion des rapports</v>
       </c>
       <c r="D23" t="str">
-        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
+        <v>Stocker rapports générés avec titre, date gen, version</v>
       </c>
       <c r="E23" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F23" t="str">
         <v>Complété</v>
       </c>
       <c r="G23" t="str">
-        <v>REQ-011, REQ-012, REQ-013</v>
+        <v>REQ-020, REQ-021</v>
       </c>
       <c r="H23" t="str">
-        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
+        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
       </c>
       <c r="I23" t="str">
-        <v>Affiché en gros chiffres zone haute dashboard</v>
+        <v>Récupérable dans UI, archivé pour traçabilité</v>
       </c>
     </row>
     <row r="24">
@@ -1085,25 +1085,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C24" t="str">
-        <v>Matrice de conformité interactive</v>
+        <v>KPIs essentiels</v>
       </c>
       <c r="D24" t="str">
-        <v>Tableau avec % conformité par criterion, tri/filtre</v>
+        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
       </c>
       <c r="E24" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F24" t="str">
         <v>Complété</v>
       </c>
       <c r="G24" t="str">
-        <v>REQ-014</v>
+        <v>REQ-012, REQ-013, REQ-014</v>
       </c>
       <c r="H24" t="str">
-        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
+        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
       </c>
       <c r="I24" t="str">
-        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
+        <v>Affiché en gros chiffres zone haute dashboard</v>
       </c>
     </row>
     <row r="25">
@@ -1114,25 +1114,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C25" t="str">
-        <v>Graphiques optionnels (futur)</v>
+        <v>Matrice de conformité interactive</v>
       </c>
       <c r="D25" t="str">
-        <v>Tendances audit timeline, pie charts conformity domains</v>
+        <v>Tableau avec % conformité par criterion, tri/filtre</v>
       </c>
       <c r="E25" t="str">
-        <v>P3</v>
+        <v>P2</v>
       </c>
       <c r="F25" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G25" t="str">
-        <v>REQ-022</v>
+        <v>REQ-015</v>
       </c>
       <c r="H25" t="str">
-        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
+        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
       </c>
       <c r="I25" t="str">
-        <v>MVP n'a pas graphiques, architecture prête pour.</v>
+        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
       </c>
     </row>
     <row r="26">
@@ -1140,28 +1140,28 @@
         <v>REQ-025</v>
       </c>
       <c r="B26" t="str">
-        <v>Configuration &amp; Flexibilité</v>
+        <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C26" t="str">
-        <v>Support multilingue</v>
+        <v>Graphiques optionnels (futur)</v>
       </c>
       <c r="D26" t="str">
-        <v>FR et EN, sélection par campaign</v>
+        <v>Tendances audit timeline, pie charts conformity domains</v>
       </c>
       <c r="E26" t="str">
-        <v>P1</v>
+        <v>P3</v>
       </c>
       <c r="F26" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G26" t="str">
-        <v>REQ-028</v>
+        <v>REQ-023</v>
       </c>
       <c r="H26" t="str">
-        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
+        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
       </c>
       <c r="I26" t="str">
-        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
+        <v>MVP n'a pas graphiques, architecture prête pour.</v>
       </c>
     </row>
     <row r="27">
@@ -1172,10 +1172,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C27" t="str">
-        <v>Modèle Ollama configurable</v>
+        <v>Support multilingue</v>
       </c>
       <c r="D27" t="str">
-        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
+        <v>FR et EN, sélection par campaign</v>
       </c>
       <c r="E27" t="str">
         <v>P1</v>
@@ -1184,13 +1184,13 @@
         <v>Complété</v>
       </c>
       <c r="G27" t="str">
-        <v>REQ-007</v>
+        <v>REQ-029</v>
       </c>
       <c r="H27" t="str">
-        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
+        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
       </c>
       <c r="I27" t="str">
-        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
+        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
       </c>
     </row>
     <row r="28">
@@ -1201,10 +1201,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C28" t="str">
-        <v>OpenAI optionnel</v>
+        <v>Modèle Ollama configurable</v>
       </c>
       <c r="D28" t="str">
-        <v>API key via .env, fallback auto Ollama si absent</v>
+        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
       </c>
       <c r="E28" t="str">
         <v>P1</v>
@@ -1213,13 +1213,13 @@
         <v>Complété</v>
       </c>
       <c r="G28" t="str">
-        <v>REQ-028</v>
+        <v>REQ-008</v>
       </c>
       <c r="H28" t="str">
-        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
+        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
       </c>
       <c r="I28" t="str">
-        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
+        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
       </c>
     </row>
     <row r="29">
@@ -1230,25 +1230,25 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C29" t="str">
-        <v>Thèmes personnalisés</v>
+        <v>OpenAI optionnel</v>
       </c>
       <c r="D29" t="str">
-        <v>Texte libre pour documents et questions</v>
+        <v>API key via .env, fallback auto Ollama si absent</v>
       </c>
       <c r="E29" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F29" t="str">
         <v>Complété</v>
       </c>
       <c r="G29" t="str">
-        <v>-</v>
+        <v>REQ-029</v>
       </c>
       <c r="H29" t="str">
-        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
+        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
       </c>
       <c r="I29" t="str">
-        <v>Permet flexibilité sur domaines audit custom</v>
+        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
       </c>
     </row>
     <row r="30">
@@ -1256,16 +1256,16 @@
         <v>REQ-029</v>
       </c>
       <c r="B30" t="str">
-        <v>Infrastructure &amp; Déploiement</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C30" t="str">
-        <v>Offline-first capability</v>
+        <v>Thèmes personnalisés</v>
       </c>
       <c r="D30" t="str">
-        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
+        <v>Texte libre pour documents et questions</v>
       </c>
       <c r="E30" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F30" t="str">
         <v>Complété</v>
@@ -1274,10 +1274,10 @@
         <v>-</v>
       </c>
       <c r="H30" t="str">
-        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
+        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
       </c>
       <c r="I30" t="str">
-        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
+        <v>Permet flexibilité sur domaines audit custom</v>
       </c>
     </row>
     <row r="31">
@@ -1288,25 +1288,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C31" t="str">
-        <v>Automation PowerShell</v>
+        <v>Offline-first capability</v>
       </c>
       <c r="D31" t="str">
-        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
+        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
       </c>
       <c r="E31" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F31" t="str">
         <v>Complété</v>
       </c>
       <c r="G31" t="str">
-        <v>REQ-026, REQ-029</v>
+        <v>-</v>
       </c>
       <c r="H31" t="str">
-        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
+        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
       </c>
       <c r="I31" t="str">
-        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
+        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
       </c>
     </row>
     <row r="32">
@@ -1317,25 +1317,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C32" t="str">
-        <v>Versionning Git &amp; GitHub</v>
+        <v>Automation PowerShell</v>
       </c>
       <c r="D32" t="str">
-        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
+        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
       </c>
       <c r="E32" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F32" t="str">
         <v>Complété</v>
       </c>
       <c r="G32" t="str">
-        <v>REQ-005, REQ-029</v>
+        <v>REQ-027, REQ-030</v>
       </c>
       <c r="H32" t="str">
-        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
+        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
       </c>
       <c r="I32" t="str">
-        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
+        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
       </c>
     </row>
     <row r="33">
@@ -1346,25 +1346,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C33" t="str">
-        <v>API REST Fastify</v>
+        <v>Versionning Git &amp; GitHub</v>
       </c>
       <c r="D33" t="str">
-        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
+        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
       </c>
       <c r="E33" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F33" t="str">
         <v>Complété</v>
       </c>
       <c r="G33" t="str">
-        <v>REQ-011, REQ-029</v>
+        <v>REQ-006, REQ-030</v>
       </c>
       <c r="H33" t="str">
-        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
+        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
       </c>
       <c r="I33" t="str">
-        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
+        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
       </c>
     </row>
     <row r="34">
@@ -1372,28 +1372,28 @@
         <v>REQ-033</v>
       </c>
       <c r="B34" t="str">
-        <v>UI/UX</v>
+        <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C34" t="str">
-        <v>UI React + TypeScript + Vite</v>
+        <v>API REST Fastify</v>
       </c>
       <c r="D34" t="str">
-        <v>Bundling optimisé, HMR dev mode</v>
+        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
       </c>
       <c r="E34" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F34" t="str">
         <v>Complété</v>
       </c>
       <c r="G34" t="str">
-        <v>REQ-015, REQ-029</v>
+        <v>REQ-012, REQ-030</v>
       </c>
       <c r="H34" t="str">
-        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
+        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
       </c>
       <c r="I34" t="str">
-        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
+        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
       </c>
     </row>
     <row r="35">
@@ -1404,10 +1404,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C35" t="str">
-        <v>Configuration IA section</v>
+        <v>UI React + TypeScript + Vite</v>
       </c>
       <c r="D35" t="str">
-        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
+        <v>Bundling optimisé, HMR dev mode</v>
       </c>
       <c r="E35" t="str">
         <v>P1</v>
@@ -1416,13 +1416,13 @@
         <v>Complété</v>
       </c>
       <c r="G35" t="str">
-        <v>REQ-022, REQ-029</v>
+        <v>REQ-016, REQ-030</v>
       </c>
       <c r="H35" t="str">
-        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
+        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
       </c>
       <c r="I35" t="str">
-        <v>UX: clair et accessible, pas scroll nécessaire</v>
+        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
       </c>
     </row>
     <row r="36">
@@ -1433,10 +1433,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C36" t="str">
-        <v>Génération questions section</v>
+        <v>Configuration IA section</v>
       </c>
       <c r="D36" t="str">
-        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
+        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
       </c>
       <c r="E36" t="str">
         <v>P1</v>
@@ -1445,13 +1445,13 @@
         <v>Complété</v>
       </c>
       <c r="G36" t="str">
-        <v>REQ-012, REQ-013, REQ-029</v>
+        <v>REQ-023, REQ-030</v>
       </c>
       <c r="H36" t="str">
-        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
+        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
       </c>
       <c r="I36" t="str">
-        <v>État uploadingReferential: loading indicator, disabled submit</v>
+        <v>UX: clair et accessible, pas scroll nécessaire</v>
       </c>
     </row>
     <row r="37">
@@ -1462,10 +1462,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C37" t="str">
-        <v>Référentiel documentaire section</v>
+        <v>Génération questions section</v>
       </c>
       <c r="D37" t="str">
-        <v>Ajouter document avec métas, liste affichée</v>
+        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
       </c>
       <c r="E37" t="str">
         <v>P1</v>
@@ -1474,13 +1474,13 @@
         <v>Complété</v>
       </c>
       <c r="G37" t="str">
-        <v>REQ-017, REQ-018, REQ-029</v>
+        <v>REQ-013, REQ-014, REQ-030</v>
       </c>
       <c r="H37" t="str">
-        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
+        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
       </c>
       <c r="I37" t="str">
-        <v>Erreurs affichées, success feedback, état documentS refresh</v>
+        <v>État uploadingReferential: loading indicator, disabled submit</v>
       </c>
     </row>
     <row r="38">
@@ -1491,10 +1491,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C38" t="str">
-        <v>Échelles métriques config</v>
+        <v>Référentiel documentaire section</v>
       </c>
       <c r="D38" t="str">
-        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
+        <v>Ajouter document avec métas, liste affichée</v>
       </c>
       <c r="E38" t="str">
         <v>P1</v>
@@ -1503,13 +1503,13 @@
         <v>Complété</v>
       </c>
       <c r="G38" t="str">
-        <v>REQ-019, REQ-020, REQ-029</v>
+        <v>REQ-018, REQ-019, REQ-030</v>
       </c>
       <c r="H38" t="str">
-        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
+        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
       </c>
       <c r="I38" t="str">
-        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
+        <v>Erreurs affichées, success feedback, état documentS refresh</v>
       </c>
     </row>
     <row r="39">
@@ -1520,10 +1520,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C39" t="str">
-        <v>Dashboard avec KPIs</v>
+        <v>Échelles métriques config</v>
       </c>
       <c r="D39" t="str">
-        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
+        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
       </c>
       <c r="E39" t="str">
         <v>P1</v>
@@ -1532,13 +1532,13 @@
         <v>Complété</v>
       </c>
       <c r="G39" t="str">
-        <v>-</v>
+        <v>REQ-020, REQ-021, REQ-030</v>
       </c>
       <c r="H39" t="str">
-        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
+        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
       </c>
       <c r="I39" t="str">
-        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
+        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
       </c>
     </row>
     <row r="40">
@@ -1549,10 +1549,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C40" t="str">
-        <v>Gestion entretiens</v>
+        <v>Dashboard avec KPIs</v>
       </c>
       <c r="D40" t="str">
-        <v>Interviewés, notes questions, scoring intégré</v>
+        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
       </c>
       <c r="E40" t="str">
         <v>P1</v>
@@ -1564,10 +1564,10 @@
         <v>-</v>
       </c>
       <c r="H40" t="str">
-        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
+        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
       </c>
       <c r="I40" t="str">
-        <v>Chaque note liée criterion + interviewee + score optionnel</v>
+        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
       </c>
     </row>
     <row r="41">
@@ -1578,10 +1578,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C41" t="str">
-        <v>Audit log viewer</v>
+        <v>Gestion entretiens</v>
       </c>
       <c r="D41" t="str">
-        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
+        <v>Interviewés, notes questions, scoring intégré</v>
       </c>
       <c r="E41" t="str">
         <v>P1</v>
@@ -1590,13 +1590,13 @@
         <v>Complété</v>
       </c>
       <c r="G41" t="str">
-        <v>REQ-039</v>
+        <v>-</v>
       </c>
       <c r="H41" t="str">
-        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
+        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
       </c>
       <c r="I41" t="str">
-        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
+        <v>Chaque note liée criterion + interviewee + score optionnel</v>
       </c>
     </row>
     <row r="42">
@@ -1607,25 +1607,25 @@
         <v>UI/UX</v>
       </c>
       <c r="C42" t="str">
-        <v>Export buttons</v>
+        <v>Audit log viewer</v>
       </c>
       <c r="D42" t="str">
-        <v>Boutons DOCX et CSV téléchargement</v>
+        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
       </c>
       <c r="E42" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F42" t="str">
         <v>Complété</v>
       </c>
       <c r="G42" t="str">
-        <v>-</v>
+        <v>REQ-040</v>
       </c>
       <c r="H42" t="str">
-        <v>POST /export-report et /export-csv. browser Blob download.</v>
+        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
       </c>
       <c r="I42" t="str">
-        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
       </c>
     </row>
     <row r="43">
@@ -1633,13 +1633,13 @@
         <v>REQ-042</v>
       </c>
       <c r="B43" t="str">
-        <v>Persévérance &amp; Facilité</v>
+        <v>UI/UX</v>
       </c>
       <c r="C43" t="str">
-        <v>Documentation complète</v>
+        <v>Export buttons</v>
       </c>
       <c r="D43" t="str">
-        <v>Setup guides, quickstart, git manual, examples références</v>
+        <v>Boutons DOCX et CSV téléchargement</v>
       </c>
       <c r="E43" t="str">
         <v>P2</v>
@@ -1651,13 +1651,13 @@
         <v>-</v>
       </c>
       <c r="H43" t="str">
-        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
+        <v>POST /export-report et /export-csv. browser Blob download.</v>
       </c>
       <c r="I43" t="str">
-        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
-      </c>
-    </row>
-    <row r="44" xml:space="preserve">
+        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" t="str">
         <v>REQ-043</v>
       </c>
@@ -1665,10 +1665,10 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C44" t="str">
-        <v>One-command installation</v>
+        <v>Documentation complète</v>
       </c>
       <c r="D44" t="str">
-        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+        <v>Setup guides, quickstart, git manual, examples références</v>
       </c>
       <c r="E44" t="str">
         <v>P2</v>
@@ -1679,12 +1679,11 @@
       <c r="G44" t="str">
         <v>-</v>
       </c>
-      <c r="H44" t="str" xml:space="preserve">
-        <v xml:space="preserve">.
- install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      <c r="H44" t="str">
+        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
       </c>
       <c r="I44" t="str">
-        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
       </c>
     </row>
     <row r="45" xml:space="preserve">
@@ -1695,41 +1694,42 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C45" t="str">
+        <v>One-command installation</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+      </c>
+      <c r="E45" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G45" t="str">
+        <v>-</v>
+      </c>
+      <c r="H45" t="str" xml:space="preserve">
+        <v xml:space="preserve">.
+ install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      </c>
+      <c r="I45" t="str">
+        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>REQ-045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C46" t="str">
         <v>One-command launch</v>
       </c>
-      <c r="D45" t="str" xml:space="preserve">
+      <c r="D46" t="str" xml:space="preserve">
         <v xml:space="preserve">npm run dev ou .
 start-rubis.ps1 pour lancer tout</v>
       </c>
-      <c r="E45" t="str">
-        <v>P2</v>
-      </c>
-      <c r="F45" t="str">
-        <v>Complété</v>
-      </c>
-      <c r="G45" t="str">
-        <v>-</v>
-      </c>
-      <c r="H45" t="str">
-        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
-      </c>
-      <c r="I45" t="str">
-        <v>Détection auto erreurs, log output lisible</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>REQ-045</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Persévérance &amp; Facilité</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Clear error messages</v>
-      </c>
-      <c r="D46" t="str">
-        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
-      </c>
       <c r="E46" t="str">
         <v>P2</v>
       </c>
@@ -1740,10 +1740,10 @@
         <v>-</v>
       </c>
       <c r="H46" t="str">
-        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
       </c>
       <c r="I46" t="str">
-        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+        <v>Détection auto erreurs, log output lisible</v>
       </c>
     </row>
     <row r="47">
@@ -1754,30 +1754,59 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C47" t="str">
-        <v>Roadmap versioning</v>
+        <v>Clear error messages</v>
       </c>
       <c r="D47" t="str">
-        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
       </c>
       <c r="E47" t="str">
         <v>P2</v>
       </c>
       <c r="F47" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G47" t="str">
         <v>-</v>
       </c>
       <c r="H47" t="str">
+        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>REQ-047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Roadmap versioning</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+      </c>
+      <c r="E48" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G48" t="str">
+        <v>-</v>
+      </c>
+      <c r="H48" t="str">
         <v>Créer ROADMAP.xlsx avec specs, priorités, statuts, directives implémentation.</v>
       </c>
-      <c r="I47" t="str">
+      <c r="I48" t="str">
         <v>À committé dans git, mis à jour post-MVP pour v2 features</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I48"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -531,28 +531,28 @@
         <v>REQ-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Cœur métier</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C5" t="str">
-        <v>Gestion des critères d'audit</v>
+        <v>Module administration des référentiels</v>
       </c>
       <c r="D5" t="str">
-        <v>Code, titre, thème pour chaque critère avec lien campagne</v>
+        <v>Interface admin pour ajouter/modifier/supprimer les référentiels disponibles dynamiquement</v>
       </c>
       <c r="E5" t="str">
-        <v>P0</v>
+        <v>P2</v>
       </c>
       <c r="F5" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G5" t="str">
-        <v>REQ-002</v>
+        <v>REQ-003, REQ-030</v>
       </c>
       <c r="H5" t="str">
-        <v>POST /criteria, GET /criteria?campaignId=. Clé étrangère campaignId.</v>
+        <v>Section admin protégée. CRUD référentiels: POST/PUT/DELETE /admin/referentials. Stockage db.data.referentials avec {id, name, category, description, isActive}. UI table éditable avec formulaire modal.</v>
       </c>
       <c r="I5" t="str">
-        <v>Critères liés à campagnes pour isolation des données</v>
+        <v>Permet personnalisation sans modifier le code. Validation côté serveur. Export/Import JSON pour backup.</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +563,10 @@
         <v>Cœur métier</v>
       </c>
       <c r="C6" t="str">
-        <v>Génération de questions</v>
+        <v>Gestion des critères d'audit</v>
       </c>
       <c r="D6" t="str">
-        <v>Questions avec text, guidance, theme générées dynamiquement</v>
+        <v>Code, titre, thème pour chaque critère avec lien campagne</v>
       </c>
       <c r="E6" t="str">
         <v>P0</v>
@@ -575,13 +575,13 @@
         <v>Complété</v>
       </c>
       <c r="G6" t="str">
-        <v>REQ-004</v>
+        <v>REQ-002</v>
       </c>
       <c r="H6" t="str">
-        <v>POST /question, GET /questions. Schéma Zod pour validation stricte.</v>
+        <v>POST /criteria, GET /criteria?campaignId=. Clé étrangère campaignId.</v>
       </c>
       <c r="I6" t="str">
-        <v>Peut être depuis template ou IA (voir section IA)</v>
+        <v>Critères liés à campagnes pour isolation des données</v>
       </c>
     </row>
     <row r="7">
@@ -589,28 +589,28 @@
         <v>REQ-006</v>
       </c>
       <c r="B7" t="str">
-        <v>IA &amp; Génération</v>
+        <v>Cœur métier</v>
       </c>
       <c r="C7" t="str">
-        <v>Génération depuis référentiel</v>
+        <v>Génération de questions</v>
       </c>
       <c r="D7" t="str">
-        <v>Parser PDF ou Excel, extraire texte, passer à IA pour générer questions</v>
+        <v>Questions avec text, guidance, theme générées dynamiquement</v>
       </c>
       <c r="E7" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F7" t="str">
         <v>Complété</v>
       </c>
       <c r="G7" t="str">
-        <v>REQ-004</v>
+        <v>REQ-005</v>
       </c>
       <c r="H7" t="str">
-        <v>POST /generate-questions-from-referential. Multipart form. parseReferentialFile() en services/referentialParser.ts</v>
+        <v>POST /question, GET /questions. Schéma Zod pour validation stricte.</v>
       </c>
       <c r="I7" t="str">
-        <v>Limite 50KB texte extrait pour perf API</v>
+        <v>Peut être depuis template ou IA (voir section IA)</v>
       </c>
     </row>
     <row r="8">
@@ -621,10 +621,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C8" t="str">
-        <v>Dual AI strategy - OpenAI</v>
+        <v>Génération depuis référentiel</v>
       </c>
       <c r="D8" t="str">
-        <v>Intégration GPT-4o pour génération rapide et haute qualité</v>
+        <v>Parser PDF ou Excel, extraire texte, passer à IA pour générer questions</v>
       </c>
       <c r="E8" t="str">
         <v>P1</v>
@@ -633,13 +633,13 @@
         <v>Complété</v>
       </c>
       <c r="G8" t="str">
-        <v>REQ-029</v>
+        <v>REQ-005</v>
       </c>
       <c r="H8" t="str">
-        <v>generateQuestionsFromOpenAI() dans openai.ts. OpenAI client avec apiKey depuis .env</v>
+        <v>POST /generate-questions-from-referential. Multipart form. parseReferentialFile() en services/referentialParser.ts</v>
       </c>
       <c r="I8" t="str">
-        <v>Fallback si OPENAI_API_KEY absent</v>
+        <v>Limite 50KB texte extrait pour perf API</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C9" t="str">
-        <v>Dual AI strategy - Ollama local</v>
+        <v>Dual AI strategy - OpenAI</v>
       </c>
       <c r="D9" t="str">
-        <v>Ollama + Mistral/Gemma3 pour mode offline-first sur éliteBook</v>
+        <v>Intégration GPT-4o pour génération rapide et haute qualité</v>
       </c>
       <c r="E9" t="str">
         <v>P1</v>
@@ -662,13 +662,13 @@
         <v>Complété</v>
       </c>
       <c r="G9" t="str">
-        <v>REQ-029</v>
+        <v>REQ-030</v>
       </c>
       <c r="H9" t="str">
-        <v>generateQuestionsFromOllama() fetch to localhost:11434/api/generate. checkOllamaAvailable() avec timeout 2s</v>
+        <v>generateQuestionsFromOpenAI() dans openai.ts. OpenAI client avec apiKey depuis .env</v>
       </c>
       <c r="I9" t="str">
-        <v>Auto-détection Ollama, fallback depuis OpenAI si non dispo</v>
+        <v>Fallback si OPENAI_API_KEY absent</v>
       </c>
     </row>
     <row r="10">
@@ -679,10 +679,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C10" t="str">
-        <v>Model switching UI</v>
+        <v>Dual AI strategy - Ollama local</v>
       </c>
       <c r="D10" t="str">
-        <v>Permuter entre mistral et gemma3:4b directement dans l'appli</v>
+        <v>Ollama + Mistral/Gemma3 pour mode offline-first sur éliteBook</v>
       </c>
       <c r="E10" t="str">
         <v>P1</v>
@@ -691,13 +691,13 @@
         <v>Complété</v>
       </c>
       <c r="G10" t="str">
-        <v>REQ-007, REQ-008</v>
+        <v>REQ-030</v>
       </c>
       <c r="H10" t="str">
-        <v>GET/POST /config endpoints. État currentOllamaModel dans server.ts. Boutons UI dans App.tsx 'Configuration IA'</v>
+        <v>generateQuestionsFromOllama() fetch to localhost:11434/api/generate. checkOllamaAvailable() avec timeout 2s</v>
       </c>
       <c r="I10" t="str">
-        <v>Changement runtime, pas besoin restart API</v>
+        <v>Auto-détection Ollama, fallback depuis OpenAI si non dispo</v>
       </c>
     </row>
     <row r="11">
@@ -708,10 +708,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C11" t="str">
-        <v>Parsing référentiel multi-format</v>
+        <v>Model switching UI</v>
       </c>
       <c r="D11" t="str">
-        <v>Support PDF et Excel avec extraction de texte</v>
+        <v>Permuter entre mistral et gemma3:4b directement dans l'appli</v>
       </c>
       <c r="E11" t="str">
         <v>P1</v>
@@ -720,13 +720,13 @@
         <v>Complété</v>
       </c>
       <c r="G11" t="str">
-        <v>REQ-006</v>
+        <v>REQ-008, REQ-009</v>
       </c>
       <c r="H11" t="str">
-        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
+        <v>GET/POST /config endpoints. État currentOllamaModel dans server.ts. Boutons UI dans App.tsx 'Configuration IA'</v>
       </c>
       <c r="I11" t="str">
-        <v>Gère encodages UTF-8, caractères spéciaux</v>
+        <v>Changement runtime, pas besoin restart API</v>
       </c>
     </row>
     <row r="12">
@@ -737,10 +737,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C12" t="str">
-        <v>Prompt dynamique contextuel</v>
+        <v>Parsing référentiel multi-format</v>
       </c>
       <c r="D12" t="str">
-        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
+        <v>Support PDF et Excel avec extraction de texte</v>
       </c>
       <c r="E12" t="str">
         <v>P1</v>
@@ -749,13 +749,13 @@
         <v>Complété</v>
       </c>
       <c r="G12" t="str">
-        <v>REQ-006</v>
+        <v>REQ-007</v>
       </c>
       <c r="H12" t="str">
-        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
+        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
       </c>
       <c r="I12" t="str">
-        <v>Zod validation sur count (1-10), language (fr/en)</v>
+        <v>Gère encodages UTF-8, caractères spéciaux</v>
       </c>
     </row>
     <row r="13">
@@ -763,28 +763,28 @@
         <v>REQ-012</v>
       </c>
       <c r="B13" t="str">
-        <v>Structuration données</v>
+        <v>IA &amp; Génération</v>
       </c>
       <c r="C13" t="str">
-        <v>Modèle Document</v>
+        <v>Prompt dynamique contextuel</v>
       </c>
       <c r="D13" t="str">
-        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
+        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
       </c>
       <c r="E13" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F13" t="str">
         <v>Complété</v>
       </c>
       <c r="G13" t="str">
-        <v>REQ-002</v>
+        <v>REQ-007</v>
       </c>
       <c r="H13" t="str">
-        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
+        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
       </c>
       <c r="I13" t="str">
-        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
+        <v>Zod validation sur count (1-10), language (fr/en)</v>
       </c>
     </row>
     <row r="14">
@@ -795,10 +795,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C14" t="str">
-        <v>Modèle Interviewé</v>
+        <v>Modèle Document</v>
       </c>
       <c r="D14" t="str">
-        <v>Nom complet, rôle, lié à campaign</v>
+        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
       </c>
       <c r="E14" t="str">
         <v>P0</v>
@@ -810,10 +810,10 @@
         <v>REQ-002</v>
       </c>
       <c r="H14" t="str">
-        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
+        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
       </c>
       <c r="I14" t="str">
-        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
+        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
       </c>
     </row>
     <row r="15">
@@ -824,10 +824,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C15" t="str">
-        <v>Modèle Note d'entretien</v>
+        <v>Modèle Interviewé</v>
       </c>
       <c r="D15" t="str">
-        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
+        <v>Nom complet, rôle, lié à campaign</v>
       </c>
       <c r="E15" t="str">
         <v>P0</v>
@@ -836,13 +836,13 @@
         <v>Complété</v>
       </c>
       <c r="G15" t="str">
-        <v>REQ-004, REQ-013</v>
+        <v>REQ-002</v>
       </c>
       <c r="H15" t="str">
-        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
+        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
       </c>
       <c r="I15" t="str">
-        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
+        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
       </c>
     </row>
     <row r="16">
@@ -853,25 +853,25 @@
         <v>Structuration données</v>
       </c>
       <c r="C16" t="str">
-        <v>Matrice de conformité</v>
+        <v>Modèle Note d'entretien</v>
       </c>
       <c r="D16" t="str">
-        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
+        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
       </c>
       <c r="E16" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F16" t="str">
         <v>Complété</v>
       </c>
       <c r="G16" t="str">
-        <v>REQ-014</v>
+        <v>REQ-005, REQ-014</v>
       </c>
       <c r="H16" t="str">
-        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
+        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
       </c>
       <c r="I16" t="str">
-        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
+        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
       </c>
     </row>
     <row r="17">
@@ -882,10 +882,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C17" t="str">
-        <v>Configuration Métriques</v>
+        <v>Matrice de conformité</v>
       </c>
       <c r="D17" t="str">
-        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
+        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
       </c>
       <c r="E17" t="str">
         <v>P1</v>
@@ -894,13 +894,13 @@
         <v>Complété</v>
       </c>
       <c r="G17" t="str">
-        <v>REQ-002</v>
+        <v>REQ-015</v>
       </c>
       <c r="H17" t="str">
-        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
+        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
       </c>
       <c r="I17" t="str">
-        <v>Format texte (ex: '1-5') pour flexibilité</v>
+        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
       </c>
     </row>
     <row r="18">
@@ -908,13 +908,13 @@
         <v>REQ-017</v>
       </c>
       <c r="B18" t="str">
-        <v>Audit &amp; Traçabilité</v>
+        <v>Structuration données</v>
       </c>
       <c r="C18" t="str">
-        <v>Audit Log complet</v>
+        <v>Configuration Métriques</v>
       </c>
       <c r="D18" t="str">
-        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
+        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
       </c>
       <c r="E18" t="str">
         <v>P1</v>
@@ -923,13 +923,13 @@
         <v>Complété</v>
       </c>
       <c r="G18" t="str">
-        <v>REQ-002, REQ-029</v>
+        <v>REQ-002</v>
       </c>
       <c r="H18" t="str">
-        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
+        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
       </c>
       <c r="I18" t="str">
-        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
+        <v>Format texte (ex: '1-5') pour flexibilité</v>
       </c>
     </row>
     <row r="19">
@@ -940,10 +940,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C19" t="str">
-        <v>Filtrage logs par période</v>
+        <v>Audit Log complet</v>
       </c>
       <c r="D19" t="str">
-        <v>Vue 7j, 30j, tout (by date range filter)</v>
+        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
       </c>
       <c r="E19" t="str">
         <v>P1</v>
@@ -952,13 +952,13 @@
         <v>Complété</v>
       </c>
       <c r="G19" t="str">
-        <v>REQ-017</v>
+        <v>REQ-002, REQ-030</v>
       </c>
       <c r="H19" t="str">
-        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
+        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
       </c>
       <c r="I19" t="str">
-        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
+        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
       </c>
     </row>
     <row r="20">
@@ -969,10 +969,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C20" t="str">
-        <v>Filtrage logs par action</v>
+        <v>Filtrage logs par période</v>
       </c>
       <c r="D20" t="str">
-        <v>Filter sur type d'action (campaign.created, etc.)</v>
+        <v>Vue 7j, 30j, tout (by date range filter)</v>
       </c>
       <c r="E20" t="str">
         <v>P1</v>
@@ -981,13 +981,13 @@
         <v>Complété</v>
       </c>
       <c r="G20" t="str">
-        <v>REQ-017</v>
+        <v>REQ-018</v>
       </c>
       <c r="H20" t="str">
-        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
+        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
       </c>
       <c r="I20" t="str">
-        <v>Enum actions découvertes dynamiquement from logs</v>
+        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
       </c>
     </row>
     <row r="21">
@@ -995,28 +995,28 @@
         <v>REQ-020</v>
       </c>
       <c r="B21" t="str">
-        <v>Rapports &amp; Exports</v>
+        <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C21" t="str">
-        <v>Export DOCX</v>
+        <v>Filtrage logs par action</v>
       </c>
       <c r="D21" t="str">
-        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
+        <v>Filter sur type d'action (campaign.created, etc.)</v>
       </c>
       <c r="E21" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F21" t="str">
         <v>Complété</v>
       </c>
       <c r="G21" t="str">
-        <v>REQ-005, REQ-015</v>
+        <v>REQ-018</v>
       </c>
       <c r="H21" t="str">
-        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
+        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
       </c>
       <c r="I21" t="str">
-        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
+        <v>Enum actions découvertes dynamiquement from logs</v>
       </c>
     </row>
     <row r="22">
@@ -1027,10 +1027,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C22" t="str">
-        <v>Export CSV</v>
+        <v>Export DOCX</v>
       </c>
       <c r="D22" t="str">
-        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
+        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
       </c>
       <c r="E22" t="str">
         <v>P2</v>
@@ -1039,13 +1039,13 @@
         <v>Complété</v>
       </c>
       <c r="G22" t="str">
-        <v>REQ-015, REQ-017</v>
+        <v>REQ-006, REQ-016</v>
       </c>
       <c r="H22" t="str">
-        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
+        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
       </c>
       <c r="I22" t="str">
-        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
+        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
       </c>
     </row>
     <row r="23">
@@ -1056,10 +1056,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C23" t="str">
-        <v>Gestion des rapports</v>
+        <v>Export CSV</v>
       </c>
       <c r="D23" t="str">
-        <v>Stocker rapports générés avec titre, date gen, version</v>
+        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
       </c>
       <c r="E23" t="str">
         <v>P2</v>
@@ -1068,13 +1068,13 @@
         <v>Complété</v>
       </c>
       <c r="G23" t="str">
-        <v>REQ-020, REQ-021</v>
+        <v>REQ-016, REQ-018</v>
       </c>
       <c r="H23" t="str">
-        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
+        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
       </c>
       <c r="I23" t="str">
-        <v>Récupérable dans UI, archivé pour traçabilité</v>
+        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
       </c>
     </row>
     <row r="24">
@@ -1082,28 +1082,28 @@
         <v>REQ-023</v>
       </c>
       <c r="B24" t="str">
-        <v>Dashboard &amp; Visualisation</v>
+        <v>Rapports &amp; Exports</v>
       </c>
       <c r="C24" t="str">
-        <v>KPIs essentiels</v>
+        <v>Gestion des rapports</v>
       </c>
       <c r="D24" t="str">
-        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
+        <v>Stocker rapports générés avec titre, date gen, version</v>
       </c>
       <c r="E24" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F24" t="str">
         <v>Complété</v>
       </c>
       <c r="G24" t="str">
-        <v>REQ-012, REQ-013, REQ-014</v>
+        <v>REQ-021, REQ-022</v>
       </c>
       <c r="H24" t="str">
-        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
+        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
       </c>
       <c r="I24" t="str">
-        <v>Affiché en gros chiffres zone haute dashboard</v>
+        <v>Récupérable dans UI, archivé pour traçabilité</v>
       </c>
     </row>
     <row r="25">
@@ -1114,25 +1114,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C25" t="str">
-        <v>Matrice de conformité interactive</v>
+        <v>KPIs essentiels</v>
       </c>
       <c r="D25" t="str">
-        <v>Tableau avec % conformité par criterion, tri/filtre</v>
+        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
       </c>
       <c r="E25" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F25" t="str">
         <v>Complété</v>
       </c>
       <c r="G25" t="str">
-        <v>REQ-015</v>
+        <v>REQ-013, REQ-014, REQ-015</v>
       </c>
       <c r="H25" t="str">
-        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
+        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
       </c>
       <c r="I25" t="str">
-        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
+        <v>Affiché en gros chiffres zone haute dashboard</v>
       </c>
     </row>
     <row r="26">
@@ -1143,25 +1143,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C26" t="str">
-        <v>Graphiques optionnels (futur)</v>
+        <v>Matrice de conformité interactive</v>
       </c>
       <c r="D26" t="str">
-        <v>Tendances audit timeline, pie charts conformity domains</v>
+        <v>Tableau avec % conformité par criterion, tri/filtre</v>
       </c>
       <c r="E26" t="str">
-        <v>P3</v>
+        <v>P2</v>
       </c>
       <c r="F26" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G26" t="str">
-        <v>REQ-023</v>
+        <v>REQ-016</v>
       </c>
       <c r="H26" t="str">
-        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
+        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
       </c>
       <c r="I26" t="str">
-        <v>MVP n'a pas graphiques, architecture prête pour.</v>
+        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
       </c>
     </row>
     <row r="27">
@@ -1169,28 +1169,28 @@
         <v>REQ-026</v>
       </c>
       <c r="B27" t="str">
-        <v>Configuration &amp; Flexibilité</v>
+        <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C27" t="str">
-        <v>Support multilingue</v>
+        <v>Graphiques optionnels (futur)</v>
       </c>
       <c r="D27" t="str">
-        <v>FR et EN, sélection par campaign</v>
+        <v>Tendances audit timeline, pie charts conformity domains</v>
       </c>
       <c r="E27" t="str">
-        <v>P1</v>
+        <v>P3</v>
       </c>
       <c r="F27" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G27" t="str">
-        <v>REQ-029</v>
+        <v>REQ-024</v>
       </c>
       <c r="H27" t="str">
-        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
+        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
       </c>
       <c r="I27" t="str">
-        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
+        <v>MVP n'a pas graphiques, architecture prête pour.</v>
       </c>
     </row>
     <row r="28">
@@ -1201,10 +1201,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C28" t="str">
-        <v>Modèle Ollama configurable</v>
+        <v>Support multilingue</v>
       </c>
       <c r="D28" t="str">
-        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
+        <v>FR et EN, sélection par campaign</v>
       </c>
       <c r="E28" t="str">
         <v>P1</v>
@@ -1213,13 +1213,13 @@
         <v>Complété</v>
       </c>
       <c r="G28" t="str">
-        <v>REQ-008</v>
+        <v>REQ-030</v>
       </c>
       <c r="H28" t="str">
-        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
+        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
       </c>
       <c r="I28" t="str">
-        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
+        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
       </c>
     </row>
     <row r="29">
@@ -1230,10 +1230,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C29" t="str">
-        <v>OpenAI optionnel</v>
+        <v>Modèle Ollama configurable</v>
       </c>
       <c r="D29" t="str">
-        <v>API key via .env, fallback auto Ollama si absent</v>
+        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
       </c>
       <c r="E29" t="str">
         <v>P1</v>
@@ -1242,13 +1242,13 @@
         <v>Complété</v>
       </c>
       <c r="G29" t="str">
-        <v>REQ-029</v>
+        <v>REQ-009</v>
       </c>
       <c r="H29" t="str">
-        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
+        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
       </c>
       <c r="I29" t="str">
-        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
+        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
       </c>
     </row>
     <row r="30">
@@ -1259,25 +1259,25 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C30" t="str">
-        <v>Thèmes personnalisés</v>
+        <v>OpenAI optionnel</v>
       </c>
       <c r="D30" t="str">
-        <v>Texte libre pour documents et questions</v>
+        <v>API key via .env, fallback auto Ollama si absent</v>
       </c>
       <c r="E30" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F30" t="str">
         <v>Complété</v>
       </c>
       <c r="G30" t="str">
-        <v>-</v>
+        <v>REQ-030</v>
       </c>
       <c r="H30" t="str">
-        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
+        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
       </c>
       <c r="I30" t="str">
-        <v>Permet flexibilité sur domaines audit custom</v>
+        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
       </c>
     </row>
     <row r="31">
@@ -1285,16 +1285,16 @@
         <v>REQ-030</v>
       </c>
       <c r="B31" t="str">
-        <v>Infrastructure &amp; Déploiement</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C31" t="str">
-        <v>Offline-first capability</v>
+        <v>Thèmes personnalisés</v>
       </c>
       <c r="D31" t="str">
-        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
+        <v>Texte libre pour documents et questions</v>
       </c>
       <c r="E31" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F31" t="str">
         <v>Complété</v>
@@ -1303,10 +1303,10 @@
         <v>-</v>
       </c>
       <c r="H31" t="str">
-        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
+        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
       </c>
       <c r="I31" t="str">
-        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
+        <v>Permet flexibilité sur domaines audit custom</v>
       </c>
     </row>
     <row r="32">
@@ -1317,25 +1317,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C32" t="str">
-        <v>Automation PowerShell</v>
+        <v>Offline-first capability</v>
       </c>
       <c r="D32" t="str">
-        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
+        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
       </c>
       <c r="E32" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F32" t="str">
         <v>Complété</v>
       </c>
       <c r="G32" t="str">
-        <v>REQ-027, REQ-030</v>
+        <v>-</v>
       </c>
       <c r="H32" t="str">
-        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
+        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
       </c>
       <c r="I32" t="str">
-        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
+        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
       </c>
     </row>
     <row r="33">
@@ -1346,25 +1346,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C33" t="str">
-        <v>Versionning Git &amp; GitHub</v>
+        <v>Automation PowerShell</v>
       </c>
       <c r="D33" t="str">
-        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
+        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
       </c>
       <c r="E33" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F33" t="str">
         <v>Complété</v>
       </c>
       <c r="G33" t="str">
-        <v>REQ-006, REQ-030</v>
+        <v>REQ-028, REQ-031</v>
       </c>
       <c r="H33" t="str">
-        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
+        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
       </c>
       <c r="I33" t="str">
-        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
+        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
       </c>
     </row>
     <row r="34">
@@ -1375,25 +1375,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C34" t="str">
-        <v>API REST Fastify</v>
+        <v>Versionning Git &amp; GitHub</v>
       </c>
       <c r="D34" t="str">
-        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
+        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
       </c>
       <c r="E34" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F34" t="str">
         <v>Complété</v>
       </c>
       <c r="G34" t="str">
-        <v>REQ-012, REQ-030</v>
+        <v>REQ-007, REQ-031</v>
       </c>
       <c r="H34" t="str">
-        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
+        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
       </c>
       <c r="I34" t="str">
-        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
+        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
       </c>
     </row>
     <row r="35">
@@ -1401,28 +1401,28 @@
         <v>REQ-034</v>
       </c>
       <c r="B35" t="str">
-        <v>UI/UX</v>
+        <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C35" t="str">
-        <v>UI React + TypeScript + Vite</v>
+        <v>API REST Fastify</v>
       </c>
       <c r="D35" t="str">
-        <v>Bundling optimisé, HMR dev mode</v>
+        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
       </c>
       <c r="E35" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F35" t="str">
         <v>Complété</v>
       </c>
       <c r="G35" t="str">
-        <v>REQ-016, REQ-030</v>
+        <v>REQ-013, REQ-031</v>
       </c>
       <c r="H35" t="str">
-        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
+        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
       </c>
       <c r="I35" t="str">
-        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
+        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
       </c>
     </row>
     <row r="36">
@@ -1433,10 +1433,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C36" t="str">
-        <v>Configuration IA section</v>
+        <v>UI React + TypeScript + Vite</v>
       </c>
       <c r="D36" t="str">
-        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
+        <v>Bundling optimisé, HMR dev mode</v>
       </c>
       <c r="E36" t="str">
         <v>P1</v>
@@ -1445,13 +1445,13 @@
         <v>Complété</v>
       </c>
       <c r="G36" t="str">
-        <v>REQ-023, REQ-030</v>
+        <v>REQ-017, REQ-031</v>
       </c>
       <c r="H36" t="str">
-        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
+        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
       </c>
       <c r="I36" t="str">
-        <v>UX: clair et accessible, pas scroll nécessaire</v>
+        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
       </c>
     </row>
     <row r="37">
@@ -1462,10 +1462,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C37" t="str">
-        <v>Génération questions section</v>
+        <v>Configuration IA section</v>
       </c>
       <c r="D37" t="str">
-        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
+        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
       </c>
       <c r="E37" t="str">
         <v>P1</v>
@@ -1474,13 +1474,13 @@
         <v>Complété</v>
       </c>
       <c r="G37" t="str">
-        <v>REQ-013, REQ-014, REQ-030</v>
+        <v>REQ-024, REQ-031</v>
       </c>
       <c r="H37" t="str">
-        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
+        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
       </c>
       <c r="I37" t="str">
-        <v>État uploadingReferential: loading indicator, disabled submit</v>
+        <v>UX: clair et accessible, pas scroll nécessaire</v>
       </c>
     </row>
     <row r="38">
@@ -1491,10 +1491,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C38" t="str">
-        <v>Référentiel documentaire section</v>
+        <v>Génération questions section</v>
       </c>
       <c r="D38" t="str">
-        <v>Ajouter document avec métas, liste affichée</v>
+        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
       </c>
       <c r="E38" t="str">
         <v>P1</v>
@@ -1503,13 +1503,13 @@
         <v>Complété</v>
       </c>
       <c r="G38" t="str">
-        <v>REQ-018, REQ-019, REQ-030</v>
+        <v>REQ-014, REQ-015, REQ-031</v>
       </c>
       <c r="H38" t="str">
-        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
+        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
       </c>
       <c r="I38" t="str">
-        <v>Erreurs affichées, success feedback, état documentS refresh</v>
+        <v>État uploadingReferential: loading indicator, disabled submit</v>
       </c>
     </row>
     <row r="39">
@@ -1520,10 +1520,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C39" t="str">
-        <v>Échelles métriques config</v>
+        <v>Référentiel documentaire section</v>
       </c>
       <c r="D39" t="str">
-        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
+        <v>Ajouter document avec métas, liste affichée</v>
       </c>
       <c r="E39" t="str">
         <v>P1</v>
@@ -1532,13 +1532,13 @@
         <v>Complété</v>
       </c>
       <c r="G39" t="str">
-        <v>REQ-020, REQ-021, REQ-030</v>
+        <v>REQ-019, REQ-020, REQ-031</v>
       </c>
       <c r="H39" t="str">
-        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
+        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
       </c>
       <c r="I39" t="str">
-        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
+        <v>Erreurs affichées, success feedback, état documentS refresh</v>
       </c>
     </row>
     <row r="40">
@@ -1549,10 +1549,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C40" t="str">
-        <v>Dashboard avec KPIs</v>
+        <v>Échelles métriques config</v>
       </c>
       <c r="D40" t="str">
-        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
+        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
       </c>
       <c r="E40" t="str">
         <v>P1</v>
@@ -1561,13 +1561,13 @@
         <v>Complété</v>
       </c>
       <c r="G40" t="str">
-        <v>-</v>
+        <v>REQ-021, REQ-022, REQ-031</v>
       </c>
       <c r="H40" t="str">
-        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
+        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
       </c>
       <c r="I40" t="str">
-        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
+        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
       </c>
     </row>
     <row r="41">
@@ -1578,10 +1578,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C41" t="str">
-        <v>Gestion entretiens</v>
+        <v>Dashboard avec KPIs</v>
       </c>
       <c r="D41" t="str">
-        <v>Interviewés, notes questions, scoring intégré</v>
+        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
       </c>
       <c r="E41" t="str">
         <v>P1</v>
@@ -1593,10 +1593,10 @@
         <v>-</v>
       </c>
       <c r="H41" t="str">
-        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
+        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
       </c>
       <c r="I41" t="str">
-        <v>Chaque note liée criterion + interviewee + score optionnel</v>
+        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
       </c>
     </row>
     <row r="42">
@@ -1607,10 +1607,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C42" t="str">
-        <v>Audit log viewer</v>
+        <v>Gestion entretiens</v>
       </c>
       <c r="D42" t="str">
-        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
+        <v>Interviewés, notes questions, scoring intégré</v>
       </c>
       <c r="E42" t="str">
         <v>P1</v>
@@ -1619,13 +1619,13 @@
         <v>Complété</v>
       </c>
       <c r="G42" t="str">
-        <v>REQ-040</v>
+        <v>-</v>
       </c>
       <c r="H42" t="str">
-        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
+        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
       </c>
       <c r="I42" t="str">
-        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
+        <v>Chaque note liée criterion + interviewee + score optionnel</v>
       </c>
     </row>
     <row r="43">
@@ -1636,25 +1636,25 @@
         <v>UI/UX</v>
       </c>
       <c r="C43" t="str">
-        <v>Export buttons</v>
+        <v>Audit log viewer</v>
       </c>
       <c r="D43" t="str">
-        <v>Boutons DOCX et CSV téléchargement</v>
+        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
       </c>
       <c r="E43" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F43" t="str">
         <v>Complété</v>
       </c>
       <c r="G43" t="str">
-        <v>-</v>
+        <v>REQ-041</v>
       </c>
       <c r="H43" t="str">
-        <v>POST /export-report et /export-csv. browser Blob download.</v>
+        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
       </c>
       <c r="I43" t="str">
-        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
       </c>
     </row>
     <row r="44">
@@ -1662,13 +1662,13 @@
         <v>REQ-043</v>
       </c>
       <c r="B44" t="str">
-        <v>Persévérance &amp; Facilité</v>
+        <v>UI/UX</v>
       </c>
       <c r="C44" t="str">
-        <v>Documentation complète</v>
+        <v>Export buttons</v>
       </c>
       <c r="D44" t="str">
-        <v>Setup guides, quickstart, git manual, examples références</v>
+        <v>Boutons DOCX et CSV téléchargement</v>
       </c>
       <c r="E44" t="str">
         <v>P2</v>
@@ -1680,13 +1680,13 @@
         <v>-</v>
       </c>
       <c r="H44" t="str">
-        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
+        <v>POST /export-report et /export-csv. browser Blob download.</v>
       </c>
       <c r="I44" t="str">
-        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
-      </c>
-    </row>
-    <row r="45" xml:space="preserve">
+        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="str">
         <v>REQ-044</v>
       </c>
@@ -1694,10 +1694,10 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C45" t="str">
-        <v>One-command installation</v>
+        <v>Documentation complète</v>
       </c>
       <c r="D45" t="str">
-        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+        <v>Setup guides, quickstart, git manual, examples références</v>
       </c>
       <c r="E45" t="str">
         <v>P2</v>
@@ -1708,12 +1708,11 @@
       <c r="G45" t="str">
         <v>-</v>
       </c>
-      <c r="H45" t="str" xml:space="preserve">
-        <v xml:space="preserve">.
- install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      <c r="H45" t="str">
+        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
       </c>
       <c r="I45" t="str">
-        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
       </c>
     </row>
     <row r="46" xml:space="preserve">
@@ -1724,41 +1723,42 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C46" t="str">
+        <v>One-command installation</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+      </c>
+      <c r="E46" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G46" t="str">
+        <v>-</v>
+      </c>
+      <c r="H46" t="str" xml:space="preserve">
+        <v xml:space="preserve">.
+ install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      </c>
+      <c r="I46" t="str">
+        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
+        <v>REQ-046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C47" t="str">
         <v>One-command launch</v>
       </c>
-      <c r="D46" t="str" xml:space="preserve">
+      <c r="D47" t="str" xml:space="preserve">
         <v xml:space="preserve">npm run dev ou .
 start-rubis.ps1 pour lancer tout</v>
       </c>
-      <c r="E46" t="str">
-        <v>P2</v>
-      </c>
-      <c r="F46" t="str">
-        <v>Complété</v>
-      </c>
-      <c r="G46" t="str">
-        <v>-</v>
-      </c>
-      <c r="H46" t="str">
-        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
-      </c>
-      <c r="I46" t="str">
-        <v>Détection auto erreurs, log output lisible</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>REQ-046</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Persévérance &amp; Facilité</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Clear error messages</v>
-      </c>
-      <c r="D47" t="str">
-        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
-      </c>
       <c r="E47" t="str">
         <v>P2</v>
       </c>
@@ -1769,10 +1769,10 @@
         <v>-</v>
       </c>
       <c r="H47" t="str">
-        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
       </c>
       <c r="I47" t="str">
-        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+        <v>Détection auto erreurs, log output lisible</v>
       </c>
     </row>
     <row r="48">
@@ -1783,30 +1783,59 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C48" t="str">
-        <v>Roadmap versioning</v>
+        <v>Clear error messages</v>
       </c>
       <c r="D48" t="str">
-        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
       </c>
       <c r="E48" t="str">
         <v>P2</v>
       </c>
       <c r="F48" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G48" t="str">
         <v>-</v>
       </c>
       <c r="H48" t="str">
+        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>REQ-048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Roadmap versioning</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+      </c>
+      <c r="E49" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G49" t="str">
+        <v>-</v>
+      </c>
+      <c r="H49" t="str">
         <v>Créer ROADMAP.xlsx avec specs, priorités, statuts, directives implémentation.</v>
       </c>
-      <c r="I48" t="str">
+      <c r="I49" t="str">
         <v>À committé dans git, mis à jour post-MVP pour v2 features</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I49"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -546,7 +546,7 @@
         <v>Planifié</v>
       </c>
       <c r="G5" t="str">
-        <v>REQ-003, REQ-030</v>
+        <v>REQ-003, REQ-031</v>
       </c>
       <c r="H5" t="str">
         <v>Section admin protégée. CRUD référentiels: POST/PUT/DELETE /admin/referentials. Stockage db.data.referentials avec {id, name, category, description, isActive}. UI table éditable avec formulaire modal.</v>
@@ -589,28 +589,28 @@
         <v>REQ-006</v>
       </c>
       <c r="B7" t="str">
-        <v>Cœur métier</v>
+        <v>IA &amp; Génération</v>
       </c>
       <c r="C7" t="str">
-        <v>Génération de questions</v>
+        <v>Extraction automatique des critères depuis référentiel</v>
       </c>
       <c r="D7" t="str">
-        <v>Questions avec text, guidance, theme générées dynamiquement</v>
+        <v>IA parse le document référentiel fourni (PDF/Excel) et extrait automatiquement tous les critères/exigences avec code, titre, description</v>
       </c>
       <c r="E7" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F7" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G7" t="str">
-        <v>REQ-005</v>
+        <v>REQ-005, REQ-003, REQ-031</v>
       </c>
       <c r="H7" t="str">
-        <v>POST /question, GET /questions. Schéma Zod pour validation stricte.</v>
+        <v>POST /extract-criteria-from-referential. Multipart upload. Parser identifie structure (ex: ISO27001 A.5.1, A.5.2...). LLM extrait: {code, title, theme, description}. Batch insert criteria. UI: upload doc + bouton 'Extraire critères', preview avant validation.</v>
       </c>
       <c r="I7" t="str">
-        <v>Peut être depuis template ou IA (voir section IA)</v>
+        <v>Exemple: ISO27001 → extraire A.5.1 à A.18.2 (93 contrôles). PASSI → extraire exigences numérotées. Gain temps énorme vs saisie manuelle. Validation humaine optionnelle avant import.</v>
       </c>
     </row>
     <row r="8">
@@ -618,16 +618,16 @@
         <v>REQ-007</v>
       </c>
       <c r="B8" t="str">
-        <v>IA &amp; Génération</v>
+        <v>Cœur métier</v>
       </c>
       <c r="C8" t="str">
-        <v>Génération depuis référentiel</v>
+        <v>Génération de questions</v>
       </c>
       <c r="D8" t="str">
-        <v>Parser PDF ou Excel, extraire texte, passer à IA pour générer questions</v>
+        <v>Questions avec text, guidance, theme générées dynamiquement</v>
       </c>
       <c r="E8" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F8" t="str">
         <v>Complété</v>
@@ -636,10 +636,10 @@
         <v>REQ-005</v>
       </c>
       <c r="H8" t="str">
-        <v>POST /generate-questions-from-referential. Multipart form. parseReferentialFile() en services/referentialParser.ts</v>
+        <v>POST /question, GET /questions. Schéma Zod pour validation stricte.</v>
       </c>
       <c r="I8" t="str">
-        <v>Limite 50KB texte extrait pour perf API</v>
+        <v>Peut être depuis template ou IA (voir section IA)</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C9" t="str">
-        <v>Dual AI strategy - OpenAI</v>
+        <v>Génération depuis référentiel</v>
       </c>
       <c r="D9" t="str">
-        <v>Intégration GPT-4o pour génération rapide et haute qualité</v>
+        <v>Parser PDF ou Excel, extraire texte, passer à IA pour générer questions</v>
       </c>
       <c r="E9" t="str">
         <v>P1</v>
@@ -662,13 +662,13 @@
         <v>Complété</v>
       </c>
       <c r="G9" t="str">
-        <v>REQ-030</v>
+        <v>REQ-006</v>
       </c>
       <c r="H9" t="str">
-        <v>generateQuestionsFromOpenAI() dans openai.ts. OpenAI client avec apiKey depuis .env</v>
+        <v>POST /generate-questions-from-referential. Multipart form. parseReferentialFile() en services/referentialParser.ts</v>
       </c>
       <c r="I9" t="str">
-        <v>Fallback si OPENAI_API_KEY absent</v>
+        <v>Limite 50KB texte extrait pour perf API</v>
       </c>
     </row>
     <row r="10">
@@ -679,10 +679,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C10" t="str">
-        <v>Dual AI strategy - Ollama local</v>
+        <v>Dual AI strategy - OpenAI</v>
       </c>
       <c r="D10" t="str">
-        <v>Ollama + Mistral/Gemma3 pour mode offline-first sur éliteBook</v>
+        <v>Intégration GPT-4o pour génération rapide et haute qualité</v>
       </c>
       <c r="E10" t="str">
         <v>P1</v>
@@ -691,13 +691,13 @@
         <v>Complété</v>
       </c>
       <c r="G10" t="str">
-        <v>REQ-030</v>
+        <v>REQ-031</v>
       </c>
       <c r="H10" t="str">
-        <v>generateQuestionsFromOllama() fetch to localhost:11434/api/generate. checkOllamaAvailable() avec timeout 2s</v>
+        <v>generateQuestionsFromOpenAI() dans openai.ts. OpenAI client avec apiKey depuis .env</v>
       </c>
       <c r="I10" t="str">
-        <v>Auto-détection Ollama, fallback depuis OpenAI si non dispo</v>
+        <v>Fallback si OPENAI_API_KEY absent</v>
       </c>
     </row>
     <row r="11">
@@ -708,10 +708,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C11" t="str">
-        <v>Model switching UI</v>
+        <v>Dual AI strategy - Ollama local</v>
       </c>
       <c r="D11" t="str">
-        <v>Permuter entre mistral et gemma3:4b directement dans l'appli</v>
+        <v>Ollama + Mistral/Gemma3 pour mode offline-first sur éliteBook</v>
       </c>
       <c r="E11" t="str">
         <v>P1</v>
@@ -720,13 +720,13 @@
         <v>Complété</v>
       </c>
       <c r="G11" t="str">
-        <v>REQ-008, REQ-009</v>
+        <v>REQ-031</v>
       </c>
       <c r="H11" t="str">
-        <v>GET/POST /config endpoints. État currentOllamaModel dans server.ts. Boutons UI dans App.tsx 'Configuration IA'</v>
+        <v>generateQuestionsFromOllama() fetch to localhost:11434/api/generate. checkOllamaAvailable() avec timeout 2s</v>
       </c>
       <c r="I11" t="str">
-        <v>Changement runtime, pas besoin restart API</v>
+        <v>Auto-détection Ollama, fallback depuis OpenAI si non dispo</v>
       </c>
     </row>
     <row r="12">
@@ -737,10 +737,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C12" t="str">
-        <v>Parsing référentiel multi-format</v>
+        <v>Model switching UI</v>
       </c>
       <c r="D12" t="str">
-        <v>Support PDF et Excel avec extraction de texte</v>
+        <v>Permuter entre mistral et gemma3:4b directement dans l'appli</v>
       </c>
       <c r="E12" t="str">
         <v>P1</v>
@@ -749,13 +749,13 @@
         <v>Complété</v>
       </c>
       <c r="G12" t="str">
-        <v>REQ-007</v>
+        <v>REQ-009, REQ-010</v>
       </c>
       <c r="H12" t="str">
-        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
+        <v>GET/POST /config endpoints. État currentOllamaModel dans server.ts. Boutons UI dans App.tsx 'Configuration IA'</v>
       </c>
       <c r="I12" t="str">
-        <v>Gère encodages UTF-8, caractères spéciaux</v>
+        <v>Changement runtime, pas besoin restart API</v>
       </c>
     </row>
     <row r="13">
@@ -766,10 +766,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C13" t="str">
-        <v>Prompt dynamique contextuel</v>
+        <v>Parsing référentiel multi-format</v>
       </c>
       <c r="D13" t="str">
-        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
+        <v>Support PDF et Excel avec extraction de texte</v>
       </c>
       <c r="E13" t="str">
         <v>P1</v>
@@ -778,13 +778,13 @@
         <v>Complété</v>
       </c>
       <c r="G13" t="str">
-        <v>REQ-007</v>
+        <v>REQ-008</v>
       </c>
       <c r="H13" t="str">
-        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
+        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
       </c>
       <c r="I13" t="str">
-        <v>Zod validation sur count (1-10), language (fr/en)</v>
+        <v>Gère encodages UTF-8, caractères spéciaux</v>
       </c>
     </row>
     <row r="14">
@@ -792,28 +792,28 @@
         <v>REQ-013</v>
       </c>
       <c r="B14" t="str">
-        <v>Structuration données</v>
+        <v>IA &amp; Génération</v>
       </c>
       <c r="C14" t="str">
-        <v>Modèle Document</v>
+        <v>Prompt dynamique contextuel</v>
       </c>
       <c r="D14" t="str">
-        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
+        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
       </c>
       <c r="E14" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F14" t="str">
         <v>Complété</v>
       </c>
       <c r="G14" t="str">
-        <v>REQ-002</v>
+        <v>REQ-008</v>
       </c>
       <c r="H14" t="str">
-        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
+        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
       </c>
       <c r="I14" t="str">
-        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
+        <v>Zod validation sur count (1-10), language (fr/en)</v>
       </c>
     </row>
     <row r="15">
@@ -824,10 +824,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C15" t="str">
-        <v>Modèle Interviewé</v>
+        <v>Modèle Document</v>
       </c>
       <c r="D15" t="str">
-        <v>Nom complet, rôle, lié à campaign</v>
+        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
       </c>
       <c r="E15" t="str">
         <v>P0</v>
@@ -839,10 +839,10 @@
         <v>REQ-002</v>
       </c>
       <c r="H15" t="str">
-        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
+        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
       </c>
       <c r="I15" t="str">
-        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
+        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
       </c>
     </row>
     <row r="16">
@@ -853,10 +853,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C16" t="str">
-        <v>Modèle Note d'entretien</v>
+        <v>Modèle Interviewé</v>
       </c>
       <c r="D16" t="str">
-        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
+        <v>Nom complet, rôle, lié à campaign</v>
       </c>
       <c r="E16" t="str">
         <v>P0</v>
@@ -865,13 +865,13 @@
         <v>Complété</v>
       </c>
       <c r="G16" t="str">
-        <v>REQ-005, REQ-014</v>
+        <v>REQ-002</v>
       </c>
       <c r="H16" t="str">
-        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
+        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
       </c>
       <c r="I16" t="str">
-        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
+        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
       </c>
     </row>
     <row r="17">
@@ -882,25 +882,25 @@
         <v>Structuration données</v>
       </c>
       <c r="C17" t="str">
-        <v>Matrice de conformité</v>
+        <v>Modèle Note d'entretien</v>
       </c>
       <c r="D17" t="str">
-        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
+        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
       </c>
       <c r="E17" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F17" t="str">
         <v>Complété</v>
       </c>
       <c r="G17" t="str">
-        <v>REQ-015</v>
+        <v>REQ-005, REQ-015</v>
       </c>
       <c r="H17" t="str">
-        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
+        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
       </c>
       <c r="I17" t="str">
-        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
+        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
       </c>
     </row>
     <row r="18">
@@ -911,10 +911,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C18" t="str">
-        <v>Configuration Métriques</v>
+        <v>Matrice de conformité</v>
       </c>
       <c r="D18" t="str">
-        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
+        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
       </c>
       <c r="E18" t="str">
         <v>P1</v>
@@ -923,13 +923,13 @@
         <v>Complété</v>
       </c>
       <c r="G18" t="str">
-        <v>REQ-002</v>
+        <v>REQ-016</v>
       </c>
       <c r="H18" t="str">
-        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
+        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
       </c>
       <c r="I18" t="str">
-        <v>Format texte (ex: '1-5') pour flexibilité</v>
+        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
       </c>
     </row>
     <row r="19">
@@ -937,13 +937,13 @@
         <v>REQ-018</v>
       </c>
       <c r="B19" t="str">
-        <v>Audit &amp; Traçabilité</v>
+        <v>Structuration données</v>
       </c>
       <c r="C19" t="str">
-        <v>Audit Log complet</v>
+        <v>Configuration Métriques</v>
       </c>
       <c r="D19" t="str">
-        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
+        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
       </c>
       <c r="E19" t="str">
         <v>P1</v>
@@ -952,13 +952,13 @@
         <v>Complété</v>
       </c>
       <c r="G19" t="str">
-        <v>REQ-002, REQ-030</v>
+        <v>REQ-002</v>
       </c>
       <c r="H19" t="str">
-        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
+        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
       </c>
       <c r="I19" t="str">
-        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
+        <v>Format texte (ex: '1-5') pour flexibilité</v>
       </c>
     </row>
     <row r="20">
@@ -969,10 +969,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C20" t="str">
-        <v>Filtrage logs par période</v>
+        <v>Audit Log complet</v>
       </c>
       <c r="D20" t="str">
-        <v>Vue 7j, 30j, tout (by date range filter)</v>
+        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
       </c>
       <c r="E20" t="str">
         <v>P1</v>
@@ -981,13 +981,13 @@
         <v>Complété</v>
       </c>
       <c r="G20" t="str">
-        <v>REQ-018</v>
+        <v>REQ-002, REQ-031</v>
       </c>
       <c r="H20" t="str">
-        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
+        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
       </c>
       <c r="I20" t="str">
-        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
+        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
       </c>
     </row>
     <row r="21">
@@ -998,10 +998,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C21" t="str">
-        <v>Filtrage logs par action</v>
+        <v>Filtrage logs par période</v>
       </c>
       <c r="D21" t="str">
-        <v>Filter sur type d'action (campaign.created, etc.)</v>
+        <v>Vue 7j, 30j, tout (by date range filter)</v>
       </c>
       <c r="E21" t="str">
         <v>P1</v>
@@ -1010,13 +1010,13 @@
         <v>Complété</v>
       </c>
       <c r="G21" t="str">
-        <v>REQ-018</v>
+        <v>REQ-019</v>
       </c>
       <c r="H21" t="str">
-        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
+        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
       </c>
       <c r="I21" t="str">
-        <v>Enum actions découvertes dynamiquement from logs</v>
+        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
       </c>
     </row>
     <row r="22">
@@ -1024,28 +1024,28 @@
         <v>REQ-021</v>
       </c>
       <c r="B22" t="str">
-        <v>Rapports &amp; Exports</v>
+        <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C22" t="str">
-        <v>Export DOCX</v>
+        <v>Filtrage logs par action</v>
       </c>
       <c r="D22" t="str">
-        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
+        <v>Filter sur type d'action (campaign.created, etc.)</v>
       </c>
       <c r="E22" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F22" t="str">
         <v>Complété</v>
       </c>
       <c r="G22" t="str">
-        <v>REQ-006, REQ-016</v>
+        <v>REQ-019</v>
       </c>
       <c r="H22" t="str">
-        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
+        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
       </c>
       <c r="I22" t="str">
-        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
+        <v>Enum actions découvertes dynamiquement from logs</v>
       </c>
     </row>
     <row r="23">
@@ -1056,10 +1056,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C23" t="str">
-        <v>Export CSV</v>
+        <v>Export DOCX</v>
       </c>
       <c r="D23" t="str">
-        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
+        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
       </c>
       <c r="E23" t="str">
         <v>P2</v>
@@ -1068,13 +1068,13 @@
         <v>Complété</v>
       </c>
       <c r="G23" t="str">
-        <v>REQ-016, REQ-018</v>
+        <v>REQ-007, REQ-017</v>
       </c>
       <c r="H23" t="str">
-        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
+        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
       </c>
       <c r="I23" t="str">
-        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
+        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
       </c>
     </row>
     <row r="24">
@@ -1085,10 +1085,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C24" t="str">
-        <v>Gestion des rapports</v>
+        <v>Export CSV</v>
       </c>
       <c r="D24" t="str">
-        <v>Stocker rapports générés avec titre, date gen, version</v>
+        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
       </c>
       <c r="E24" t="str">
         <v>P2</v>
@@ -1097,13 +1097,13 @@
         <v>Complété</v>
       </c>
       <c r="G24" t="str">
-        <v>REQ-021, REQ-022</v>
+        <v>REQ-017, REQ-019</v>
       </c>
       <c r="H24" t="str">
-        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
+        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
       </c>
       <c r="I24" t="str">
-        <v>Récupérable dans UI, archivé pour traçabilité</v>
+        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
       </c>
     </row>
     <row r="25">
@@ -1111,28 +1111,28 @@
         <v>REQ-024</v>
       </c>
       <c r="B25" t="str">
-        <v>Dashboard &amp; Visualisation</v>
+        <v>Rapports &amp; Exports</v>
       </c>
       <c r="C25" t="str">
-        <v>KPIs essentiels</v>
+        <v>Gestion des rapports</v>
       </c>
       <c r="D25" t="str">
-        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
+        <v>Stocker rapports générés avec titre, date gen, version</v>
       </c>
       <c r="E25" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F25" t="str">
         <v>Complété</v>
       </c>
       <c r="G25" t="str">
-        <v>REQ-013, REQ-014, REQ-015</v>
+        <v>REQ-022, REQ-023</v>
       </c>
       <c r="H25" t="str">
-        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
+        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
       </c>
       <c r="I25" t="str">
-        <v>Affiché en gros chiffres zone haute dashboard</v>
+        <v>Récupérable dans UI, archivé pour traçabilité</v>
       </c>
     </row>
     <row r="26">
@@ -1143,25 +1143,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C26" t="str">
-        <v>Matrice de conformité interactive</v>
+        <v>KPIs essentiels</v>
       </c>
       <c r="D26" t="str">
-        <v>Tableau avec % conformité par criterion, tri/filtre</v>
+        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
       </c>
       <c r="E26" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F26" t="str">
         <v>Complété</v>
       </c>
       <c r="G26" t="str">
-        <v>REQ-016</v>
+        <v>REQ-014, REQ-015, REQ-016</v>
       </c>
       <c r="H26" t="str">
-        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
+        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
       </c>
       <c r="I26" t="str">
-        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
+        <v>Affiché en gros chiffres zone haute dashboard</v>
       </c>
     </row>
     <row r="27">
@@ -1172,25 +1172,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C27" t="str">
-        <v>Graphiques optionnels (futur)</v>
+        <v>Matrice de conformité interactive</v>
       </c>
       <c r="D27" t="str">
-        <v>Tendances audit timeline, pie charts conformity domains</v>
+        <v>Tableau avec % conformité par criterion, tri/filtre</v>
       </c>
       <c r="E27" t="str">
-        <v>P3</v>
+        <v>P2</v>
       </c>
       <c r="F27" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G27" t="str">
-        <v>REQ-024</v>
+        <v>REQ-017</v>
       </c>
       <c r="H27" t="str">
-        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
+        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
       </c>
       <c r="I27" t="str">
-        <v>MVP n'a pas graphiques, architecture prête pour.</v>
+        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
       </c>
     </row>
     <row r="28">
@@ -1198,28 +1198,28 @@
         <v>REQ-027</v>
       </c>
       <c r="B28" t="str">
-        <v>Configuration &amp; Flexibilité</v>
+        <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C28" t="str">
-        <v>Support multilingue</v>
+        <v>Graphiques optionnels (futur)</v>
       </c>
       <c r="D28" t="str">
-        <v>FR et EN, sélection par campaign</v>
+        <v>Tendances audit timeline, pie charts conformity domains</v>
       </c>
       <c r="E28" t="str">
-        <v>P1</v>
+        <v>P3</v>
       </c>
       <c r="F28" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G28" t="str">
-        <v>REQ-030</v>
+        <v>REQ-025</v>
       </c>
       <c r="H28" t="str">
-        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
+        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
       </c>
       <c r="I28" t="str">
-        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
+        <v>MVP n'a pas graphiques, architecture prête pour.</v>
       </c>
     </row>
     <row r="29">
@@ -1230,10 +1230,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C29" t="str">
-        <v>Modèle Ollama configurable</v>
+        <v>Support multilingue</v>
       </c>
       <c r="D29" t="str">
-        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
+        <v>FR et EN, sélection par campaign</v>
       </c>
       <c r="E29" t="str">
         <v>P1</v>
@@ -1242,13 +1242,13 @@
         <v>Complété</v>
       </c>
       <c r="G29" t="str">
-        <v>REQ-009</v>
+        <v>REQ-031</v>
       </c>
       <c r="H29" t="str">
-        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
+        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
       </c>
       <c r="I29" t="str">
-        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
+        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
       </c>
     </row>
     <row r="30">
@@ -1259,10 +1259,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C30" t="str">
-        <v>OpenAI optionnel</v>
+        <v>Modèle Ollama configurable</v>
       </c>
       <c r="D30" t="str">
-        <v>API key via .env, fallback auto Ollama si absent</v>
+        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
       </c>
       <c r="E30" t="str">
         <v>P1</v>
@@ -1271,13 +1271,13 @@
         <v>Complété</v>
       </c>
       <c r="G30" t="str">
-        <v>REQ-030</v>
+        <v>REQ-010</v>
       </c>
       <c r="H30" t="str">
-        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
+        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
       </c>
       <c r="I30" t="str">
-        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
+        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
       </c>
     </row>
     <row r="31">
@@ -1288,25 +1288,25 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C31" t="str">
-        <v>Thèmes personnalisés</v>
+        <v>OpenAI optionnel</v>
       </c>
       <c r="D31" t="str">
-        <v>Texte libre pour documents et questions</v>
+        <v>API key via .env, fallback auto Ollama si absent</v>
       </c>
       <c r="E31" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F31" t="str">
         <v>Complété</v>
       </c>
       <c r="G31" t="str">
-        <v>-</v>
+        <v>REQ-031</v>
       </c>
       <c r="H31" t="str">
-        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
+        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
       </c>
       <c r="I31" t="str">
-        <v>Permet flexibilité sur domaines audit custom</v>
+        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
       </c>
     </row>
     <row r="32">
@@ -1314,16 +1314,16 @@
         <v>REQ-031</v>
       </c>
       <c r="B32" t="str">
-        <v>Infrastructure &amp; Déploiement</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C32" t="str">
-        <v>Offline-first capability</v>
+        <v>Thèmes personnalisés</v>
       </c>
       <c r="D32" t="str">
-        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
+        <v>Texte libre pour documents et questions</v>
       </c>
       <c r="E32" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F32" t="str">
         <v>Complété</v>
@@ -1332,10 +1332,10 @@
         <v>-</v>
       </c>
       <c r="H32" t="str">
-        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
+        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
       </c>
       <c r="I32" t="str">
-        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
+        <v>Permet flexibilité sur domaines audit custom</v>
       </c>
     </row>
     <row r="33">
@@ -1346,25 +1346,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C33" t="str">
-        <v>Automation PowerShell</v>
+        <v>Offline-first capability</v>
       </c>
       <c r="D33" t="str">
-        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
+        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
       </c>
       <c r="E33" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F33" t="str">
         <v>Complété</v>
       </c>
       <c r="G33" t="str">
-        <v>REQ-028, REQ-031</v>
+        <v>-</v>
       </c>
       <c r="H33" t="str">
-        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
+        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
       </c>
       <c r="I33" t="str">
-        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
+        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
       </c>
     </row>
     <row r="34">
@@ -1375,25 +1375,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C34" t="str">
-        <v>Versionning Git &amp; GitHub</v>
+        <v>Automation PowerShell</v>
       </c>
       <c r="D34" t="str">
-        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
+        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
       </c>
       <c r="E34" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F34" t="str">
         <v>Complété</v>
       </c>
       <c r="G34" t="str">
-        <v>REQ-007, REQ-031</v>
+        <v>REQ-029, REQ-032</v>
       </c>
       <c r="H34" t="str">
-        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
+        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
       </c>
       <c r="I34" t="str">
-        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
+        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
       </c>
     </row>
     <row r="35">
@@ -1404,25 +1404,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C35" t="str">
-        <v>API REST Fastify</v>
+        <v>Versionning Git &amp; GitHub</v>
       </c>
       <c r="D35" t="str">
-        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
+        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
       </c>
       <c r="E35" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F35" t="str">
         <v>Complété</v>
       </c>
       <c r="G35" t="str">
-        <v>REQ-013, REQ-031</v>
+        <v>REQ-008, REQ-032</v>
       </c>
       <c r="H35" t="str">
-        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
+        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
       </c>
       <c r="I35" t="str">
-        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
+        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
       </c>
     </row>
     <row r="36">
@@ -1430,28 +1430,28 @@
         <v>REQ-035</v>
       </c>
       <c r="B36" t="str">
-        <v>UI/UX</v>
+        <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C36" t="str">
-        <v>UI React + TypeScript + Vite</v>
+        <v>API REST Fastify</v>
       </c>
       <c r="D36" t="str">
-        <v>Bundling optimisé, HMR dev mode</v>
+        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
       </c>
       <c r="E36" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F36" t="str">
         <v>Complété</v>
       </c>
       <c r="G36" t="str">
-        <v>REQ-017, REQ-031</v>
+        <v>REQ-014, REQ-032</v>
       </c>
       <c r="H36" t="str">
-        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
+        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
       </c>
       <c r="I36" t="str">
-        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
+        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
       </c>
     </row>
     <row r="37">
@@ -1462,10 +1462,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C37" t="str">
-        <v>Configuration IA section</v>
+        <v>UI React + TypeScript + Vite</v>
       </c>
       <c r="D37" t="str">
-        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
+        <v>Bundling optimisé, HMR dev mode</v>
       </c>
       <c r="E37" t="str">
         <v>P1</v>
@@ -1474,13 +1474,13 @@
         <v>Complété</v>
       </c>
       <c r="G37" t="str">
-        <v>REQ-024, REQ-031</v>
+        <v>REQ-018, REQ-032</v>
       </c>
       <c r="H37" t="str">
-        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
+        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
       </c>
       <c r="I37" t="str">
-        <v>UX: clair et accessible, pas scroll nécessaire</v>
+        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
       </c>
     </row>
     <row r="38">
@@ -1491,10 +1491,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C38" t="str">
-        <v>Génération questions section</v>
+        <v>Configuration IA section</v>
       </c>
       <c r="D38" t="str">
-        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
+        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
       </c>
       <c r="E38" t="str">
         <v>P1</v>
@@ -1503,13 +1503,13 @@
         <v>Complété</v>
       </c>
       <c r="G38" t="str">
-        <v>REQ-014, REQ-015, REQ-031</v>
+        <v>REQ-025, REQ-032</v>
       </c>
       <c r="H38" t="str">
-        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
+        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
       </c>
       <c r="I38" t="str">
-        <v>État uploadingReferential: loading indicator, disabled submit</v>
+        <v>UX: clair et accessible, pas scroll nécessaire</v>
       </c>
     </row>
     <row r="39">
@@ -1520,10 +1520,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C39" t="str">
-        <v>Référentiel documentaire section</v>
+        <v>Génération questions section</v>
       </c>
       <c r="D39" t="str">
-        <v>Ajouter document avec métas, liste affichée</v>
+        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
       </c>
       <c r="E39" t="str">
         <v>P1</v>
@@ -1532,13 +1532,13 @@
         <v>Complété</v>
       </c>
       <c r="G39" t="str">
-        <v>REQ-019, REQ-020, REQ-031</v>
+        <v>REQ-015, REQ-016, REQ-032</v>
       </c>
       <c r="H39" t="str">
-        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
+        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
       </c>
       <c r="I39" t="str">
-        <v>Erreurs affichées, success feedback, état documentS refresh</v>
+        <v>État uploadingReferential: loading indicator, disabled submit</v>
       </c>
     </row>
     <row r="40">
@@ -1549,10 +1549,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C40" t="str">
-        <v>Échelles métriques config</v>
+        <v>Référentiel documentaire section</v>
       </c>
       <c r="D40" t="str">
-        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
+        <v>Ajouter document avec métas, liste affichée</v>
       </c>
       <c r="E40" t="str">
         <v>P1</v>
@@ -1561,13 +1561,13 @@
         <v>Complété</v>
       </c>
       <c r="G40" t="str">
-        <v>REQ-021, REQ-022, REQ-031</v>
+        <v>REQ-020, REQ-021, REQ-032</v>
       </c>
       <c r="H40" t="str">
-        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
+        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
       </c>
       <c r="I40" t="str">
-        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
+        <v>Erreurs affichées, success feedback, état documentS refresh</v>
       </c>
     </row>
     <row r="41">
@@ -1578,10 +1578,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C41" t="str">
-        <v>Dashboard avec KPIs</v>
+        <v>Échelles métriques config</v>
       </c>
       <c r="D41" t="str">
-        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
+        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
       </c>
       <c r="E41" t="str">
         <v>P1</v>
@@ -1590,13 +1590,13 @@
         <v>Complété</v>
       </c>
       <c r="G41" t="str">
-        <v>-</v>
+        <v>REQ-022, REQ-023, REQ-032</v>
       </c>
       <c r="H41" t="str">
-        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
+        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
       </c>
       <c r="I41" t="str">
-        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
+        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
       </c>
     </row>
     <row r="42">
@@ -1607,10 +1607,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C42" t="str">
-        <v>Gestion entretiens</v>
+        <v>Dashboard avec KPIs</v>
       </c>
       <c r="D42" t="str">
-        <v>Interviewés, notes questions, scoring intégré</v>
+        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
       </c>
       <c r="E42" t="str">
         <v>P1</v>
@@ -1622,10 +1622,10 @@
         <v>-</v>
       </c>
       <c r="H42" t="str">
-        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
+        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
       </c>
       <c r="I42" t="str">
-        <v>Chaque note liée criterion + interviewee + score optionnel</v>
+        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
       </c>
     </row>
     <row r="43">
@@ -1636,10 +1636,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C43" t="str">
-        <v>Audit log viewer</v>
+        <v>Gestion entretiens</v>
       </c>
       <c r="D43" t="str">
-        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
+        <v>Interviewés, notes questions, scoring intégré</v>
       </c>
       <c r="E43" t="str">
         <v>P1</v>
@@ -1648,13 +1648,13 @@
         <v>Complété</v>
       </c>
       <c r="G43" t="str">
-        <v>REQ-041</v>
+        <v>-</v>
       </c>
       <c r="H43" t="str">
-        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
+        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
       </c>
       <c r="I43" t="str">
-        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
+        <v>Chaque note liée criterion + interviewee + score optionnel</v>
       </c>
     </row>
     <row r="44">
@@ -1665,25 +1665,25 @@
         <v>UI/UX</v>
       </c>
       <c r="C44" t="str">
-        <v>Export buttons</v>
+        <v>Audit log viewer</v>
       </c>
       <c r="D44" t="str">
-        <v>Boutons DOCX et CSV téléchargement</v>
+        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
       </c>
       <c r="E44" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F44" t="str">
         <v>Complété</v>
       </c>
       <c r="G44" t="str">
-        <v>-</v>
+        <v>REQ-042</v>
       </c>
       <c r="H44" t="str">
-        <v>POST /export-report et /export-csv. browser Blob download.</v>
+        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
       </c>
       <c r="I44" t="str">
-        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
       </c>
     </row>
     <row r="45">
@@ -1691,13 +1691,13 @@
         <v>REQ-044</v>
       </c>
       <c r="B45" t="str">
-        <v>Persévérance &amp; Facilité</v>
+        <v>UI/UX</v>
       </c>
       <c r="C45" t="str">
-        <v>Documentation complète</v>
+        <v>Export buttons</v>
       </c>
       <c r="D45" t="str">
-        <v>Setup guides, quickstart, git manual, examples références</v>
+        <v>Boutons DOCX et CSV téléchargement</v>
       </c>
       <c r="E45" t="str">
         <v>P2</v>
@@ -1709,13 +1709,13 @@
         <v>-</v>
       </c>
       <c r="H45" t="str">
-        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
+        <v>POST /export-report et /export-csv. browser Blob download.</v>
       </c>
       <c r="I45" t="str">
-        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
-      </c>
-    </row>
-    <row r="46" xml:space="preserve">
+        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="str">
         <v>REQ-045</v>
       </c>
@@ -1723,10 +1723,10 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C46" t="str">
-        <v>One-command installation</v>
+        <v>Documentation complète</v>
       </c>
       <c r="D46" t="str">
-        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+        <v>Setup guides, quickstart, git manual, examples références</v>
       </c>
       <c r="E46" t="str">
         <v>P2</v>
@@ -1737,12 +1737,11 @@
       <c r="G46" t="str">
         <v>-</v>
       </c>
-      <c r="H46" t="str" xml:space="preserve">
-        <v xml:space="preserve">.
- install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      <c r="H46" t="str">
+        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
       </c>
       <c r="I46" t="str">
-        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
       </c>
     </row>
     <row r="47" xml:space="preserve">
@@ -1753,41 +1752,42 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C47" t="str">
+        <v>One-command installation</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+      </c>
+      <c r="E47" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G47" t="str">
+        <v>-</v>
+      </c>
+      <c r="H47" t="str" xml:space="preserve">
+        <v xml:space="preserve">.
+ install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      </c>
+      <c r="I47" t="str">
+        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>REQ-047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C48" t="str">
         <v>One-command launch</v>
       </c>
-      <c r="D47" t="str" xml:space="preserve">
+      <c r="D48" t="str" xml:space="preserve">
         <v xml:space="preserve">npm run dev ou .
 start-rubis.ps1 pour lancer tout</v>
       </c>
-      <c r="E47" t="str">
-        <v>P2</v>
-      </c>
-      <c r="F47" t="str">
-        <v>Complété</v>
-      </c>
-      <c r="G47" t="str">
-        <v>-</v>
-      </c>
-      <c r="H47" t="str">
-        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
-      </c>
-      <c r="I47" t="str">
-        <v>Détection auto erreurs, log output lisible</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>REQ-047</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Persévérance &amp; Facilité</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Clear error messages</v>
-      </c>
-      <c r="D48" t="str">
-        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
-      </c>
       <c r="E48" t="str">
         <v>P2</v>
       </c>
@@ -1798,10 +1798,10 @@
         <v>-</v>
       </c>
       <c r="H48" t="str">
-        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
       </c>
       <c r="I48" t="str">
-        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+        <v>Détection auto erreurs, log output lisible</v>
       </c>
     </row>
     <row r="49">
@@ -1812,30 +1812,59 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C49" t="str">
-        <v>Roadmap versioning</v>
+        <v>Clear error messages</v>
       </c>
       <c r="D49" t="str">
-        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
       </c>
       <c r="E49" t="str">
         <v>P2</v>
       </c>
       <c r="F49" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G49" t="str">
         <v>-</v>
       </c>
       <c r="H49" t="str">
+        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>REQ-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Roadmap versioning</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+      </c>
+      <c r="E50" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G50" t="str">
+        <v>-</v>
+      </c>
+      <c r="H50" t="str">
         <v>Créer ROADMAP.xlsx avec specs, priorités, statuts, directives implémentation.</v>
       </c>
-      <c r="I49" t="str">
+      <c r="I50" t="str">
         <v>À committé dans git, mis à jour post-MVP pour v2 features</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -763,28 +763,28 @@
         <v>REQ-012</v>
       </c>
       <c r="B13" t="str">
-        <v>IA &amp; Génération</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C13" t="str">
-        <v>Parsing référentiel multi-format</v>
+        <v>Sélection IA par phase dans module admin</v>
       </c>
       <c r="D13" t="str">
-        <v>Support PDF et Excel avec extraction de texte</v>
+        <v>Permet à l'utilisateur de choisir quelle IA utiliser (OpenAI ou Ollama) pour chaque phase du workflow d'audit via interface d'administration</v>
       </c>
       <c r="E13" t="str">
         <v>P1</v>
       </c>
       <c r="F13" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G13" t="str">
-        <v>REQ-008</v>
+        <v>REQ-004, REQ-009, REQ-010, REQ-031</v>
       </c>
       <c r="H13" t="str">
-        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
+        <v>Section admin protégée. Config par phase: {phase: '1.1-Préparation'|'1.2-Entretiens'|'1.3-Scoring'|'1.4-Rapports', aiProvider: 'openai'|'ollama', ollamaModel?: 'mistral'|'gemma3:4b'}. Endpoints: GET/POST /admin/ai-config. Stockage db.data.aiConfig. UI: table éditable avec dropdown provider + model. Au runtime, generateQuestions() check phase active et route vers bon provider.</v>
       </c>
       <c r="I13" t="str">
-        <v>Gère encodages UTF-8, caractères spéciaux</v>
+        <v>Flexibilité maximale: OpenAI rapide pour prépa, Ollama offline pour entretiens terrain. Validation: si OpenAI sélectionné, vérifier OPENAI_API_KEY présent. Config par campagne ou globale selon besoin.</v>
       </c>
     </row>
     <row r="14">
@@ -795,10 +795,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C14" t="str">
-        <v>Prompt dynamique contextuel</v>
+        <v>Parsing référentiel multi-format</v>
       </c>
       <c r="D14" t="str">
-        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
+        <v>Support PDF et Excel avec extraction de texte</v>
       </c>
       <c r="E14" t="str">
         <v>P1</v>
@@ -810,10 +810,10 @@
         <v>REQ-008</v>
       </c>
       <c r="H14" t="str">
-        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
+        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
       </c>
       <c r="I14" t="str">
-        <v>Zod validation sur count (1-10), language (fr/en)</v>
+        <v>Gère encodages UTF-8, caractères spéciaux</v>
       </c>
     </row>
     <row r="15">
@@ -821,28 +821,28 @@
         <v>REQ-014</v>
       </c>
       <c r="B15" t="str">
-        <v>Structuration données</v>
+        <v>IA &amp; Génération</v>
       </c>
       <c r="C15" t="str">
-        <v>Modèle Document</v>
+        <v>Prompt dynamique contextuel</v>
       </c>
       <c r="D15" t="str">
-        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
+        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
       </c>
       <c r="E15" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F15" t="str">
         <v>Complété</v>
       </c>
       <c r="G15" t="str">
-        <v>REQ-002</v>
+        <v>REQ-008</v>
       </c>
       <c r="H15" t="str">
-        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
+        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
       </c>
       <c r="I15" t="str">
-        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
+        <v>Zod validation sur count (1-10), language (fr/en)</v>
       </c>
     </row>
     <row r="16">
@@ -853,10 +853,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C16" t="str">
-        <v>Modèle Interviewé</v>
+        <v>Modèle Document</v>
       </c>
       <c r="D16" t="str">
-        <v>Nom complet, rôle, lié à campaign</v>
+        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
       </c>
       <c r="E16" t="str">
         <v>P0</v>
@@ -868,10 +868,10 @@
         <v>REQ-002</v>
       </c>
       <c r="H16" t="str">
-        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
+        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
       </c>
       <c r="I16" t="str">
-        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
+        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
       </c>
     </row>
     <row r="17">
@@ -882,10 +882,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C17" t="str">
-        <v>Modèle Note d'entretien</v>
+        <v>Modèle Interviewé</v>
       </c>
       <c r="D17" t="str">
-        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
+        <v>Nom complet, rôle, lié à campaign</v>
       </c>
       <c r="E17" t="str">
         <v>P0</v>
@@ -894,13 +894,13 @@
         <v>Complété</v>
       </c>
       <c r="G17" t="str">
-        <v>REQ-005, REQ-015</v>
+        <v>REQ-002</v>
       </c>
       <c r="H17" t="str">
-        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
+        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
       </c>
       <c r="I17" t="str">
-        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
+        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
       </c>
     </row>
     <row r="18">
@@ -911,25 +911,25 @@
         <v>Structuration données</v>
       </c>
       <c r="C18" t="str">
-        <v>Matrice de conformité</v>
+        <v>Modèle Note d'entretien</v>
       </c>
       <c r="D18" t="str">
-        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
+        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
       </c>
       <c r="E18" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F18" t="str">
         <v>Complété</v>
       </c>
       <c r="G18" t="str">
-        <v>REQ-016</v>
+        <v>REQ-005, REQ-016</v>
       </c>
       <c r="H18" t="str">
-        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
+        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
       </c>
       <c r="I18" t="str">
-        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
+        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
       </c>
     </row>
     <row r="19">
@@ -940,10 +940,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C19" t="str">
-        <v>Configuration Métriques</v>
+        <v>Matrice de conformité</v>
       </c>
       <c r="D19" t="str">
-        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
+        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
       </c>
       <c r="E19" t="str">
         <v>P1</v>
@@ -952,13 +952,13 @@
         <v>Complété</v>
       </c>
       <c r="G19" t="str">
-        <v>REQ-002</v>
+        <v>REQ-017</v>
       </c>
       <c r="H19" t="str">
-        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
+        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
       </c>
       <c r="I19" t="str">
-        <v>Format texte (ex: '1-5') pour flexibilité</v>
+        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
       </c>
     </row>
     <row r="20">
@@ -966,13 +966,13 @@
         <v>REQ-019</v>
       </c>
       <c r="B20" t="str">
-        <v>Audit &amp; Traçabilité</v>
+        <v>Structuration données</v>
       </c>
       <c r="C20" t="str">
-        <v>Audit Log complet</v>
+        <v>Configuration Métriques</v>
       </c>
       <c r="D20" t="str">
-        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
+        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
       </c>
       <c r="E20" t="str">
         <v>P1</v>
@@ -981,13 +981,13 @@
         <v>Complété</v>
       </c>
       <c r="G20" t="str">
-        <v>REQ-002, REQ-031</v>
+        <v>REQ-002</v>
       </c>
       <c r="H20" t="str">
-        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
+        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
       </c>
       <c r="I20" t="str">
-        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
+        <v>Format texte (ex: '1-5') pour flexibilité</v>
       </c>
     </row>
     <row r="21">
@@ -998,10 +998,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C21" t="str">
-        <v>Filtrage logs par période</v>
+        <v>Audit Log complet</v>
       </c>
       <c r="D21" t="str">
-        <v>Vue 7j, 30j, tout (by date range filter)</v>
+        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
       </c>
       <c r="E21" t="str">
         <v>P1</v>
@@ -1010,13 +1010,13 @@
         <v>Complété</v>
       </c>
       <c r="G21" t="str">
-        <v>REQ-019</v>
+        <v>REQ-002, REQ-032</v>
       </c>
       <c r="H21" t="str">
-        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
+        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
       </c>
       <c r="I21" t="str">
-        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
+        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
       </c>
     </row>
     <row r="22">
@@ -1027,10 +1027,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C22" t="str">
-        <v>Filtrage logs par action</v>
+        <v>Filtrage logs par période</v>
       </c>
       <c r="D22" t="str">
-        <v>Filter sur type d'action (campaign.created, etc.)</v>
+        <v>Vue 7j, 30j, tout (by date range filter)</v>
       </c>
       <c r="E22" t="str">
         <v>P1</v>
@@ -1039,13 +1039,13 @@
         <v>Complété</v>
       </c>
       <c r="G22" t="str">
-        <v>REQ-019</v>
+        <v>REQ-020</v>
       </c>
       <c r="H22" t="str">
-        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
+        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
       </c>
       <c r="I22" t="str">
-        <v>Enum actions découvertes dynamiquement from logs</v>
+        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
       </c>
     </row>
     <row r="23">
@@ -1053,28 +1053,28 @@
         <v>REQ-022</v>
       </c>
       <c r="B23" t="str">
-        <v>Rapports &amp; Exports</v>
+        <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C23" t="str">
-        <v>Export DOCX</v>
+        <v>Filtrage logs par action</v>
       </c>
       <c r="D23" t="str">
-        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
+        <v>Filter sur type d'action (campaign.created, etc.)</v>
       </c>
       <c r="E23" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F23" t="str">
         <v>Complété</v>
       </c>
       <c r="G23" t="str">
-        <v>REQ-007, REQ-017</v>
+        <v>REQ-020</v>
       </c>
       <c r="H23" t="str">
-        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
+        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
       </c>
       <c r="I23" t="str">
-        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
+        <v>Enum actions découvertes dynamiquement from logs</v>
       </c>
     </row>
     <row r="24">
@@ -1085,10 +1085,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C24" t="str">
-        <v>Export CSV</v>
+        <v>Export DOCX</v>
       </c>
       <c r="D24" t="str">
-        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
+        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
       </c>
       <c r="E24" t="str">
         <v>P2</v>
@@ -1097,13 +1097,13 @@
         <v>Complété</v>
       </c>
       <c r="G24" t="str">
-        <v>REQ-017, REQ-019</v>
+        <v>REQ-007, REQ-018</v>
       </c>
       <c r="H24" t="str">
-        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
+        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
       </c>
       <c r="I24" t="str">
-        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
+        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
       </c>
     </row>
     <row r="25">
@@ -1114,10 +1114,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C25" t="str">
-        <v>Gestion des rapports</v>
+        <v>Export CSV</v>
       </c>
       <c r="D25" t="str">
-        <v>Stocker rapports générés avec titre, date gen, version</v>
+        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
       </c>
       <c r="E25" t="str">
         <v>P2</v>
@@ -1126,13 +1126,13 @@
         <v>Complété</v>
       </c>
       <c r="G25" t="str">
-        <v>REQ-022, REQ-023</v>
+        <v>REQ-018, REQ-020</v>
       </c>
       <c r="H25" t="str">
-        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
+        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
       </c>
       <c r="I25" t="str">
-        <v>Récupérable dans UI, archivé pour traçabilité</v>
+        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
       </c>
     </row>
     <row r="26">
@@ -1140,28 +1140,28 @@
         <v>REQ-025</v>
       </c>
       <c r="B26" t="str">
-        <v>Dashboard &amp; Visualisation</v>
+        <v>Rapports &amp; Exports</v>
       </c>
       <c r="C26" t="str">
-        <v>KPIs essentiels</v>
+        <v>Gestion des rapports</v>
       </c>
       <c r="D26" t="str">
-        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
+        <v>Stocker rapports générés avec titre, date gen, version</v>
       </c>
       <c r="E26" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F26" t="str">
         <v>Complété</v>
       </c>
       <c r="G26" t="str">
-        <v>REQ-014, REQ-015, REQ-016</v>
+        <v>REQ-023, REQ-024</v>
       </c>
       <c r="H26" t="str">
-        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
+        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
       </c>
       <c r="I26" t="str">
-        <v>Affiché en gros chiffres zone haute dashboard</v>
+        <v>Récupérable dans UI, archivé pour traçabilité</v>
       </c>
     </row>
     <row r="27">
@@ -1172,25 +1172,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C27" t="str">
-        <v>Matrice de conformité interactive</v>
+        <v>KPIs essentiels</v>
       </c>
       <c r="D27" t="str">
-        <v>Tableau avec % conformité par criterion, tri/filtre</v>
+        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
       </c>
       <c r="E27" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F27" t="str">
         <v>Complété</v>
       </c>
       <c r="G27" t="str">
-        <v>REQ-017</v>
+        <v>REQ-015, REQ-016, REQ-017</v>
       </c>
       <c r="H27" t="str">
-        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
+        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
       </c>
       <c r="I27" t="str">
-        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
+        <v>Affiché en gros chiffres zone haute dashboard</v>
       </c>
     </row>
     <row r="28">
@@ -1201,25 +1201,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C28" t="str">
-        <v>Graphiques optionnels (futur)</v>
+        <v>Matrice de conformité interactive</v>
       </c>
       <c r="D28" t="str">
-        <v>Tendances audit timeline, pie charts conformity domains</v>
+        <v>Tableau avec % conformité par criterion, tri/filtre</v>
       </c>
       <c r="E28" t="str">
-        <v>P3</v>
+        <v>P2</v>
       </c>
       <c r="F28" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G28" t="str">
-        <v>REQ-025</v>
+        <v>REQ-018</v>
       </c>
       <c r="H28" t="str">
-        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
+        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
       </c>
       <c r="I28" t="str">
-        <v>MVP n'a pas graphiques, architecture prête pour.</v>
+        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
       </c>
     </row>
     <row r="29">
@@ -1227,28 +1227,28 @@
         <v>REQ-028</v>
       </c>
       <c r="B29" t="str">
-        <v>Configuration &amp; Flexibilité</v>
+        <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C29" t="str">
-        <v>Support multilingue</v>
+        <v>Graphiques optionnels (futur)</v>
       </c>
       <c r="D29" t="str">
-        <v>FR et EN, sélection par campaign</v>
+        <v>Tendances audit timeline, pie charts conformity domains</v>
       </c>
       <c r="E29" t="str">
-        <v>P1</v>
+        <v>P3</v>
       </c>
       <c r="F29" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G29" t="str">
-        <v>REQ-031</v>
+        <v>REQ-026</v>
       </c>
       <c r="H29" t="str">
-        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
+        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
       </c>
       <c r="I29" t="str">
-        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
+        <v>MVP n'a pas graphiques, architecture prête pour.</v>
       </c>
     </row>
     <row r="30">
@@ -1259,10 +1259,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C30" t="str">
-        <v>Modèle Ollama configurable</v>
+        <v>Support multilingue</v>
       </c>
       <c r="D30" t="str">
-        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
+        <v>FR et EN, sélection par campaign</v>
       </c>
       <c r="E30" t="str">
         <v>P1</v>
@@ -1271,13 +1271,13 @@
         <v>Complété</v>
       </c>
       <c r="G30" t="str">
-        <v>REQ-010</v>
+        <v>REQ-032</v>
       </c>
       <c r="H30" t="str">
-        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
+        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
       </c>
       <c r="I30" t="str">
-        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
+        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
       </c>
     </row>
     <row r="31">
@@ -1288,10 +1288,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C31" t="str">
-        <v>OpenAI optionnel</v>
+        <v>Modèle Ollama configurable</v>
       </c>
       <c r="D31" t="str">
-        <v>API key via .env, fallback auto Ollama si absent</v>
+        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
       </c>
       <c r="E31" t="str">
         <v>P1</v>
@@ -1300,13 +1300,13 @@
         <v>Complété</v>
       </c>
       <c r="G31" t="str">
-        <v>REQ-031</v>
+        <v>REQ-010</v>
       </c>
       <c r="H31" t="str">
-        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
+        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
       </c>
       <c r="I31" t="str">
-        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
+        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
       </c>
     </row>
     <row r="32">
@@ -1317,25 +1317,25 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C32" t="str">
-        <v>Thèmes personnalisés</v>
+        <v>OpenAI optionnel</v>
       </c>
       <c r="D32" t="str">
-        <v>Texte libre pour documents et questions</v>
+        <v>API key via .env, fallback auto Ollama si absent</v>
       </c>
       <c r="E32" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F32" t="str">
         <v>Complété</v>
       </c>
       <c r="G32" t="str">
-        <v>-</v>
+        <v>REQ-032</v>
       </c>
       <c r="H32" t="str">
-        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
+        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
       </c>
       <c r="I32" t="str">
-        <v>Permet flexibilité sur domaines audit custom</v>
+        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
       </c>
     </row>
     <row r="33">
@@ -1343,16 +1343,16 @@
         <v>REQ-032</v>
       </c>
       <c r="B33" t="str">
-        <v>Infrastructure &amp; Déploiement</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C33" t="str">
-        <v>Offline-first capability</v>
+        <v>Thèmes personnalisés</v>
       </c>
       <c r="D33" t="str">
-        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
+        <v>Texte libre pour documents et questions</v>
       </c>
       <c r="E33" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F33" t="str">
         <v>Complété</v>
@@ -1361,10 +1361,10 @@
         <v>-</v>
       </c>
       <c r="H33" t="str">
-        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
+        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
       </c>
       <c r="I33" t="str">
-        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
+        <v>Permet flexibilité sur domaines audit custom</v>
       </c>
     </row>
     <row r="34">
@@ -1375,25 +1375,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C34" t="str">
-        <v>Automation PowerShell</v>
+        <v>Offline-first capability</v>
       </c>
       <c r="D34" t="str">
-        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
+        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
       </c>
       <c r="E34" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F34" t="str">
         <v>Complété</v>
       </c>
       <c r="G34" t="str">
-        <v>REQ-029, REQ-032</v>
+        <v>-</v>
       </c>
       <c r="H34" t="str">
-        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
+        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
       </c>
       <c r="I34" t="str">
-        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
+        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
       </c>
     </row>
     <row r="35">
@@ -1404,25 +1404,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C35" t="str">
-        <v>Versionning Git &amp; GitHub</v>
+        <v>Automation PowerShell</v>
       </c>
       <c r="D35" t="str">
-        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
+        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
       </c>
       <c r="E35" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F35" t="str">
         <v>Complété</v>
       </c>
       <c r="G35" t="str">
-        <v>REQ-008, REQ-032</v>
+        <v>REQ-030, REQ-033</v>
       </c>
       <c r="H35" t="str">
-        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
+        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
       </c>
       <c r="I35" t="str">
-        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
+        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
       </c>
     </row>
     <row r="36">
@@ -1433,25 +1433,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C36" t="str">
-        <v>API REST Fastify</v>
+        <v>Versionning Git &amp; GitHub</v>
       </c>
       <c r="D36" t="str">
-        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
+        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
       </c>
       <c r="E36" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F36" t="str">
         <v>Complété</v>
       </c>
       <c r="G36" t="str">
-        <v>REQ-014, REQ-032</v>
+        <v>REQ-008, REQ-033</v>
       </c>
       <c r="H36" t="str">
-        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
+        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
       </c>
       <c r="I36" t="str">
-        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
+        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
       </c>
     </row>
     <row r="37">
@@ -1459,28 +1459,28 @@
         <v>REQ-036</v>
       </c>
       <c r="B37" t="str">
-        <v>UI/UX</v>
+        <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C37" t="str">
-        <v>UI React + TypeScript + Vite</v>
+        <v>API REST Fastify</v>
       </c>
       <c r="D37" t="str">
-        <v>Bundling optimisé, HMR dev mode</v>
+        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
       </c>
       <c r="E37" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F37" t="str">
         <v>Complété</v>
       </c>
       <c r="G37" t="str">
-        <v>REQ-018, REQ-032</v>
+        <v>REQ-015, REQ-033</v>
       </c>
       <c r="H37" t="str">
-        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
+        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
       </c>
       <c r="I37" t="str">
-        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
+        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
       </c>
     </row>
     <row r="38">
@@ -1491,10 +1491,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C38" t="str">
-        <v>Configuration IA section</v>
+        <v>UI React + TypeScript + Vite</v>
       </c>
       <c r="D38" t="str">
-        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
+        <v>Bundling optimisé, HMR dev mode</v>
       </c>
       <c r="E38" t="str">
         <v>P1</v>
@@ -1503,13 +1503,13 @@
         <v>Complété</v>
       </c>
       <c r="G38" t="str">
-        <v>REQ-025, REQ-032</v>
+        <v>REQ-019, REQ-033</v>
       </c>
       <c r="H38" t="str">
-        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
+        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
       </c>
       <c r="I38" t="str">
-        <v>UX: clair et accessible, pas scroll nécessaire</v>
+        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
       </c>
     </row>
     <row r="39">
@@ -1520,10 +1520,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C39" t="str">
-        <v>Génération questions section</v>
+        <v>Configuration IA section</v>
       </c>
       <c r="D39" t="str">
-        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
+        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
       </c>
       <c r="E39" t="str">
         <v>P1</v>
@@ -1532,13 +1532,13 @@
         <v>Complété</v>
       </c>
       <c r="G39" t="str">
-        <v>REQ-015, REQ-016, REQ-032</v>
+        <v>REQ-026, REQ-033</v>
       </c>
       <c r="H39" t="str">
-        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
+        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
       </c>
       <c r="I39" t="str">
-        <v>État uploadingReferential: loading indicator, disabled submit</v>
+        <v>UX: clair et accessible, pas scroll nécessaire</v>
       </c>
     </row>
     <row r="40">
@@ -1549,10 +1549,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C40" t="str">
-        <v>Référentiel documentaire section</v>
+        <v>Génération questions section</v>
       </c>
       <c r="D40" t="str">
-        <v>Ajouter document avec métas, liste affichée</v>
+        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
       </c>
       <c r="E40" t="str">
         <v>P1</v>
@@ -1561,13 +1561,13 @@
         <v>Complété</v>
       </c>
       <c r="G40" t="str">
-        <v>REQ-020, REQ-021, REQ-032</v>
+        <v>REQ-016, REQ-017, REQ-033</v>
       </c>
       <c r="H40" t="str">
-        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
+        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
       </c>
       <c r="I40" t="str">
-        <v>Erreurs affichées, success feedback, état documentS refresh</v>
+        <v>État uploadingReferential: loading indicator, disabled submit</v>
       </c>
     </row>
     <row r="41">
@@ -1578,10 +1578,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C41" t="str">
-        <v>Échelles métriques config</v>
+        <v>Référentiel documentaire section</v>
       </c>
       <c r="D41" t="str">
-        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
+        <v>Ajouter document avec métas, liste affichée</v>
       </c>
       <c r="E41" t="str">
         <v>P1</v>
@@ -1590,13 +1590,13 @@
         <v>Complété</v>
       </c>
       <c r="G41" t="str">
-        <v>REQ-022, REQ-023, REQ-032</v>
+        <v>REQ-021, REQ-022, REQ-033</v>
       </c>
       <c r="H41" t="str">
-        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
+        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
       </c>
       <c r="I41" t="str">
-        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
+        <v>Erreurs affichées, success feedback, état documentS refresh</v>
       </c>
     </row>
     <row r="42">
@@ -1607,10 +1607,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C42" t="str">
-        <v>Dashboard avec KPIs</v>
+        <v>Échelles métriques config</v>
       </c>
       <c r="D42" t="str">
-        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
+        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
       </c>
       <c r="E42" t="str">
         <v>P1</v>
@@ -1619,13 +1619,13 @@
         <v>Complété</v>
       </c>
       <c r="G42" t="str">
-        <v>-</v>
+        <v>REQ-023, REQ-024, REQ-033</v>
       </c>
       <c r="H42" t="str">
-        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
+        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
       </c>
       <c r="I42" t="str">
-        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
+        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
       </c>
     </row>
     <row r="43">
@@ -1636,10 +1636,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C43" t="str">
-        <v>Gestion entretiens</v>
+        <v>Dashboard avec KPIs</v>
       </c>
       <c r="D43" t="str">
-        <v>Interviewés, notes questions, scoring intégré</v>
+        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
       </c>
       <c r="E43" t="str">
         <v>P1</v>
@@ -1651,10 +1651,10 @@
         <v>-</v>
       </c>
       <c r="H43" t="str">
-        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
+        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
       </c>
       <c r="I43" t="str">
-        <v>Chaque note liée criterion + interviewee + score optionnel</v>
+        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
       </c>
     </row>
     <row r="44">
@@ -1665,10 +1665,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C44" t="str">
-        <v>Audit log viewer</v>
+        <v>Gestion entretiens</v>
       </c>
       <c r="D44" t="str">
-        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
+        <v>Interviewés, notes questions, scoring intégré</v>
       </c>
       <c r="E44" t="str">
         <v>P1</v>
@@ -1677,13 +1677,13 @@
         <v>Complété</v>
       </c>
       <c r="G44" t="str">
-        <v>REQ-042</v>
+        <v>-</v>
       </c>
       <c r="H44" t="str">
-        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
+        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
       </c>
       <c r="I44" t="str">
-        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
+        <v>Chaque note liée criterion + interviewee + score optionnel</v>
       </c>
     </row>
     <row r="45">
@@ -1694,25 +1694,25 @@
         <v>UI/UX</v>
       </c>
       <c r="C45" t="str">
-        <v>Export buttons</v>
+        <v>Audit log viewer</v>
       </c>
       <c r="D45" t="str">
-        <v>Boutons DOCX et CSV téléchargement</v>
+        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
       </c>
       <c r="E45" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F45" t="str">
         <v>Complété</v>
       </c>
       <c r="G45" t="str">
-        <v>-</v>
+        <v>REQ-043</v>
       </c>
       <c r="H45" t="str">
-        <v>POST /export-report et /export-csv. browser Blob download.</v>
+        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
       </c>
       <c r="I45" t="str">
-        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
       </c>
     </row>
     <row r="46">
@@ -1720,13 +1720,13 @@
         <v>REQ-045</v>
       </c>
       <c r="B46" t="str">
-        <v>Persévérance &amp; Facilité</v>
+        <v>UI/UX</v>
       </c>
       <c r="C46" t="str">
-        <v>Documentation complète</v>
+        <v>Export buttons</v>
       </c>
       <c r="D46" t="str">
-        <v>Setup guides, quickstart, git manual, examples références</v>
+        <v>Boutons DOCX et CSV téléchargement</v>
       </c>
       <c r="E46" t="str">
         <v>P2</v>
@@ -1738,13 +1738,13 @@
         <v>-</v>
       </c>
       <c r="H46" t="str">
-        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
+        <v>POST /export-report et /export-csv. browser Blob download.</v>
       </c>
       <c r="I46" t="str">
-        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
-      </c>
-    </row>
-    <row r="47" xml:space="preserve">
+        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="str">
         <v>REQ-046</v>
       </c>
@@ -1752,10 +1752,10 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C47" t="str">
-        <v>One-command installation</v>
+        <v>Documentation complète</v>
       </c>
       <c r="D47" t="str">
-        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+        <v>Setup guides, quickstart, git manual, examples références</v>
       </c>
       <c r="E47" t="str">
         <v>P2</v>
@@ -1766,12 +1766,11 @@
       <c r="G47" t="str">
         <v>-</v>
       </c>
-      <c r="H47" t="str" xml:space="preserve">
-        <v xml:space="preserve">.
- install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      <c r="H47" t="str">
+        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
       </c>
       <c r="I47" t="str">
-        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
       </c>
     </row>
     <row r="48" xml:space="preserve">
@@ -1782,41 +1781,42 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C48" t="str">
+        <v>One-command installation</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+      </c>
+      <c r="E48" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G48" t="str">
+        <v>-</v>
+      </c>
+      <c r="H48" t="str" xml:space="preserve">
+        <v xml:space="preserve">.
+ install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      </c>
+      <c r="I48" t="str">
+        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
+        <v>REQ-048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C49" t="str">
         <v>One-command launch</v>
       </c>
-      <c r="D48" t="str" xml:space="preserve">
+      <c r="D49" t="str" xml:space="preserve">
         <v xml:space="preserve">npm run dev ou .
 start-rubis.ps1 pour lancer tout</v>
       </c>
-      <c r="E48" t="str">
-        <v>P2</v>
-      </c>
-      <c r="F48" t="str">
-        <v>Complété</v>
-      </c>
-      <c r="G48" t="str">
-        <v>-</v>
-      </c>
-      <c r="H48" t="str">
-        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
-      </c>
-      <c r="I48" t="str">
-        <v>Détection auto erreurs, log output lisible</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>REQ-048</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Persévérance &amp; Facilité</v>
-      </c>
-      <c r="C49" t="str">
-        <v>Clear error messages</v>
-      </c>
-      <c r="D49" t="str">
-        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
-      </c>
       <c r="E49" t="str">
         <v>P2</v>
       </c>
@@ -1827,10 +1827,10 @@
         <v>-</v>
       </c>
       <c r="H49" t="str">
-        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
       </c>
       <c r="I49" t="str">
-        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+        <v>Détection auto erreurs, log output lisible</v>
       </c>
     </row>
     <row r="50">
@@ -1841,30 +1841,59 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C50" t="str">
-        <v>Roadmap versioning</v>
+        <v>Clear error messages</v>
       </c>
       <c r="D50" t="str">
-        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
       </c>
       <c r="E50" t="str">
         <v>P2</v>
       </c>
       <c r="F50" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G50" t="str">
         <v>-</v>
       </c>
       <c r="H50" t="str">
+        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>REQ-050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Roadmap versioning</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+      </c>
+      <c r="E51" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G51" t="str">
+        <v>-</v>
+      </c>
+      <c r="H51" t="str">
         <v>Créer ROADMAP.xlsx avec specs, priorités, statuts, directives implémentation.</v>
       </c>
-      <c r="I50" t="str">
+      <c r="I51" t="str">
         <v>À committé dans git, mis à jour post-MVP pour v2 features</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -778,7 +778,7 @@
         <v>Planifié</v>
       </c>
       <c r="G13" t="str">
-        <v>REQ-004, REQ-009, REQ-010, REQ-031</v>
+        <v>REQ-004, REQ-009, REQ-010, REQ-032</v>
       </c>
       <c r="H13" t="str">
         <v>Section admin protégée. Config par phase: {phase: '1.1-Préparation'|'1.2-Entretiens'|'1.3-Scoring'|'1.4-Rapports', aiProvider: 'openai'|'ollama', ollamaModel?: 'mistral'|'gemma3:4b'}. Endpoints: GET/POST /admin/ai-config. Stockage db.data.aiConfig. UI: table éditable avec dropdown provider + model. Au runtime, generateQuestions() check phase active et route vers bon provider.</v>
@@ -792,28 +792,28 @@
         <v>REQ-013</v>
       </c>
       <c r="B14" t="str">
-        <v>IA &amp; Génération</v>
+        <v>Structuration données</v>
       </c>
       <c r="C14" t="str">
-        <v>Parsing référentiel multi-format</v>
+        <v>Gestion intelligente des documents référentiels</v>
       </c>
       <c r="D14" t="str">
-        <v>Support PDF et Excel avec extraction de texte</v>
+        <v>Utilisateur télécharge documents PDF/Excel. IA extrait automatiquement: titre, version, date publication, nb pages, sensibilité, auteurs, vérificateurs, approbateurs. Stockage métadonnées en table + date ajout + UI vérification/modification</v>
       </c>
       <c r="E14" t="str">
         <v>P1</v>
       </c>
       <c r="F14" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G14" t="str">
-        <v>REQ-008</v>
+        <v>REQ-009, REQ-010, REQ-032</v>
       </c>
       <c r="H14" t="str">
-        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
+        <v>Endpoint: POST /referential-documents/upload (multipart {file}). Service: extractDocumentMetadata(file) via LLM. Extract: {title, version, publicationDate, pageCount, sensitivity, authors, reviewers, approvers}. Stockage db.data.referentialDocuments: {id, campaignId, filename, uploadedAt, extractedMetadata, userVerifiedMetadata, fileSize, mimeType, storagePath}. UI: Upload form + table affichant docs avec métadonnées + bouton édition modal (formulaire avec fields pré-remplis) + bouton suppression. Validation: titre requis, autres optionnels. LLM prompt analyse: first/last page pour date/version, 'confidential'/'secret'/'public' keywords pour sensibilité, author/prepared/reviewed/approved/checked by patterns pour noms.</v>
       </c>
       <c r="I14" t="str">
-        <v>Gère encodages UTF-8, caractères spéciaux</v>
+        <v>Table central du référentiel: contient tous docs uploadés par user. Métadonnées extraites automatiquement, utilisateur valide/corrige si nécessaire. Stocke version AI-extracted + version user-corrected pour traçabilité. Liaison ultérieure: critères extraits depuis docs (REQ-006) utiliseront ces métadonnées.</v>
       </c>
     </row>
     <row r="15">
@@ -824,10 +824,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C15" t="str">
-        <v>Prompt dynamique contextuel</v>
+        <v>Parsing référentiel multi-format</v>
       </c>
       <c r="D15" t="str">
-        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
+        <v>Support PDF et Excel avec extraction de texte</v>
       </c>
       <c r="E15" t="str">
         <v>P1</v>
@@ -836,13 +836,13 @@
         <v>Complété</v>
       </c>
       <c r="G15" t="str">
-        <v>REQ-008</v>
+        <v>REQ-013</v>
       </c>
       <c r="H15" t="str">
-        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
+        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
       </c>
       <c r="I15" t="str">
-        <v>Zod validation sur count (1-10), language (fr/en)</v>
+        <v>Gère encodages UTF-8, caractères spéciaux</v>
       </c>
     </row>
     <row r="16">
@@ -850,28 +850,28 @@
         <v>REQ-015</v>
       </c>
       <c r="B16" t="str">
-        <v>Structuration données</v>
+        <v>IA &amp; Génération</v>
       </c>
       <c r="C16" t="str">
-        <v>Modèle Document</v>
+        <v>Prompt dynamique contextuel</v>
       </c>
       <c r="D16" t="str">
-        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
+        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
       </c>
       <c r="E16" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F16" t="str">
         <v>Complété</v>
       </c>
       <c r="G16" t="str">
-        <v>REQ-002</v>
+        <v>REQ-013</v>
       </c>
       <c r="H16" t="str">
-        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
+        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
       </c>
       <c r="I16" t="str">
-        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
+        <v>Zod validation sur count (1-10), language (fr/en)</v>
       </c>
     </row>
     <row r="17">
@@ -882,10 +882,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C17" t="str">
-        <v>Modèle Interviewé</v>
+        <v>Modèle Document</v>
       </c>
       <c r="D17" t="str">
-        <v>Nom complet, rôle, lié à campaign</v>
+        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
       </c>
       <c r="E17" t="str">
         <v>P0</v>
@@ -897,10 +897,10 @@
         <v>REQ-002</v>
       </c>
       <c r="H17" t="str">
-        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
+        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
       </c>
       <c r="I17" t="str">
-        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
+        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
       </c>
     </row>
     <row r="18">
@@ -911,10 +911,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C18" t="str">
-        <v>Modèle Note d'entretien</v>
+        <v>Modèle Interviewé</v>
       </c>
       <c r="D18" t="str">
-        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
+        <v>Nom complet, rôle, lié à campaign</v>
       </c>
       <c r="E18" t="str">
         <v>P0</v>
@@ -923,13 +923,13 @@
         <v>Complété</v>
       </c>
       <c r="G18" t="str">
-        <v>REQ-005, REQ-016</v>
+        <v>REQ-002</v>
       </c>
       <c r="H18" t="str">
-        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
+        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
       </c>
       <c r="I18" t="str">
-        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
+        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
       </c>
     </row>
     <row r="19">
@@ -940,25 +940,25 @@
         <v>Structuration données</v>
       </c>
       <c r="C19" t="str">
-        <v>Matrice de conformité</v>
+        <v>Modèle Note d'entretien</v>
       </c>
       <c r="D19" t="str">
-        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
+        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
       </c>
       <c r="E19" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F19" t="str">
         <v>Complété</v>
       </c>
       <c r="G19" t="str">
-        <v>REQ-017</v>
+        <v>REQ-005, REQ-017</v>
       </c>
       <c r="H19" t="str">
-        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
+        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
       </c>
       <c r="I19" t="str">
-        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
+        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
       </c>
     </row>
     <row r="20">
@@ -969,10 +969,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C20" t="str">
-        <v>Configuration Métriques</v>
+        <v>Matrice de conformité</v>
       </c>
       <c r="D20" t="str">
-        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
+        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
       </c>
       <c r="E20" t="str">
         <v>P1</v>
@@ -981,13 +981,13 @@
         <v>Complété</v>
       </c>
       <c r="G20" t="str">
-        <v>REQ-002</v>
+        <v>REQ-018</v>
       </c>
       <c r="H20" t="str">
-        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
+        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
       </c>
       <c r="I20" t="str">
-        <v>Format texte (ex: '1-5') pour flexibilité</v>
+        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
       </c>
     </row>
     <row r="21">
@@ -995,13 +995,13 @@
         <v>REQ-020</v>
       </c>
       <c r="B21" t="str">
-        <v>Audit &amp; Traçabilité</v>
+        <v>Structuration données</v>
       </c>
       <c r="C21" t="str">
-        <v>Audit Log complet</v>
+        <v>Configuration Métriques</v>
       </c>
       <c r="D21" t="str">
-        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
+        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
       </c>
       <c r="E21" t="str">
         <v>P1</v>
@@ -1010,13 +1010,13 @@
         <v>Complété</v>
       </c>
       <c r="G21" t="str">
-        <v>REQ-002, REQ-032</v>
+        <v>REQ-002</v>
       </c>
       <c r="H21" t="str">
-        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
+        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
       </c>
       <c r="I21" t="str">
-        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
+        <v>Format texte (ex: '1-5') pour flexibilité</v>
       </c>
     </row>
     <row r="22">
@@ -1027,10 +1027,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C22" t="str">
-        <v>Filtrage logs par période</v>
+        <v>Audit Log complet</v>
       </c>
       <c r="D22" t="str">
-        <v>Vue 7j, 30j, tout (by date range filter)</v>
+        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
       </c>
       <c r="E22" t="str">
         <v>P1</v>
@@ -1039,13 +1039,13 @@
         <v>Complété</v>
       </c>
       <c r="G22" t="str">
-        <v>REQ-020</v>
+        <v>REQ-002, REQ-032</v>
       </c>
       <c r="H22" t="str">
-        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
+        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
       </c>
       <c r="I22" t="str">
-        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
+        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
       </c>
     </row>
     <row r="23">
@@ -1056,10 +1056,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C23" t="str">
-        <v>Filtrage logs par action</v>
+        <v>Filtrage logs par période</v>
       </c>
       <c r="D23" t="str">
-        <v>Filter sur type d'action (campaign.created, etc.)</v>
+        <v>Vue 7j, 30j, tout (by date range filter)</v>
       </c>
       <c r="E23" t="str">
         <v>P1</v>
@@ -1068,13 +1068,13 @@
         <v>Complété</v>
       </c>
       <c r="G23" t="str">
-        <v>REQ-020</v>
+        <v>REQ-021</v>
       </c>
       <c r="H23" t="str">
-        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
+        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
       </c>
       <c r="I23" t="str">
-        <v>Enum actions découvertes dynamiquement from logs</v>
+        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
       </c>
     </row>
     <row r="24">
@@ -1082,28 +1082,28 @@
         <v>REQ-023</v>
       </c>
       <c r="B24" t="str">
-        <v>Rapports &amp; Exports</v>
+        <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C24" t="str">
-        <v>Export DOCX</v>
+        <v>Filtrage logs par action</v>
       </c>
       <c r="D24" t="str">
-        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
+        <v>Filter sur type d'action (campaign.created, etc.)</v>
       </c>
       <c r="E24" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F24" t="str">
         <v>Complété</v>
       </c>
       <c r="G24" t="str">
-        <v>REQ-007, REQ-018</v>
+        <v>REQ-021</v>
       </c>
       <c r="H24" t="str">
-        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
+        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
       </c>
       <c r="I24" t="str">
-        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
+        <v>Enum actions découvertes dynamiquement from logs</v>
       </c>
     </row>
     <row r="25">
@@ -1114,10 +1114,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C25" t="str">
-        <v>Export CSV</v>
+        <v>Export DOCX</v>
       </c>
       <c r="D25" t="str">
-        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
+        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
       </c>
       <c r="E25" t="str">
         <v>P2</v>
@@ -1126,13 +1126,13 @@
         <v>Complété</v>
       </c>
       <c r="G25" t="str">
-        <v>REQ-018, REQ-020</v>
+        <v>REQ-007, REQ-019</v>
       </c>
       <c r="H25" t="str">
-        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
+        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
       </c>
       <c r="I25" t="str">
-        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
+        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
       </c>
     </row>
     <row r="26">
@@ -1143,10 +1143,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C26" t="str">
-        <v>Gestion des rapports</v>
+        <v>Export CSV</v>
       </c>
       <c r="D26" t="str">
-        <v>Stocker rapports générés avec titre, date gen, version</v>
+        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
       </c>
       <c r="E26" t="str">
         <v>P2</v>
@@ -1155,13 +1155,13 @@
         <v>Complété</v>
       </c>
       <c r="G26" t="str">
-        <v>REQ-023, REQ-024</v>
+        <v>REQ-019, REQ-021</v>
       </c>
       <c r="H26" t="str">
-        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
+        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
       </c>
       <c r="I26" t="str">
-        <v>Récupérable dans UI, archivé pour traçabilité</v>
+        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
       </c>
     </row>
     <row r="27">
@@ -1169,28 +1169,28 @@
         <v>REQ-026</v>
       </c>
       <c r="B27" t="str">
-        <v>Dashboard &amp; Visualisation</v>
+        <v>Rapports &amp; Exports</v>
       </c>
       <c r="C27" t="str">
-        <v>KPIs essentiels</v>
+        <v>Gestion des rapports</v>
       </c>
       <c r="D27" t="str">
-        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
+        <v>Stocker rapports générés avec titre, date gen, version</v>
       </c>
       <c r="E27" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F27" t="str">
         <v>Complété</v>
       </c>
       <c r="G27" t="str">
-        <v>REQ-015, REQ-016, REQ-017</v>
+        <v>REQ-024, REQ-025</v>
       </c>
       <c r="H27" t="str">
-        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
+        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
       </c>
       <c r="I27" t="str">
-        <v>Affiché en gros chiffres zone haute dashboard</v>
+        <v>Récupérable dans UI, archivé pour traçabilité</v>
       </c>
     </row>
     <row r="28">
@@ -1201,25 +1201,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C28" t="str">
-        <v>Matrice de conformité interactive</v>
+        <v>KPIs essentiels</v>
       </c>
       <c r="D28" t="str">
-        <v>Tableau avec % conformité par criterion, tri/filtre</v>
+        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
       </c>
       <c r="E28" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F28" t="str">
         <v>Complété</v>
       </c>
       <c r="G28" t="str">
-        <v>REQ-018</v>
+        <v>REQ-016, REQ-017, REQ-018</v>
       </c>
       <c r="H28" t="str">
-        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
+        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
       </c>
       <c r="I28" t="str">
-        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
+        <v>Affiché en gros chiffres zone haute dashboard</v>
       </c>
     </row>
     <row r="29">
@@ -1230,25 +1230,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C29" t="str">
-        <v>Graphiques optionnels (futur)</v>
+        <v>Matrice de conformité interactive</v>
       </c>
       <c r="D29" t="str">
-        <v>Tendances audit timeline, pie charts conformity domains</v>
+        <v>Tableau avec % conformité par criterion, tri/filtre</v>
       </c>
       <c r="E29" t="str">
-        <v>P3</v>
+        <v>P2</v>
       </c>
       <c r="F29" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G29" t="str">
-        <v>REQ-026</v>
+        <v>REQ-019</v>
       </c>
       <c r="H29" t="str">
-        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
+        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
       </c>
       <c r="I29" t="str">
-        <v>MVP n'a pas graphiques, architecture prête pour.</v>
+        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
       </c>
     </row>
     <row r="30">
@@ -1256,28 +1256,28 @@
         <v>REQ-029</v>
       </c>
       <c r="B30" t="str">
-        <v>Configuration &amp; Flexibilité</v>
+        <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C30" t="str">
-        <v>Support multilingue</v>
+        <v>Graphiques optionnels (futur)</v>
       </c>
       <c r="D30" t="str">
-        <v>FR et EN, sélection par campaign</v>
+        <v>Tendances audit timeline, pie charts conformity domains</v>
       </c>
       <c r="E30" t="str">
-        <v>P1</v>
+        <v>P3</v>
       </c>
       <c r="F30" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G30" t="str">
-        <v>REQ-032</v>
+        <v>REQ-027</v>
       </c>
       <c r="H30" t="str">
-        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
+        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
       </c>
       <c r="I30" t="str">
-        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
+        <v>MVP n'a pas graphiques, architecture prête pour.</v>
       </c>
     </row>
     <row r="31">
@@ -1288,10 +1288,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C31" t="str">
-        <v>Modèle Ollama configurable</v>
+        <v>Support multilingue</v>
       </c>
       <c r="D31" t="str">
-        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
+        <v>FR et EN, sélection par campaign</v>
       </c>
       <c r="E31" t="str">
         <v>P1</v>
@@ -1300,13 +1300,13 @@
         <v>Complété</v>
       </c>
       <c r="G31" t="str">
-        <v>REQ-010</v>
+        <v>REQ-032</v>
       </c>
       <c r="H31" t="str">
-        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
+        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
       </c>
       <c r="I31" t="str">
-        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
+        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
       </c>
     </row>
     <row r="32">
@@ -1317,10 +1317,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C32" t="str">
-        <v>OpenAI optionnel</v>
+        <v>Modèle Ollama configurable</v>
       </c>
       <c r="D32" t="str">
-        <v>API key via .env, fallback auto Ollama si absent</v>
+        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
       </c>
       <c r="E32" t="str">
         <v>P1</v>
@@ -1329,13 +1329,13 @@
         <v>Complété</v>
       </c>
       <c r="G32" t="str">
-        <v>REQ-032</v>
+        <v>REQ-010</v>
       </c>
       <c r="H32" t="str">
-        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
+        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
       </c>
       <c r="I32" t="str">
-        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
+        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
       </c>
     </row>
     <row r="33">
@@ -1346,25 +1346,25 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C33" t="str">
-        <v>Thèmes personnalisés</v>
+        <v>OpenAI optionnel</v>
       </c>
       <c r="D33" t="str">
-        <v>Texte libre pour documents et questions</v>
+        <v>API key via .env, fallback auto Ollama si absent</v>
       </c>
       <c r="E33" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F33" t="str">
         <v>Complété</v>
       </c>
       <c r="G33" t="str">
-        <v>-</v>
+        <v>REQ-032</v>
       </c>
       <c r="H33" t="str">
-        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
+        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
       </c>
       <c r="I33" t="str">
-        <v>Permet flexibilité sur domaines audit custom</v>
+        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
       </c>
     </row>
     <row r="34">
@@ -1372,16 +1372,16 @@
         <v>REQ-033</v>
       </c>
       <c r="B34" t="str">
-        <v>Infrastructure &amp; Déploiement</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C34" t="str">
-        <v>Offline-first capability</v>
+        <v>Thèmes personnalisés</v>
       </c>
       <c r="D34" t="str">
-        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
+        <v>Texte libre pour documents et questions</v>
       </c>
       <c r="E34" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F34" t="str">
         <v>Complété</v>
@@ -1390,10 +1390,10 @@
         <v>-</v>
       </c>
       <c r="H34" t="str">
-        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
+        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
       </c>
       <c r="I34" t="str">
-        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
+        <v>Permet flexibilité sur domaines audit custom</v>
       </c>
     </row>
     <row r="35">
@@ -1404,25 +1404,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C35" t="str">
-        <v>Automation PowerShell</v>
+        <v>Offline-first capability</v>
       </c>
       <c r="D35" t="str">
-        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
+        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
       </c>
       <c r="E35" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F35" t="str">
         <v>Complété</v>
       </c>
       <c r="G35" t="str">
-        <v>REQ-030, REQ-033</v>
+        <v>-</v>
       </c>
       <c r="H35" t="str">
-        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
+        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
       </c>
       <c r="I35" t="str">
-        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
+        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
       </c>
     </row>
     <row r="36">
@@ -1433,25 +1433,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C36" t="str">
-        <v>Versionning Git &amp; GitHub</v>
+        <v>Automation PowerShell</v>
       </c>
       <c r="D36" t="str">
-        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
+        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
       </c>
       <c r="E36" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F36" t="str">
         <v>Complété</v>
       </c>
       <c r="G36" t="str">
-        <v>REQ-008, REQ-033</v>
+        <v>REQ-031, REQ-034</v>
       </c>
       <c r="H36" t="str">
-        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
+        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
       </c>
       <c r="I36" t="str">
-        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
+        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
       </c>
     </row>
     <row r="37">
@@ -1462,25 +1462,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C37" t="str">
-        <v>API REST Fastify</v>
+        <v>Versionning Git &amp; GitHub</v>
       </c>
       <c r="D37" t="str">
-        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
+        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
       </c>
       <c r="E37" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F37" t="str">
         <v>Complété</v>
       </c>
       <c r="G37" t="str">
-        <v>REQ-015, REQ-033</v>
+        <v>REQ-015, REQ-034</v>
       </c>
       <c r="H37" t="str">
-        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
+        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
       </c>
       <c r="I37" t="str">
-        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
+        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
       </c>
     </row>
     <row r="38">
@@ -1488,28 +1488,28 @@
         <v>REQ-037</v>
       </c>
       <c r="B38" t="str">
-        <v>UI/UX</v>
+        <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C38" t="str">
-        <v>UI React + TypeScript + Vite</v>
+        <v>API REST Fastify</v>
       </c>
       <c r="D38" t="str">
-        <v>Bundling optimisé, HMR dev mode</v>
+        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
       </c>
       <c r="E38" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F38" t="str">
         <v>Complété</v>
       </c>
       <c r="G38" t="str">
-        <v>REQ-019, REQ-033</v>
+        <v>REQ-016, REQ-034</v>
       </c>
       <c r="H38" t="str">
-        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
+        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
       </c>
       <c r="I38" t="str">
-        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
+        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
       </c>
     </row>
     <row r="39">
@@ -1520,10 +1520,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C39" t="str">
-        <v>Configuration IA section</v>
+        <v>UI React + TypeScript + Vite</v>
       </c>
       <c r="D39" t="str">
-        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
+        <v>Bundling optimisé, HMR dev mode</v>
       </c>
       <c r="E39" t="str">
         <v>P1</v>
@@ -1532,13 +1532,13 @@
         <v>Complété</v>
       </c>
       <c r="G39" t="str">
-        <v>REQ-026, REQ-033</v>
+        <v>REQ-020, REQ-034</v>
       </c>
       <c r="H39" t="str">
-        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
+        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
       </c>
       <c r="I39" t="str">
-        <v>UX: clair et accessible, pas scroll nécessaire</v>
+        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
       </c>
     </row>
     <row r="40">
@@ -1549,10 +1549,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C40" t="str">
-        <v>Génération questions section</v>
+        <v>Configuration IA section</v>
       </c>
       <c r="D40" t="str">
-        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
+        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
       </c>
       <c r="E40" t="str">
         <v>P1</v>
@@ -1561,13 +1561,13 @@
         <v>Complété</v>
       </c>
       <c r="G40" t="str">
-        <v>REQ-016, REQ-017, REQ-033</v>
+        <v>REQ-027, REQ-034</v>
       </c>
       <c r="H40" t="str">
-        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
+        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
       </c>
       <c r="I40" t="str">
-        <v>État uploadingReferential: loading indicator, disabled submit</v>
+        <v>UX: clair et accessible, pas scroll nécessaire</v>
       </c>
     </row>
     <row r="41">
@@ -1578,10 +1578,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C41" t="str">
-        <v>Référentiel documentaire section</v>
+        <v>Génération questions section</v>
       </c>
       <c r="D41" t="str">
-        <v>Ajouter document avec métas, liste affichée</v>
+        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
       </c>
       <c r="E41" t="str">
         <v>P1</v>
@@ -1590,13 +1590,13 @@
         <v>Complété</v>
       </c>
       <c r="G41" t="str">
-        <v>REQ-021, REQ-022, REQ-033</v>
+        <v>REQ-017, REQ-018, REQ-034</v>
       </c>
       <c r="H41" t="str">
-        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
+        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
       </c>
       <c r="I41" t="str">
-        <v>Erreurs affichées, success feedback, état documentS refresh</v>
+        <v>État uploadingReferential: loading indicator, disabled submit</v>
       </c>
     </row>
     <row r="42">
@@ -1607,10 +1607,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C42" t="str">
-        <v>Échelles métriques config</v>
+        <v>Référentiel documentaire section</v>
       </c>
       <c r="D42" t="str">
-        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
+        <v>Ajouter document avec métas, liste affichée</v>
       </c>
       <c r="E42" t="str">
         <v>P1</v>
@@ -1619,13 +1619,13 @@
         <v>Complété</v>
       </c>
       <c r="G42" t="str">
-        <v>REQ-023, REQ-024, REQ-033</v>
+        <v>REQ-022, REQ-023, REQ-034</v>
       </c>
       <c r="H42" t="str">
-        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
+        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
       </c>
       <c r="I42" t="str">
-        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
+        <v>Erreurs affichées, success feedback, état documentS refresh</v>
       </c>
     </row>
     <row r="43">
@@ -1636,10 +1636,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C43" t="str">
-        <v>Dashboard avec KPIs</v>
+        <v>Échelles métriques config</v>
       </c>
       <c r="D43" t="str">
-        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
+        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
       </c>
       <c r="E43" t="str">
         <v>P1</v>
@@ -1648,13 +1648,13 @@
         <v>Complété</v>
       </c>
       <c r="G43" t="str">
-        <v>-</v>
+        <v>REQ-024, REQ-025, REQ-034</v>
       </c>
       <c r="H43" t="str">
-        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
+        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
       </c>
       <c r="I43" t="str">
-        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
+        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
       </c>
     </row>
     <row r="44">
@@ -1665,10 +1665,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C44" t="str">
-        <v>Gestion entretiens</v>
+        <v>Dashboard avec KPIs</v>
       </c>
       <c r="D44" t="str">
-        <v>Interviewés, notes questions, scoring intégré</v>
+        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
       </c>
       <c r="E44" t="str">
         <v>P1</v>
@@ -1680,10 +1680,10 @@
         <v>-</v>
       </c>
       <c r="H44" t="str">
-        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
+        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
       </c>
       <c r="I44" t="str">
-        <v>Chaque note liée criterion + interviewee + score optionnel</v>
+        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
       </c>
     </row>
     <row r="45">
@@ -1694,10 +1694,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C45" t="str">
-        <v>Audit log viewer</v>
+        <v>Gestion entretiens</v>
       </c>
       <c r="D45" t="str">
-        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
+        <v>Interviewés, notes questions, scoring intégré</v>
       </c>
       <c r="E45" t="str">
         <v>P1</v>
@@ -1706,13 +1706,13 @@
         <v>Complété</v>
       </c>
       <c r="G45" t="str">
-        <v>REQ-043</v>
+        <v>-</v>
       </c>
       <c r="H45" t="str">
-        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
+        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
       </c>
       <c r="I45" t="str">
-        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
+        <v>Chaque note liée criterion + interviewee + score optionnel</v>
       </c>
     </row>
     <row r="46">
@@ -1723,25 +1723,25 @@
         <v>UI/UX</v>
       </c>
       <c r="C46" t="str">
-        <v>Export buttons</v>
+        <v>Audit log viewer</v>
       </c>
       <c r="D46" t="str">
-        <v>Boutons DOCX et CSV téléchargement</v>
+        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
       </c>
       <c r="E46" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F46" t="str">
         <v>Complété</v>
       </c>
       <c r="G46" t="str">
-        <v>-</v>
+        <v>REQ-044</v>
       </c>
       <c r="H46" t="str">
-        <v>POST /export-report et /export-csv. browser Blob download.</v>
+        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
       </c>
       <c r="I46" t="str">
-        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
       </c>
     </row>
     <row r="47">
@@ -1749,13 +1749,13 @@
         <v>REQ-046</v>
       </c>
       <c r="B47" t="str">
-        <v>Persévérance &amp; Facilité</v>
+        <v>UI/UX</v>
       </c>
       <c r="C47" t="str">
-        <v>Documentation complète</v>
+        <v>Export buttons</v>
       </c>
       <c r="D47" t="str">
-        <v>Setup guides, quickstart, git manual, examples références</v>
+        <v>Boutons DOCX et CSV téléchargement</v>
       </c>
       <c r="E47" t="str">
         <v>P2</v>
@@ -1767,13 +1767,13 @@
         <v>-</v>
       </c>
       <c r="H47" t="str">
-        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
+        <v>POST /export-report et /export-csv. browser Blob download.</v>
       </c>
       <c r="I47" t="str">
-        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
-      </c>
-    </row>
-    <row r="48" xml:space="preserve">
+        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" t="str">
         <v>REQ-047</v>
       </c>
@@ -1781,10 +1781,10 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C48" t="str">
-        <v>One-command installation</v>
+        <v>Documentation complète</v>
       </c>
       <c r="D48" t="str">
-        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+        <v>Setup guides, quickstart, git manual, examples références</v>
       </c>
       <c r="E48" t="str">
         <v>P2</v>
@@ -1795,12 +1795,11 @@
       <c r="G48" t="str">
         <v>-</v>
       </c>
-      <c r="H48" t="str" xml:space="preserve">
-        <v xml:space="preserve">.
- install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      <c r="H48" t="str">
+        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
       </c>
       <c r="I48" t="str">
-        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
       </c>
     </row>
     <row r="49" xml:space="preserve">
@@ -1811,41 +1810,42 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C49" t="str">
+        <v>One-command installation</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+      </c>
+      <c r="E49" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G49" t="str">
+        <v>-</v>
+      </c>
+      <c r="H49" t="str" xml:space="preserve">
+        <v xml:space="preserve">.
+ install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      </c>
+      <c r="I49" t="str">
+        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
+        <v>REQ-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C50" t="str">
         <v>One-command launch</v>
       </c>
-      <c r="D49" t="str" xml:space="preserve">
+      <c r="D50" t="str" xml:space="preserve">
         <v xml:space="preserve">npm run dev ou .
 start-rubis.ps1 pour lancer tout</v>
       </c>
-      <c r="E49" t="str">
-        <v>P2</v>
-      </c>
-      <c r="F49" t="str">
-        <v>Complété</v>
-      </c>
-      <c r="G49" t="str">
-        <v>-</v>
-      </c>
-      <c r="H49" t="str">
-        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
-      </c>
-      <c r="I49" t="str">
-        <v>Détection auto erreurs, log output lisible</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>REQ-049</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Persévérance &amp; Facilité</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Clear error messages</v>
-      </c>
-      <c r="D50" t="str">
-        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
-      </c>
       <c r="E50" t="str">
         <v>P2</v>
       </c>
@@ -1856,10 +1856,10 @@
         <v>-</v>
       </c>
       <c r="H50" t="str">
-        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
       </c>
       <c r="I50" t="str">
-        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+        <v>Détection auto erreurs, log output lisible</v>
       </c>
     </row>
     <row r="51">
@@ -1870,30 +1870,59 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C51" t="str">
-        <v>Roadmap versioning</v>
+        <v>Clear error messages</v>
       </c>
       <c r="D51" t="str">
-        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
       </c>
       <c r="E51" t="str">
         <v>P2</v>
       </c>
       <c r="F51" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G51" t="str">
         <v>-</v>
       </c>
       <c r="H51" t="str">
+        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>REQ-051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Roadmap versioning</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+      </c>
+      <c r="E52" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G52" t="str">
+        <v>-</v>
+      </c>
+      <c r="H52" t="str">
         <v>Créer ROADMAP.xlsx avec specs, priorités, statuts, directives implémentation.</v>
       </c>
-      <c r="I51" t="str">
+      <c r="I52" t="str">
         <v>À committé dans git, mis à jour post-MVP pour v2 features</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I52"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -546,7 +546,7 @@
         <v>Planifié</v>
       </c>
       <c r="G5" t="str">
-        <v>REQ-003, REQ-031</v>
+        <v>REQ-003, REQ-033</v>
       </c>
       <c r="H5" t="str">
         <v>Section admin protégée. CRUD référentiels: POST/PUT/DELETE /admin/referentials. Stockage db.data.referentials avec {id, name, category, description, isActive}. UI table éditable avec formulaire modal.</v>
@@ -604,7 +604,7 @@
         <v>Planifié</v>
       </c>
       <c r="G7" t="str">
-        <v>REQ-005, REQ-003, REQ-031</v>
+        <v>REQ-005, REQ-003, REQ-033</v>
       </c>
       <c r="H7" t="str">
         <v>POST /extract-criteria-from-referential. Multipart upload. Parser identifie structure (ex: ISO27001 A.5.1, A.5.2...). LLM extrait: {code, title, theme, description}. Batch insert criteria. UI: upload doc + bouton 'Extraire critères', preview avant validation.</v>
@@ -691,7 +691,7 @@
         <v>Complété</v>
       </c>
       <c r="G10" t="str">
-        <v>REQ-031</v>
+        <v>REQ-033</v>
       </c>
       <c r="H10" t="str">
         <v>generateQuestionsFromOpenAI() dans openai.ts. OpenAI client avec apiKey depuis .env</v>
@@ -720,7 +720,7 @@
         <v>Complété</v>
       </c>
       <c r="G11" t="str">
-        <v>REQ-031</v>
+        <v>REQ-033</v>
       </c>
       <c r="H11" t="str">
         <v>generateQuestionsFromOllama() fetch to localhost:11434/api/generate. checkOllamaAvailable() avec timeout 2s</v>
@@ -778,7 +778,7 @@
         <v>Planifié</v>
       </c>
       <c r="G13" t="str">
-        <v>REQ-004, REQ-009, REQ-010, REQ-032</v>
+        <v>REQ-004, REQ-009, REQ-010, REQ-033</v>
       </c>
       <c r="H13" t="str">
         <v>Section admin protégée. Config par phase: {phase: '1.1-Préparation'|'1.2-Entretiens'|'1.3-Scoring'|'1.4-Rapports', aiProvider: 'openai'|'ollama', ollamaModel?: 'mistral'|'gemma3:4b'}. Endpoints: GET/POST /admin/ai-config. Stockage db.data.aiConfig. UI: table éditable avec dropdown provider + model. Au runtime, generateQuestions() check phase active et route vers bon provider.</v>
@@ -807,7 +807,7 @@
         <v>Planifié</v>
       </c>
       <c r="G14" t="str">
-        <v>REQ-009, REQ-010, REQ-032</v>
+        <v>REQ-009, REQ-010, REQ-033</v>
       </c>
       <c r="H14" t="str">
         <v>Endpoint: POST /referential-documents/upload (multipart {file}). Service: extractDocumentMetadata(file) via LLM. Extract: {title, version, publicationDate, pageCount, sensitivity, authors, reviewers, approvers}. Stockage db.data.referentialDocuments: {id, campaignId, filename, uploadedAt, extractedMetadata, userVerifiedMetadata, fileSize, mimeType, storagePath}. UI: Upload form + table affichant docs avec métadonnées + bouton édition modal (formulaire avec fields pré-remplis) + bouton suppression. Validation: titre requis, autres optionnels. LLM prompt analyse: first/last page pour date/version, 'confidential'/'secret'/'public' keywords pour sensibilité, author/prepared/reviewed/approved/checked by patterns pour noms.</v>
@@ -821,28 +821,28 @@
         <v>REQ-014</v>
       </c>
       <c r="B15" t="str">
-        <v>IA &amp; Génération</v>
+        <v>Structuration données</v>
       </c>
       <c r="C15" t="str">
-        <v>Parsing référentiel multi-format</v>
+        <v>Métriques par défaut + détection IA cible</v>
       </c>
       <c r="D15" t="str">
-        <v>Support PDF et Excel avec extraction de texte</v>
+        <v>Métriques par défaut chargées au démarrage: types constats (Conforme/Remarque/Non-conformité mineure/majeure/NA), facilité d'exploitation, impact, complexité mise en œuvre, priorité, niveaux conformité/sécurité. IA détecte si système cible a ses propres métriques, les replace si trouvées. Utilisateur peut vérifier/modifier. Code couleur par métrique.</v>
       </c>
       <c r="E15" t="str">
         <v>P1</v>
       </c>
       <c r="F15" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G15" t="str">
-        <v>REQ-013</v>
+        <v>REQ-013, REQ-009, REQ-010, REQ-033</v>
       </c>
       <c r="H15" t="str">
-        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
+        <v>Charger data/metrics-config.json au démarrage. Fichier: auditConclusions, exploitationDifficulty, impact, implementationComplexity, implementationPriority, conformityLevel, securityLevel (avec color, colorCode). Endpoints: GET /metrics (récupère config active), POST /admin/metrics/detect (IA analyse docs/config système cible pour détecter métriques locales). Service detectTargetMetrics(systemConfig, referentialDocs) via LLM. Si métriques trouvées, stocker en db.data.targetMetrics avec {campaignId, detectedMetrics, confidence%, userApprovedMetrics, timestamp}. UI admin: affichage métriques par défaut vs détectées, toggle pour utiliser cibles ou défauts, bouton validation. Chaque métrique: label, description, code couleur (affichage cohérent).</v>
       </c>
       <c r="I15" t="str">
-        <v>Gère encodages UTF-8, caractères spéciaux</v>
+        <v>Garantit cohérence couleurs à travers l'app (rouge=critique, orange=majeur, jaune=important, vert=conforme). Stockage dual: defaut + cible permet audit trail et comparaison. LLM détecte patterns dans docs: 'criticité', 'sévérité', 'facilité', 'impact' etc.</v>
       </c>
     </row>
     <row r="16">
@@ -850,28 +850,28 @@
         <v>REQ-015</v>
       </c>
       <c r="B16" t="str">
-        <v>IA &amp; Génération</v>
+        <v>Structuration données</v>
       </c>
       <c r="C16" t="str">
-        <v>Prompt dynamique contextuel</v>
+        <v>Matrice calcul risque + code couleur</v>
       </c>
       <c r="D16" t="str">
-        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
+        <v>Matrice 2D Impact × Facilité d'exploitation pour calcul niveau risque. Code couleur cohérent (rouge=Critique, orange=Majeur, jaune=Important, blanc=Mineur). Affichage visuel et export. Intégration dans module admin pour vérification/ajustement.</v>
       </c>
       <c r="E16" t="str">
         <v>P1</v>
       </c>
       <c r="F16" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G16" t="str">
-        <v>REQ-013</v>
+        <v>REQ-014, REQ-033</v>
       </c>
       <c r="H16" t="str">
-        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
+        <v>Endpoint: GET /risk-matrix (retourne matrice + mapping couleurs). Structure: {rows: ['Mineur','Important','Majeur','Critique'], columns: ['Difficile','Élevée','Modérée','Facile'], matrix: [[result00...result33]], colorMapping: {Critique:#FF0000, Majeur:#FFA500, Important:#FFFF00, Mineur:#F5F5F5}}. Service calculateRisk(impact, difficulty) → risk level + color. DB: db.data.riskMatrix (config) pour permettre override custom. UI: affichage table React avec couleurs, hover show descriptions, click editable. Admin module: section 'Vérification matrice risque' avec table editable + override custom. Export PDF/DOCX: inclure matrice de risque calculée. Utilisation: chaque non-conformité/vulnérabilité mappée via (impact, difficulty) pour obtenir niveau risque visuel.</v>
       </c>
       <c r="I16" t="str">
-        <v>Zod validation sur count (1-10), language (fr/en)</v>
+        <v>Matrice reference PASSI/guide ANSSI. Couleurs immédiatement compréhensibles: évite ambiguïté. Export avec couleurs préservées. Stocke versions: par défaut + custom. Admin peut tester impact d'ajustements de matrice sur risques globaux.</v>
       </c>
     </row>
     <row r="17">
@@ -879,28 +879,28 @@
         <v>REQ-016</v>
       </c>
       <c r="B17" t="str">
-        <v>Structuration données</v>
+        <v>IA &amp; Génération</v>
       </c>
       <c r="C17" t="str">
-        <v>Modèle Document</v>
+        <v>Parsing référentiel multi-format</v>
       </c>
       <c r="D17" t="str">
-        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
+        <v>Support PDF et Excel avec extraction de texte</v>
       </c>
       <c r="E17" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F17" t="str">
         <v>Complété</v>
       </c>
       <c r="G17" t="str">
-        <v>REQ-002</v>
+        <v>REQ-013</v>
       </c>
       <c r="H17" t="str">
-        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
+        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
       </c>
       <c r="I17" t="str">
-        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
+        <v>Gère encodages UTF-8, caractères spéciaux</v>
       </c>
     </row>
     <row r="18">
@@ -908,28 +908,28 @@
         <v>REQ-017</v>
       </c>
       <c r="B18" t="str">
-        <v>Structuration données</v>
+        <v>IA &amp; Génération</v>
       </c>
       <c r="C18" t="str">
-        <v>Modèle Interviewé</v>
+        <v>Prompt dynamique contextuel</v>
       </c>
       <c r="D18" t="str">
-        <v>Nom complet, rôle, lié à campaign</v>
+        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
       </c>
       <c r="E18" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F18" t="str">
         <v>Complété</v>
       </c>
       <c r="G18" t="str">
-        <v>REQ-002</v>
+        <v>REQ-013</v>
       </c>
       <c r="H18" t="str">
-        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
+        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
       </c>
       <c r="I18" t="str">
-        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
+        <v>Zod validation sur count (1-10), language (fr/en)</v>
       </c>
     </row>
     <row r="19">
@@ -940,10 +940,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C19" t="str">
-        <v>Modèle Note d'entretien</v>
+        <v>Modèle Document</v>
       </c>
       <c r="D19" t="str">
-        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
+        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
       </c>
       <c r="E19" t="str">
         <v>P0</v>
@@ -952,13 +952,13 @@
         <v>Complété</v>
       </c>
       <c r="G19" t="str">
-        <v>REQ-005, REQ-017</v>
+        <v>REQ-002</v>
       </c>
       <c r="H19" t="str">
-        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
+        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
       </c>
       <c r="I19" t="str">
-        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
+        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
       </c>
     </row>
     <row r="20">
@@ -969,25 +969,25 @@
         <v>Structuration données</v>
       </c>
       <c r="C20" t="str">
-        <v>Matrice de conformité</v>
+        <v>Modèle Interviewé</v>
       </c>
       <c r="D20" t="str">
-        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
+        <v>Nom complet, rôle, lié à campaign</v>
       </c>
       <c r="E20" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F20" t="str">
         <v>Complété</v>
       </c>
       <c r="G20" t="str">
-        <v>REQ-018</v>
+        <v>REQ-002</v>
       </c>
       <c r="H20" t="str">
-        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
+        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
       </c>
       <c r="I20" t="str">
-        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
+        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
       </c>
     </row>
     <row r="21">
@@ -998,25 +998,25 @@
         <v>Structuration données</v>
       </c>
       <c r="C21" t="str">
-        <v>Configuration Métriques</v>
+        <v>Modèle Note d'entretien</v>
       </c>
       <c r="D21" t="str">
-        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
+        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
       </c>
       <c r="E21" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F21" t="str">
         <v>Complété</v>
       </c>
       <c r="G21" t="str">
-        <v>REQ-002</v>
+        <v>REQ-005, REQ-019</v>
       </c>
       <c r="H21" t="str">
-        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
+        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
       </c>
       <c r="I21" t="str">
-        <v>Format texte (ex: '1-5') pour flexibilité</v>
+        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
       </c>
     </row>
     <row r="22">
@@ -1024,13 +1024,13 @@
         <v>REQ-021</v>
       </c>
       <c r="B22" t="str">
-        <v>Audit &amp; Traçabilité</v>
+        <v>Structuration données</v>
       </c>
       <c r="C22" t="str">
-        <v>Audit Log complet</v>
+        <v>Matrice de conformité</v>
       </c>
       <c r="D22" t="str">
-        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
+        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
       </c>
       <c r="E22" t="str">
         <v>P1</v>
@@ -1039,13 +1039,13 @@
         <v>Complété</v>
       </c>
       <c r="G22" t="str">
-        <v>REQ-002, REQ-032</v>
+        <v>REQ-020</v>
       </c>
       <c r="H22" t="str">
-        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
+        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
       </c>
       <c r="I22" t="str">
-        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
+        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
       </c>
     </row>
     <row r="23">
@@ -1053,13 +1053,13 @@
         <v>REQ-022</v>
       </c>
       <c r="B23" t="str">
-        <v>Audit &amp; Traçabilité</v>
+        <v>Structuration données</v>
       </c>
       <c r="C23" t="str">
-        <v>Filtrage logs par période</v>
+        <v>Configuration Métriques</v>
       </c>
       <c r="D23" t="str">
-        <v>Vue 7j, 30j, tout (by date range filter)</v>
+        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
       </c>
       <c r="E23" t="str">
         <v>P1</v>
@@ -1068,13 +1068,13 @@
         <v>Complété</v>
       </c>
       <c r="G23" t="str">
-        <v>REQ-021</v>
+        <v>REQ-002</v>
       </c>
       <c r="H23" t="str">
-        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
+        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
       </c>
       <c r="I23" t="str">
-        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
+        <v>Format texte (ex: '1-5') pour flexibilité</v>
       </c>
     </row>
     <row r="24">
@@ -1085,10 +1085,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C24" t="str">
-        <v>Filtrage logs par action</v>
+        <v>Audit Log complet</v>
       </c>
       <c r="D24" t="str">
-        <v>Filter sur type d'action (campaign.created, etc.)</v>
+        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
       </c>
       <c r="E24" t="str">
         <v>P1</v>
@@ -1097,13 +1097,13 @@
         <v>Complété</v>
       </c>
       <c r="G24" t="str">
-        <v>REQ-021</v>
+        <v>REQ-002, REQ-033</v>
       </c>
       <c r="H24" t="str">
-        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
+        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
       </c>
       <c r="I24" t="str">
-        <v>Enum actions découvertes dynamiquement from logs</v>
+        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
       </c>
     </row>
     <row r="25">
@@ -1111,28 +1111,28 @@
         <v>REQ-024</v>
       </c>
       <c r="B25" t="str">
-        <v>Rapports &amp; Exports</v>
+        <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C25" t="str">
-        <v>Export DOCX</v>
+        <v>Filtrage logs par période</v>
       </c>
       <c r="D25" t="str">
-        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
+        <v>Vue 7j, 30j, tout (by date range filter)</v>
       </c>
       <c r="E25" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F25" t="str">
         <v>Complété</v>
       </c>
       <c r="G25" t="str">
-        <v>REQ-007, REQ-019</v>
+        <v>REQ-023</v>
       </c>
       <c r="H25" t="str">
-        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
+        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
       </c>
       <c r="I25" t="str">
-        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
+        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
       </c>
     </row>
     <row r="26">
@@ -1140,28 +1140,28 @@
         <v>REQ-025</v>
       </c>
       <c r="B26" t="str">
-        <v>Rapports &amp; Exports</v>
+        <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C26" t="str">
-        <v>Export CSV</v>
+        <v>Filtrage logs par action</v>
       </c>
       <c r="D26" t="str">
-        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
+        <v>Filter sur type d'action (campaign.created, etc.)</v>
       </c>
       <c r="E26" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F26" t="str">
         <v>Complété</v>
       </c>
       <c r="G26" t="str">
-        <v>REQ-019, REQ-021</v>
+        <v>REQ-023</v>
       </c>
       <c r="H26" t="str">
-        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
+        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
       </c>
       <c r="I26" t="str">
-        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
+        <v>Enum actions découvertes dynamiquement from logs</v>
       </c>
     </row>
     <row r="27">
@@ -1172,10 +1172,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C27" t="str">
-        <v>Gestion des rapports</v>
+        <v>Export DOCX</v>
       </c>
       <c r="D27" t="str">
-        <v>Stocker rapports générés avec titre, date gen, version</v>
+        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
       </c>
       <c r="E27" t="str">
         <v>P2</v>
@@ -1184,13 +1184,13 @@
         <v>Complété</v>
       </c>
       <c r="G27" t="str">
-        <v>REQ-024, REQ-025</v>
+        <v>REQ-007, REQ-021</v>
       </c>
       <c r="H27" t="str">
-        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
+        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
       </c>
       <c r="I27" t="str">
-        <v>Récupérable dans UI, archivé pour traçabilité</v>
+        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
       </c>
     </row>
     <row r="28">
@@ -1198,28 +1198,28 @@
         <v>REQ-027</v>
       </c>
       <c r="B28" t="str">
-        <v>Dashboard &amp; Visualisation</v>
+        <v>Rapports &amp; Exports</v>
       </c>
       <c r="C28" t="str">
-        <v>KPIs essentiels</v>
+        <v>Export CSV</v>
       </c>
       <c r="D28" t="str">
-        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
+        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
       </c>
       <c r="E28" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F28" t="str">
         <v>Complété</v>
       </c>
       <c r="G28" t="str">
-        <v>REQ-016, REQ-017, REQ-018</v>
+        <v>REQ-021, REQ-023</v>
       </c>
       <c r="H28" t="str">
-        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
+        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
       </c>
       <c r="I28" t="str">
-        <v>Affiché en gros chiffres zone haute dashboard</v>
+        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
       </c>
     </row>
     <row r="29">
@@ -1227,13 +1227,13 @@
         <v>REQ-028</v>
       </c>
       <c r="B29" t="str">
-        <v>Dashboard &amp; Visualisation</v>
+        <v>Rapports &amp; Exports</v>
       </c>
       <c r="C29" t="str">
-        <v>Matrice de conformité interactive</v>
+        <v>Gestion des rapports</v>
       </c>
       <c r="D29" t="str">
-        <v>Tableau avec % conformité par criterion, tri/filtre</v>
+        <v>Stocker rapports générés avec titre, date gen, version</v>
       </c>
       <c r="E29" t="str">
         <v>P2</v>
@@ -1242,13 +1242,13 @@
         <v>Complété</v>
       </c>
       <c r="G29" t="str">
-        <v>REQ-019</v>
+        <v>REQ-026, REQ-027</v>
       </c>
       <c r="H29" t="str">
-        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
+        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
       </c>
       <c r="I29" t="str">
-        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
+        <v>Récupérable dans UI, archivé pour traçabilité</v>
       </c>
     </row>
     <row r="30">
@@ -1259,25 +1259,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C30" t="str">
-        <v>Graphiques optionnels (futur)</v>
+        <v>KPIs essentiels</v>
       </c>
       <c r="D30" t="str">
-        <v>Tendances audit timeline, pie charts conformity domains</v>
+        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
       </c>
       <c r="E30" t="str">
-        <v>P3</v>
+        <v>P1</v>
       </c>
       <c r="F30" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G30" t="str">
-        <v>REQ-027</v>
+        <v>REQ-018, REQ-019, REQ-020</v>
       </c>
       <c r="H30" t="str">
-        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
+        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
       </c>
       <c r="I30" t="str">
-        <v>MVP n'a pas graphiques, architecture prête pour.</v>
+        <v>Affiché en gros chiffres zone haute dashboard</v>
       </c>
     </row>
     <row r="31">
@@ -1285,28 +1285,28 @@
         <v>REQ-030</v>
       </c>
       <c r="B31" t="str">
-        <v>Configuration &amp; Flexibilité</v>
+        <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C31" t="str">
-        <v>Support multilingue</v>
+        <v>Matrice de conformité interactive</v>
       </c>
       <c r="D31" t="str">
-        <v>FR et EN, sélection par campaign</v>
+        <v>Tableau avec % conformité par criterion, tri/filtre</v>
       </c>
       <c r="E31" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F31" t="str">
         <v>Complété</v>
       </c>
       <c r="G31" t="str">
-        <v>REQ-032</v>
+        <v>REQ-021</v>
       </c>
       <c r="H31" t="str">
-        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
+        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
       </c>
       <c r="I31" t="str">
-        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
+        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
       </c>
     </row>
     <row r="32">
@@ -1314,28 +1314,28 @@
         <v>REQ-031</v>
       </c>
       <c r="B32" t="str">
-        <v>Configuration &amp; Flexibilité</v>
+        <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C32" t="str">
-        <v>Modèle Ollama configurable</v>
+        <v>Graphiques optionnels (futur)</v>
       </c>
       <c r="D32" t="str">
-        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
+        <v>Tendances audit timeline, pie charts conformity domains</v>
       </c>
       <c r="E32" t="str">
-        <v>P1</v>
+        <v>P3</v>
       </c>
       <c r="F32" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G32" t="str">
-        <v>REQ-010</v>
+        <v>REQ-029</v>
       </c>
       <c r="H32" t="str">
-        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
+        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
       </c>
       <c r="I32" t="str">
-        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
+        <v>MVP n'a pas graphiques, architecture prête pour.</v>
       </c>
     </row>
     <row r="33">
@@ -1346,10 +1346,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C33" t="str">
-        <v>OpenAI optionnel</v>
+        <v>Support multilingue</v>
       </c>
       <c r="D33" t="str">
-        <v>API key via .env, fallback auto Ollama si absent</v>
+        <v>FR et EN, sélection par campaign</v>
       </c>
       <c r="E33" t="str">
         <v>P1</v>
@@ -1358,13 +1358,13 @@
         <v>Complété</v>
       </c>
       <c r="G33" t="str">
-        <v>REQ-032</v>
+        <v>REQ-033</v>
       </c>
       <c r="H33" t="str">
-        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
+        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
       </c>
       <c r="I33" t="str">
-        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
+        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
       </c>
     </row>
     <row r="34">
@@ -1375,25 +1375,25 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C34" t="str">
-        <v>Thèmes personnalisés</v>
+        <v>Modèle Ollama configurable</v>
       </c>
       <c r="D34" t="str">
-        <v>Texte libre pour documents et questions</v>
+        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
       </c>
       <c r="E34" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F34" t="str">
         <v>Complété</v>
       </c>
       <c r="G34" t="str">
-        <v>-</v>
+        <v>REQ-010</v>
       </c>
       <c r="H34" t="str">
-        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
+        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
       </c>
       <c r="I34" t="str">
-        <v>Permet flexibilité sur domaines audit custom</v>
+        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
       </c>
     </row>
     <row r="35">
@@ -1401,13 +1401,13 @@
         <v>REQ-034</v>
       </c>
       <c r="B35" t="str">
-        <v>Infrastructure &amp; Déploiement</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C35" t="str">
-        <v>Offline-first capability</v>
+        <v>OpenAI optionnel</v>
       </c>
       <c r="D35" t="str">
-        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
+        <v>API key via .env, fallback auto Ollama si absent</v>
       </c>
       <c r="E35" t="str">
         <v>P1</v>
@@ -1416,13 +1416,13 @@
         <v>Complété</v>
       </c>
       <c r="G35" t="str">
-        <v>-</v>
+        <v>REQ-033</v>
       </c>
       <c r="H35" t="str">
-        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
+        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
       </c>
       <c r="I35" t="str">
-        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
+        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
       </c>
     </row>
     <row r="36">
@@ -1430,13 +1430,13 @@
         <v>REQ-035</v>
       </c>
       <c r="B36" t="str">
-        <v>Infrastructure &amp; Déploiement</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C36" t="str">
-        <v>Automation PowerShell</v>
+        <v>Thèmes personnalisés</v>
       </c>
       <c r="D36" t="str">
-        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
+        <v>Texte libre pour documents et questions</v>
       </c>
       <c r="E36" t="str">
         <v>P2</v>
@@ -1445,13 +1445,13 @@
         <v>Complété</v>
       </c>
       <c r="G36" t="str">
-        <v>REQ-031, REQ-034</v>
+        <v>-</v>
       </c>
       <c r="H36" t="str">
-        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
+        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
       </c>
       <c r="I36" t="str">
-        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
+        <v>Permet flexibilité sur domaines audit custom</v>
       </c>
     </row>
     <row r="37">
@@ -1462,10 +1462,10 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C37" t="str">
-        <v>Versionning Git &amp; GitHub</v>
+        <v>Offline-first capability</v>
       </c>
       <c r="D37" t="str">
-        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
+        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
       </c>
       <c r="E37" t="str">
         <v>P1</v>
@@ -1474,13 +1474,13 @@
         <v>Complété</v>
       </c>
       <c r="G37" t="str">
-        <v>REQ-015, REQ-034</v>
+        <v>-</v>
       </c>
       <c r="H37" t="str">
-        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
+        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
       </c>
       <c r="I37" t="str">
-        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
+        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
       </c>
     </row>
     <row r="38">
@@ -1491,25 +1491,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C38" t="str">
-        <v>API REST Fastify</v>
+        <v>Automation PowerShell</v>
       </c>
       <c r="D38" t="str">
-        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
+        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
       </c>
       <c r="E38" t="str">
-        <v>P0</v>
+        <v>P2</v>
       </c>
       <c r="F38" t="str">
         <v>Complété</v>
       </c>
       <c r="G38" t="str">
-        <v>REQ-016, REQ-034</v>
+        <v>REQ-033, REQ-036</v>
       </c>
       <c r="H38" t="str">
-        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
+        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
       </c>
       <c r="I38" t="str">
-        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
+        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
       </c>
     </row>
     <row r="39">
@@ -1517,13 +1517,13 @@
         <v>REQ-038</v>
       </c>
       <c r="B39" t="str">
-        <v>UI/UX</v>
+        <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C39" t="str">
-        <v>UI React + TypeScript + Vite</v>
+        <v>Versionning Git &amp; GitHub</v>
       </c>
       <c r="D39" t="str">
-        <v>Bundling optimisé, HMR dev mode</v>
+        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
       </c>
       <c r="E39" t="str">
         <v>P1</v>
@@ -1532,13 +1532,13 @@
         <v>Complété</v>
       </c>
       <c r="G39" t="str">
-        <v>REQ-020, REQ-034</v>
+        <v>REQ-017, REQ-036</v>
       </c>
       <c r="H39" t="str">
-        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
+        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
       </c>
       <c r="I39" t="str">
-        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
+        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
       </c>
     </row>
     <row r="40">
@@ -1546,28 +1546,28 @@
         <v>REQ-039</v>
       </c>
       <c r="B40" t="str">
-        <v>UI/UX</v>
+        <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C40" t="str">
-        <v>Configuration IA section</v>
+        <v>API REST Fastify</v>
       </c>
       <c r="D40" t="str">
-        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
+        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
       </c>
       <c r="E40" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F40" t="str">
         <v>Complété</v>
       </c>
       <c r="G40" t="str">
-        <v>REQ-027, REQ-034</v>
+        <v>REQ-018, REQ-036</v>
       </c>
       <c r="H40" t="str">
-        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
+        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
       </c>
       <c r="I40" t="str">
-        <v>UX: clair et accessible, pas scroll nécessaire</v>
+        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
       </c>
     </row>
     <row r="41">
@@ -1578,10 +1578,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C41" t="str">
-        <v>Génération questions section</v>
+        <v>UI React + TypeScript + Vite</v>
       </c>
       <c r="D41" t="str">
-        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
+        <v>Bundling optimisé, HMR dev mode</v>
       </c>
       <c r="E41" t="str">
         <v>P1</v>
@@ -1590,13 +1590,13 @@
         <v>Complété</v>
       </c>
       <c r="G41" t="str">
-        <v>REQ-017, REQ-018, REQ-034</v>
+        <v>REQ-022, REQ-036</v>
       </c>
       <c r="H41" t="str">
-        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
+        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
       </c>
       <c r="I41" t="str">
-        <v>État uploadingReferential: loading indicator, disabled submit</v>
+        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
       </c>
     </row>
     <row r="42">
@@ -1607,10 +1607,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C42" t="str">
-        <v>Référentiel documentaire section</v>
+        <v>Configuration IA section</v>
       </c>
       <c r="D42" t="str">
-        <v>Ajouter document avec métas, liste affichée</v>
+        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
       </c>
       <c r="E42" t="str">
         <v>P1</v>
@@ -1619,13 +1619,13 @@
         <v>Complété</v>
       </c>
       <c r="G42" t="str">
-        <v>REQ-022, REQ-023, REQ-034</v>
+        <v>REQ-029, REQ-036</v>
       </c>
       <c r="H42" t="str">
-        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
+        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
       </c>
       <c r="I42" t="str">
-        <v>Erreurs affichées, success feedback, état documentS refresh</v>
+        <v>UX: clair et accessible, pas scroll nécessaire</v>
       </c>
     </row>
     <row r="43">
@@ -1636,10 +1636,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C43" t="str">
-        <v>Échelles métriques config</v>
+        <v>Génération questions section</v>
       </c>
       <c r="D43" t="str">
-        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
+        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
       </c>
       <c r="E43" t="str">
         <v>P1</v>
@@ -1648,13 +1648,13 @@
         <v>Complété</v>
       </c>
       <c r="G43" t="str">
-        <v>REQ-024, REQ-025, REQ-034</v>
+        <v>REQ-019, REQ-020, REQ-036</v>
       </c>
       <c r="H43" t="str">
-        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
+        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
       </c>
       <c r="I43" t="str">
-        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
+        <v>État uploadingReferential: loading indicator, disabled submit</v>
       </c>
     </row>
     <row r="44">
@@ -1665,10 +1665,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C44" t="str">
-        <v>Dashboard avec KPIs</v>
+        <v>Référentiel documentaire section</v>
       </c>
       <c r="D44" t="str">
-        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
+        <v>Ajouter document avec métas, liste affichée</v>
       </c>
       <c r="E44" t="str">
         <v>P1</v>
@@ -1677,13 +1677,13 @@
         <v>Complété</v>
       </c>
       <c r="G44" t="str">
-        <v>-</v>
+        <v>REQ-024, REQ-025, REQ-036</v>
       </c>
       <c r="H44" t="str">
-        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
+        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
       </c>
       <c r="I44" t="str">
-        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
+        <v>Erreurs affichées, success feedback, état documentS refresh</v>
       </c>
     </row>
     <row r="45">
@@ -1694,10 +1694,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C45" t="str">
-        <v>Gestion entretiens</v>
+        <v>Échelles métriques config</v>
       </c>
       <c r="D45" t="str">
-        <v>Interviewés, notes questions, scoring intégré</v>
+        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
       </c>
       <c r="E45" t="str">
         <v>P1</v>
@@ -1706,13 +1706,13 @@
         <v>Complété</v>
       </c>
       <c r="G45" t="str">
-        <v>-</v>
+        <v>REQ-026, REQ-027, REQ-036</v>
       </c>
       <c r="H45" t="str">
-        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
+        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
       </c>
       <c r="I45" t="str">
-        <v>Chaque note liée criterion + interviewee + score optionnel</v>
+        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
       </c>
     </row>
     <row r="46">
@@ -1723,10 +1723,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C46" t="str">
-        <v>Audit log viewer</v>
+        <v>Dashboard avec KPIs</v>
       </c>
       <c r="D46" t="str">
-        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
+        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
       </c>
       <c r="E46" t="str">
         <v>P1</v>
@@ -1735,13 +1735,13 @@
         <v>Complété</v>
       </c>
       <c r="G46" t="str">
-        <v>REQ-044</v>
+        <v>-</v>
       </c>
       <c r="H46" t="str">
-        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
+        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
       </c>
       <c r="I46" t="str">
-        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
+        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
       </c>
     </row>
     <row r="47">
@@ -1752,13 +1752,13 @@
         <v>UI/UX</v>
       </c>
       <c r="C47" t="str">
-        <v>Export buttons</v>
+        <v>Gestion entretiens</v>
       </c>
       <c r="D47" t="str">
-        <v>Boutons DOCX et CSV téléchargement</v>
+        <v>Interviewés, notes questions, scoring intégré</v>
       </c>
       <c r="E47" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F47" t="str">
         <v>Complété</v>
@@ -1767,10 +1767,10 @@
         <v>-</v>
       </c>
       <c r="H47" t="str">
-        <v>POST /export-report et /export-csv. browser Blob download.</v>
+        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
       </c>
       <c r="I47" t="str">
-        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+        <v>Chaque note liée criterion + interviewee + score optionnel</v>
       </c>
     </row>
     <row r="48">
@@ -1778,42 +1778,42 @@
         <v>REQ-047</v>
       </c>
       <c r="B48" t="str">
-        <v>Persévérance &amp; Facilité</v>
+        <v>UI/UX</v>
       </c>
       <c r="C48" t="str">
-        <v>Documentation complète</v>
+        <v>Audit log viewer</v>
       </c>
       <c r="D48" t="str">
-        <v>Setup guides, quickstart, git manual, examples références</v>
+        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
       </c>
       <c r="E48" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F48" t="str">
         <v>Complété</v>
       </c>
       <c r="G48" t="str">
-        <v>-</v>
+        <v>REQ-046</v>
       </c>
       <c r="H48" t="str">
-        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
+        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
       </c>
       <c r="I48" t="str">
-        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
-      </c>
-    </row>
-    <row r="49" xml:space="preserve">
+        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" t="str">
         <v>REQ-048</v>
       </c>
       <c r="B49" t="str">
-        <v>Persévérance &amp; Facilité</v>
+        <v>UI/UX</v>
       </c>
       <c r="C49" t="str">
-        <v>One-command installation</v>
+        <v>Export buttons</v>
       </c>
       <c r="D49" t="str">
-        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+        <v>Boutons DOCX et CSV téléchargement</v>
       </c>
       <c r="E49" t="str">
         <v>P2</v>
@@ -1824,105 +1824,163 @@
       <c r="G49" t="str">
         <v>-</v>
       </c>
-      <c r="H49" t="str" xml:space="preserve">
+      <c r="H49" t="str">
+        <v>POST /export-report et /export-csv. browser Blob download.</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>REQ-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Documentation complète</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Setup guides, quickstart, git manual, examples références</v>
+      </c>
+      <c r="E50" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G50" t="str">
+        <v>-</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
+      </c>
+      <c r="I50" t="str">
+        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
+        <v>REQ-050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C51" t="str">
+        <v>One-command installation</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+      </c>
+      <c r="E51" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G51" t="str">
+        <v>-</v>
+      </c>
+      <c r="H51" t="str" xml:space="preserve">
         <v xml:space="preserve">.
  install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
       </c>
-      <c r="I49" t="str">
+      <c r="I51" t="str">
         <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
       </c>
     </row>
-    <row r="50" xml:space="preserve">
-      <c r="A50" t="str">
-        <v>REQ-049</v>
-      </c>
-      <c r="B50" t="str">
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
+        <v>REQ-051</v>
+      </c>
+      <c r="B52" t="str">
         <v>Persévérance &amp; Facilité</v>
       </c>
-      <c r="C50" t="str">
+      <c r="C52" t="str">
         <v>One-command launch</v>
       </c>
-      <c r="D50" t="str" xml:space="preserve">
+      <c r="D52" t="str" xml:space="preserve">
         <v xml:space="preserve">npm run dev ou .
 start-rubis.ps1 pour lancer tout</v>
       </c>
-      <c r="E50" t="str">
-        <v>P2</v>
-      </c>
-      <c r="F50" t="str">
-        <v>Complété</v>
-      </c>
-      <c r="G50" t="str">
-        <v>-</v>
-      </c>
-      <c r="H50" t="str">
-        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
-      </c>
-      <c r="I50" t="str">
-        <v>Détection auto erreurs, log output lisible</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>REQ-050</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Persévérance &amp; Facilité</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Clear error messages</v>
-      </c>
-      <c r="D51" t="str">
-        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
-      </c>
-      <c r="E51" t="str">
-        <v>P2</v>
-      </c>
-      <c r="F51" t="str">
-        <v>Complété</v>
-      </c>
-      <c r="G51" t="str">
-        <v>-</v>
-      </c>
-      <c r="H51" t="str">
-        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
-      </c>
-      <c r="I51" t="str">
-        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>REQ-051</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Persévérance &amp; Facilité</v>
-      </c>
-      <c r="C52" t="str">
-        <v>Roadmap versioning</v>
-      </c>
-      <c r="D52" t="str">
-        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
-      </c>
       <c r="E52" t="str">
         <v>P2</v>
       </c>
       <c r="F52" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G52" t="str">
         <v>-</v>
       </c>
       <c r="H52" t="str">
+        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Détection auto erreurs, log output lisible</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>REQ-052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Clear error messages</v>
+      </c>
+      <c r="D53" t="str">
+        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
+      </c>
+      <c r="E53" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G53" t="str">
+        <v>-</v>
+      </c>
+      <c r="H53" t="str">
+        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>REQ-053</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Roadmap versioning</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+      </c>
+      <c r="E54" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G54" t="str">
+        <v>-</v>
+      </c>
+      <c r="H54" t="str">
         <v>Créer ROADMAP.xlsx avec specs, priorités, statuts, directives implémentation.</v>
       </c>
-      <c r="I52" t="str">
+      <c r="I54" t="str">
         <v>À committé dans git, mis à jour post-MVP pour v2 features</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -879,28 +879,28 @@
         <v>REQ-016</v>
       </c>
       <c r="B17" t="str">
-        <v>IA &amp; Génération</v>
+        <v>Structuration données</v>
       </c>
       <c r="C17" t="str">
-        <v>Parsing référentiel multi-format</v>
+        <v>Fiche interviewés enrichie format contact + association critères</v>
       </c>
       <c r="D17" t="str">
-        <v>Support PDF et Excel avec extraction de texte</v>
+        <v>Format contact style Outlook avec champs structurés (email, téléphone, adresse, département, dates). Possibilité d'associer l'interviewé à certains critères d'audit spécifiques. Affichage type contact card. Module admin pour gestion et liaison critères.</v>
       </c>
       <c r="E17" t="str">
         <v>P1</v>
       </c>
       <c r="F17" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G17" t="str">
-        <v>REQ-013</v>
+        <v>REQ-005, REQ-033</v>
       </c>
       <c r="H17" t="str">
-        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
+        <v>Enrichir db.data.interviewees: {id, campaignId, fullName, role, email, phone, address, city, zipcode, department, company, lastContactDate, linkedCriteria: [criterionIds], notes, photo?: base64}. Endpoints: POST /interviewees (création contact), PUT /interviewees/:id (mise à jour), GET /interviewees/:id (affichage fiche), DELETE /interviewees/:id, POST /interviewees/:id/link-criteria (lier critères). UI: Contact card display (avatar placeholder, infos structurées, statut contact). Form de création/édition: champs formulaire + dropdown multi-select pour associer critères audit. Table des interviewés avec aperçu, recherche par nom/role/département. Admin module: gestion complète + aperçu graphique liaison critères par interviewé.</v>
       </c>
       <c r="I17" t="str">
-        <v>Gère encodages UTF-8, caractères spéciaux</v>
+        <v>Facilite organisation interviews par domaine/critère. Contact card style Outlook améliore UX. Association critères permet allocation ressources et suivi entretiens. Stockage linkedCriteria permet filtres et reporting (ex: 'Quels interviewés pour critère A.5.1?').</v>
       </c>
     </row>
     <row r="18">
@@ -911,10 +911,10 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C18" t="str">
-        <v>Prompt dynamique contextuel</v>
+        <v>Parsing référentiel multi-format</v>
       </c>
       <c r="D18" t="str">
-        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
+        <v>Support PDF et Excel avec extraction de texte</v>
       </c>
       <c r="E18" t="str">
         <v>P1</v>
@@ -926,10 +926,10 @@
         <v>REQ-013</v>
       </c>
       <c r="H18" t="str">
-        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
+        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
       </c>
       <c r="I18" t="str">
-        <v>Zod validation sur count (1-10), language (fr/en)</v>
+        <v>Gère encodages UTF-8, caractères spéciaux</v>
       </c>
     </row>
     <row r="19">
@@ -937,28 +937,28 @@
         <v>REQ-018</v>
       </c>
       <c r="B19" t="str">
-        <v>Structuration données</v>
+        <v>IA &amp; Génération</v>
       </c>
       <c r="C19" t="str">
-        <v>Modèle Document</v>
+        <v>Prompt dynamique contextuel</v>
       </c>
       <c r="D19" t="str">
-        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
+        <v>Criterion code/title, langue FR/EN, nombre questions 1-10</v>
       </c>
       <c r="E19" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F19" t="str">
         <v>Complété</v>
       </c>
       <c r="G19" t="str">
-        <v>REQ-002</v>
+        <v>REQ-013</v>
       </c>
       <c r="H19" t="str">
-        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
+        <v>openai.ts generateQuestionsFromReferential() construit userPrompt avec contexte injection</v>
       </c>
       <c r="I19" t="str">
-        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
+        <v>Zod validation sur count (1-10), language (fr/en)</v>
       </c>
     </row>
     <row r="20">
@@ -969,10 +969,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C20" t="str">
-        <v>Modèle Interviewé</v>
+        <v>Modèle Document</v>
       </c>
       <c r="D20" t="str">
-        <v>Nom complet, rôle, lié à campaign</v>
+        <v>Nom, thématique, version, date, sensibilité, résumé avec versioning</v>
       </c>
       <c r="E20" t="str">
         <v>P0</v>
@@ -984,10 +984,10 @@
         <v>REQ-002</v>
       </c>
       <c r="H20" t="str">
-        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
+        <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
       </c>
       <c r="I20" t="str">
-        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
+        <v>Sensitivity enum: Public/Interne/Sensible/Confidentiel</v>
       </c>
     </row>
     <row r="21">
@@ -998,10 +998,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C21" t="str">
-        <v>Modèle Note d'entretien</v>
+        <v>Modèle Interviewé</v>
       </c>
       <c r="D21" t="str">
-        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
+        <v>Nom complet, rôle, lié à campaign</v>
       </c>
       <c r="E21" t="str">
         <v>P0</v>
@@ -1010,13 +1010,13 @@
         <v>Complété</v>
       </c>
       <c r="G21" t="str">
-        <v>REQ-005, REQ-019</v>
+        <v>REQ-002</v>
       </c>
       <c r="H21" t="str">
-        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
+        <v>db.data.interviewees: {id, campaignId, fullName, role}</v>
       </c>
       <c r="I21" t="str">
-        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
+        <v>Rôle texte libre (ex: RSSI, Directeur IT, etc.)</v>
       </c>
     </row>
     <row r="22">
@@ -1027,25 +1027,25 @@
         <v>Structuration données</v>
       </c>
       <c r="C22" t="str">
-        <v>Matrice de conformité</v>
+        <v>Modèle Note d'entretien</v>
       </c>
       <c r="D22" t="str">
-        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
+        <v>Contenu libre + scoring, lié à criterion et interviewé</v>
       </c>
       <c r="E22" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F22" t="str">
         <v>Complété</v>
       </c>
       <c r="G22" t="str">
-        <v>REQ-020</v>
+        <v>REQ-005, REQ-020</v>
       </c>
       <c r="H22" t="str">
-        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
+        <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
       </c>
       <c r="I22" t="str">
-        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
+        <v>Score: 0-5 ou texte (conformité). Timestamp auto.</v>
       </c>
     </row>
     <row r="23">
@@ -1056,10 +1056,10 @@
         <v>Structuration données</v>
       </c>
       <c r="C23" t="str">
-        <v>Configuration Métriques</v>
+        <v>Matrice de conformité</v>
       </c>
       <c r="D23" t="str">
-        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
+        <v>Criterion code/title/theme, moyenne pondérée, questions répondues vs total</v>
       </c>
       <c r="E23" t="str">
         <v>P1</v>
@@ -1068,13 +1068,13 @@
         <v>Complété</v>
       </c>
       <c r="G23" t="str">
-        <v>REQ-002</v>
+        <v>REQ-021</v>
       </c>
       <c r="H23" t="str">
-        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
+        <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
       </c>
       <c r="I23" t="str">
-        <v>Format texte (ex: '1-5') pour flexibilité</v>
+        <v>Poids configurable (voir Métriques). Moyenne excluant null/undefined.</v>
       </c>
     </row>
     <row r="24">
@@ -1082,13 +1082,13 @@
         <v>REQ-023</v>
       </c>
       <c r="B24" t="str">
-        <v>Audit &amp; Traçabilité</v>
+        <v>Structuration données</v>
       </c>
       <c r="C24" t="str">
-        <v>Audit Log complet</v>
+        <v>Configuration Métriques</v>
       </c>
       <c r="D24" t="str">
-        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
+        <v>Échelles personnalisables: Confidentialité, Intégrité, Disponibilité, Preuve</v>
       </c>
       <c r="E24" t="str">
         <v>P1</v>
@@ -1097,13 +1097,13 @@
         <v>Complété</v>
       </c>
       <c r="G24" t="str">
-        <v>REQ-002, REQ-033</v>
+        <v>REQ-002</v>
       </c>
       <c r="H24" t="str">
-        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
+        <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
       </c>
       <c r="I24" t="str">
-        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
+        <v>Format texte (ex: '1-5') pour flexibilité</v>
       </c>
     </row>
     <row r="25">
@@ -1114,10 +1114,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C25" t="str">
-        <v>Filtrage logs par période</v>
+        <v>Audit Log complet</v>
       </c>
       <c r="D25" t="str">
-        <v>Vue 7j, 30j, tout (by date range filter)</v>
+        <v>Action, timestamp, détails, lié à campagne, stocker tous mouvements</v>
       </c>
       <c r="E25" t="str">
         <v>P1</v>
@@ -1126,13 +1126,13 @@
         <v>Complété</v>
       </c>
       <c r="G25" t="str">
-        <v>REQ-023</v>
+        <v>REQ-002, REQ-033</v>
       </c>
       <c r="H25" t="str">
-        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
+        <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
       </c>
       <c r="I25" t="str">
-        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
+        <v>Toutes mutations app tracées: campaign.created, criterion.created, etc.</v>
       </c>
     </row>
     <row r="26">
@@ -1143,10 +1143,10 @@
         <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C26" t="str">
-        <v>Filtrage logs par action</v>
+        <v>Filtrage logs par période</v>
       </c>
       <c r="D26" t="str">
-        <v>Filter sur type d'action (campaign.created, etc.)</v>
+        <v>Vue 7j, 30j, tout (by date range filter)</v>
       </c>
       <c r="E26" t="str">
         <v>P1</v>
@@ -1155,13 +1155,13 @@
         <v>Complété</v>
       </c>
       <c r="G26" t="str">
-        <v>REQ-023</v>
+        <v>REQ-024</v>
       </c>
       <c r="H26" t="str">
-        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
+        <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
       </c>
       <c r="I26" t="str">
-        <v>Enum actions découvertes dynamiquement from logs</v>
+        <v>Filter UI: dropdown 3 options + affichage dynamique</v>
       </c>
     </row>
     <row r="27">
@@ -1169,28 +1169,28 @@
         <v>REQ-026</v>
       </c>
       <c r="B27" t="str">
-        <v>Rapports &amp; Exports</v>
+        <v>Audit &amp; Traçabilité</v>
       </c>
       <c r="C27" t="str">
-        <v>Export DOCX</v>
+        <v>Filtrage logs par action</v>
       </c>
       <c r="D27" t="str">
-        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
+        <v>Filter sur type d'action (campaign.created, etc.)</v>
       </c>
       <c r="E27" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F27" t="str">
         <v>Complété</v>
       </c>
       <c r="G27" t="str">
-        <v>REQ-007, REQ-021</v>
+        <v>REQ-024</v>
       </c>
       <c r="H27" t="str">
-        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
+        <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
       </c>
       <c r="I27" t="str">
-        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
+        <v>Enum actions découvertes dynamiquement from logs</v>
       </c>
     </row>
     <row r="28">
@@ -1201,10 +1201,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C28" t="str">
-        <v>Export CSV</v>
+        <v>Export DOCX</v>
       </c>
       <c r="D28" t="str">
-        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
+        <v>Générer .docx avec questions, réponses, scoring, détails audit</v>
       </c>
       <c r="E28" t="str">
         <v>P2</v>
@@ -1213,13 +1213,13 @@
         <v>Complété</v>
       </c>
       <c r="G28" t="str">
-        <v>REQ-021, REQ-023</v>
+        <v>REQ-007, REQ-022</v>
       </c>
       <c r="H28" t="str">
-        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
+        <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
       </c>
       <c r="I28" t="str">
-        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
+        <v>Téléchargement direct browser, nom: Rubis_Campaign_[date].docx</v>
       </c>
     </row>
     <row r="29">
@@ -1230,10 +1230,10 @@
         <v>Rapports &amp; Exports</v>
       </c>
       <c r="C29" t="str">
-        <v>Gestion des rapports</v>
+        <v>Export CSV</v>
       </c>
       <c r="D29" t="str">
-        <v>Stocker rapports générés avec titre, date gen, version</v>
+        <v>Audit logs + conformity matrix en CSV téléchargeable</v>
       </c>
       <c r="E29" t="str">
         <v>P2</v>
@@ -1242,13 +1242,13 @@
         <v>Complété</v>
       </c>
       <c r="G29" t="str">
-        <v>REQ-026, REQ-027</v>
+        <v>REQ-022, REQ-024</v>
       </c>
       <c r="H29" t="str">
-        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
+        <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
       </c>
       <c r="I29" t="str">
-        <v>Récupérable dans UI, archivé pour traçabilité</v>
+        <v>2 fichiers: audit_logs.csv + conformity_matrix.csv</v>
       </c>
     </row>
     <row r="30">
@@ -1256,28 +1256,28 @@
         <v>REQ-029</v>
       </c>
       <c r="B30" t="str">
-        <v>Dashboard &amp; Visualisation</v>
+        <v>Rapports &amp; Exports</v>
       </c>
       <c r="C30" t="str">
-        <v>KPIs essentiels</v>
+        <v>Gestion des rapports</v>
       </c>
       <c r="D30" t="str">
-        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
+        <v>Stocker rapports générés avec titre, date gen, version</v>
       </c>
       <c r="E30" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F30" t="str">
         <v>Complété</v>
       </c>
       <c r="G30" t="str">
-        <v>REQ-018, REQ-019, REQ-020</v>
+        <v>REQ-027, REQ-028</v>
       </c>
       <c r="H30" t="str">
-        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
+        <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
       </c>
       <c r="I30" t="str">
-        <v>Affiché en gros chiffres zone haute dashboard</v>
+        <v>Récupérable dans UI, archivé pour traçabilité</v>
       </c>
     </row>
     <row r="31">
@@ -1288,25 +1288,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C31" t="str">
-        <v>Matrice de conformité interactive</v>
+        <v>KPIs essentiels</v>
       </c>
       <c r="D31" t="str">
-        <v>Tableau avec % conformité par criterion, tri/filtre</v>
+        <v>Compteurs: documents, interviewés, notes, docs en attente, rapports, questions</v>
       </c>
       <c r="E31" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F31" t="str">
         <v>Complété</v>
       </c>
       <c r="G31" t="str">
-        <v>REQ-021</v>
+        <v>REQ-019, REQ-020, REQ-021</v>
       </c>
       <c r="H31" t="str">
-        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
+        <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
       </c>
       <c r="I31" t="str">
-        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
+        <v>Affiché en gros chiffres zone haute dashboard</v>
       </c>
     </row>
     <row r="32">
@@ -1317,25 +1317,25 @@
         <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C32" t="str">
-        <v>Graphiques optionnels (futur)</v>
+        <v>Matrice de conformité interactive</v>
       </c>
       <c r="D32" t="str">
-        <v>Tendances audit timeline, pie charts conformity domains</v>
+        <v>Tableau avec % conformité par criterion, tri/filtre</v>
       </c>
       <c r="E32" t="str">
-        <v>P3</v>
+        <v>P2</v>
       </c>
       <c r="F32" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G32" t="str">
-        <v>REQ-029</v>
+        <v>REQ-022</v>
       </c>
       <c r="H32" t="str">
-        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
+        <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
       </c>
       <c r="I32" t="str">
-        <v>MVP n'a pas graphiques, architecture prête pour.</v>
+        <v>Couleurs: rouge &lt;50%, orange 50-80%, vert &gt;80%</v>
       </c>
     </row>
     <row r="33">
@@ -1343,28 +1343,28 @@
         <v>REQ-032</v>
       </c>
       <c r="B33" t="str">
-        <v>Configuration &amp; Flexibilité</v>
+        <v>Dashboard &amp; Visualisation</v>
       </c>
       <c r="C33" t="str">
-        <v>Support multilingue</v>
+        <v>Graphiques optionnels (futur)</v>
       </c>
       <c r="D33" t="str">
-        <v>FR et EN, sélection par campaign</v>
+        <v>Tendances audit timeline, pie charts conformity domains</v>
       </c>
       <c r="E33" t="str">
-        <v>P1</v>
+        <v>P3</v>
       </c>
       <c r="F33" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G33" t="str">
-        <v>REQ-033</v>
+        <v>REQ-030</v>
       </c>
       <c r="H33" t="str">
-        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
+        <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
       </c>
       <c r="I33" t="str">
-        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
+        <v>MVP n'a pas graphiques, architecture prête pour.</v>
       </c>
     </row>
     <row r="34">
@@ -1375,10 +1375,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C34" t="str">
-        <v>Modèle Ollama configurable</v>
+        <v>Support multilingue</v>
       </c>
       <c r="D34" t="str">
-        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
+        <v>FR et EN, sélection par campaign</v>
       </c>
       <c r="E34" t="str">
         <v>P1</v>
@@ -1387,13 +1387,13 @@
         <v>Complété</v>
       </c>
       <c r="G34" t="str">
-        <v>REQ-010</v>
+        <v>REQ-033</v>
       </c>
       <c r="H34" t="str">
-        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
+        <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
       </c>
       <c r="I34" t="str">
-        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
+        <v>Prompts IA adaptent langue dynamiquement (français si campaign.language=fr)</v>
       </c>
     </row>
     <row r="35">
@@ -1404,10 +1404,10 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C35" t="str">
-        <v>OpenAI optionnel</v>
+        <v>Modèle Ollama configurable</v>
       </c>
       <c r="D35" t="str">
-        <v>API key via .env, fallback auto Ollama si absent</v>
+        <v>Switcher mistral ou gemma3:4b sans redémarrage</v>
       </c>
       <c r="E35" t="str">
         <v>P1</v>
@@ -1416,13 +1416,13 @@
         <v>Complété</v>
       </c>
       <c r="G35" t="str">
-        <v>REQ-033</v>
+        <v>REQ-010</v>
       </c>
       <c r="H35" t="str">
-        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
+        <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
       </c>
       <c r="I35" t="str">
-        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
+        <v>Persist pas en DB (runtime only). Config peut sauver .env si demandé.</v>
       </c>
     </row>
     <row r="36">
@@ -1433,25 +1433,25 @@
         <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C36" t="str">
-        <v>Thèmes personnalisés</v>
+        <v>OpenAI optionnel</v>
       </c>
       <c r="D36" t="str">
-        <v>Texte libre pour documents et questions</v>
+        <v>API key via .env, fallback auto Ollama si absent</v>
       </c>
       <c r="E36" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F36" t="str">
         <v>Complété</v>
       </c>
       <c r="G36" t="str">
-        <v>-</v>
+        <v>REQ-033</v>
       </c>
       <c r="H36" t="str">
-        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
+        <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
       </c>
       <c r="I36" t="str">
-        <v>Permet flexibilité sur domaines audit custom</v>
+        <v>generateQuestionsFromOpenAI() try-catch, log warn si clé manquante</v>
       </c>
     </row>
     <row r="37">
@@ -1459,16 +1459,16 @@
         <v>REQ-036</v>
       </c>
       <c r="B37" t="str">
-        <v>Infrastructure &amp; Déploiement</v>
+        <v>Configuration &amp; Flexibilité</v>
       </c>
       <c r="C37" t="str">
-        <v>Offline-first capability</v>
+        <v>Thèmes personnalisés</v>
       </c>
       <c r="D37" t="str">
-        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
+        <v>Texte libre pour documents et questions</v>
       </c>
       <c r="E37" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F37" t="str">
         <v>Complété</v>
@@ -1477,10 +1477,10 @@
         <v>-</v>
       </c>
       <c r="H37" t="str">
-        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
+        <v>document.theme et question.theme: string (no enum). UI input texte libre.</v>
       </c>
       <c r="I37" t="str">
-        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
+        <v>Permet flexibilité sur domaines audit custom</v>
       </c>
     </row>
     <row r="38">
@@ -1491,25 +1491,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C38" t="str">
-        <v>Automation PowerShell</v>
+        <v>Offline-first capability</v>
       </c>
       <c r="D38" t="str">
-        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
+        <v>Aucune dépendance cloud obligatoire, Ollama local suffisant</v>
       </c>
       <c r="E38" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F38" t="str">
         <v>Complété</v>
       </c>
       <c r="G38" t="str">
-        <v>REQ-033, REQ-036</v>
+        <v>-</v>
       </c>
       <c r="H38" t="str">
-        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
+        <v>Ollama localhost:11434 défaut. OpenAI optionnel. DB lowdb fichier local.</v>
       </c>
       <c r="I38" t="str">
-        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
+        <v>Testé sur HP EliteBook Ryzen 5 8540U, 15GB RAM, 138GB disk</v>
       </c>
     </row>
     <row r="39">
@@ -1520,25 +1520,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C39" t="str">
-        <v>Versionning Git &amp; GitHub</v>
+        <v>Automation PowerShell</v>
       </c>
       <c r="D39" t="str">
-        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
+        <v>Scripts install-ollama, start-rubis, compare-models pour non-techniques</v>
       </c>
       <c r="E39" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="F39" t="str">
         <v>Complété</v>
       </c>
       <c r="G39" t="str">
-        <v>REQ-017, REQ-036</v>
+        <v>REQ-034, REQ-037</v>
       </c>
       <c r="H39" t="str">
-        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
+        <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
       </c>
       <c r="I39" t="str">
-        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
+        <v>Chaque script &gt;=70 lines, logs détaillés, exit codes corrects</v>
       </c>
     </row>
     <row r="40">
@@ -1549,25 +1549,25 @@
         <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C40" t="str">
-        <v>API REST Fastify</v>
+        <v>Versionning Git &amp; GitHub</v>
       </c>
       <c r="D40" t="str">
-        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
+        <v>Repository github.com/emi5650/Rubis, SSH auth, 54 commits initiaux</v>
       </c>
       <c r="E40" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="F40" t="str">
         <v>Complété</v>
       </c>
       <c r="G40" t="str">
-        <v>REQ-018, REQ-036</v>
+        <v>REQ-018, REQ-037</v>
       </c>
       <c r="H40" t="str">
-        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
+        <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
       </c>
       <c r="I40" t="str">
-        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
+        <v>SSH key generé + configuré. Prêt pour CI/CD futur.</v>
       </c>
     </row>
     <row r="41">
@@ -1575,28 +1575,28 @@
         <v>REQ-040</v>
       </c>
       <c r="B41" t="str">
-        <v>UI/UX</v>
+        <v>Infrastructure &amp; Déploiement</v>
       </c>
       <c r="C41" t="str">
-        <v>UI React + TypeScript + Vite</v>
+        <v>API REST Fastify</v>
       </c>
       <c r="D41" t="str">
-        <v>Bundling optimisé, HMR dev mode</v>
+        <v>Framework web API 5.x, CORS enabled, multipart upload 50MB limit</v>
       </c>
       <c r="E41" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="F41" t="str">
         <v>Complété</v>
       </c>
       <c r="G41" t="str">
-        <v>REQ-022, REQ-036</v>
+        <v>REQ-019, REQ-037</v>
       </c>
       <c r="H41" t="str">
-        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
+        <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
       </c>
       <c r="I41" t="str">
-        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
+        <v>Écoute 0.0.0.0:4000 pour accès réseau local</v>
       </c>
     </row>
     <row r="42">
@@ -1607,10 +1607,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C42" t="str">
-        <v>Configuration IA section</v>
+        <v>UI React + TypeScript + Vite</v>
       </c>
       <c r="D42" t="str">
-        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
+        <v>Bundling optimisé, HMR dev mode</v>
       </c>
       <c r="E42" t="str">
         <v>P1</v>
@@ -1619,13 +1619,13 @@
         <v>Complété</v>
       </c>
       <c r="G42" t="str">
-        <v>REQ-029, REQ-036</v>
+        <v>REQ-023, REQ-037</v>
       </c>
       <c r="H42" t="str">
-        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
+        <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
       </c>
       <c r="I42" t="str">
-        <v>UX: clair et accessible, pas scroll nécessaire</v>
+        <v>Production build: 229KB JS gzip, 1.17KB CSS gzip</v>
       </c>
     </row>
     <row r="43">
@@ -1636,10 +1636,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C43" t="str">
-        <v>Génération questions section</v>
+        <v>Configuration IA section</v>
       </c>
       <c r="D43" t="str">
-        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
+        <v>Boutons model switching mistral/gemma3:4b avec statut visuel</v>
       </c>
       <c r="E43" t="str">
         <v>P1</v>
@@ -1648,13 +1648,13 @@
         <v>Complété</v>
       </c>
       <c r="G43" t="str">
-        <v>REQ-019, REQ-020, REQ-036</v>
+        <v>REQ-030, REQ-037</v>
       </c>
       <c r="H43" t="str">
-        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
+        <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
       </c>
       <c r="I43" t="str">
-        <v>État uploadingReferential: loading indicator, disabled submit</v>
+        <v>UX: clair et accessible, pas scroll nécessaire</v>
       </c>
     </row>
     <row r="44">
@@ -1665,10 +1665,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C44" t="str">
-        <v>Référentiel documentaire section</v>
+        <v>Génération questions section</v>
       </c>
       <c r="D44" t="str">
-        <v>Ajouter document avec métas, liste affichée</v>
+        <v>Upload fichier, select count, bouton 'Générer via IA', affichage résultat</v>
       </c>
       <c r="E44" t="str">
         <v>P1</v>
@@ -1677,13 +1677,13 @@
         <v>Complété</v>
       </c>
       <c r="G44" t="str">
-        <v>REQ-024, REQ-025, REQ-036</v>
+        <v>REQ-020, REQ-021, REQ-037</v>
       </c>
       <c r="H44" t="str">
-        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
+        <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
       </c>
       <c r="I44" t="str">
-        <v>Erreurs affichées, success feedback, état documentS refresh</v>
+        <v>État uploadingReferential: loading indicator, disabled submit</v>
       </c>
     </row>
     <row r="45">
@@ -1694,10 +1694,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C45" t="str">
-        <v>Échelles métriques config</v>
+        <v>Référentiel documentaire section</v>
       </c>
       <c r="D45" t="str">
-        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
+        <v>Ajouter document avec métas, liste affichée</v>
       </c>
       <c r="E45" t="str">
         <v>P1</v>
@@ -1706,13 +1706,13 @@
         <v>Complété</v>
       </c>
       <c r="G45" t="str">
-        <v>REQ-026, REQ-027, REQ-036</v>
+        <v>REQ-025, REQ-026, REQ-037</v>
       </c>
       <c r="H45" t="str">
-        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
+        <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
       </c>
       <c r="I45" t="str">
-        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
+        <v>Erreurs affichées, success feedback, état documentS refresh</v>
       </c>
     </row>
     <row r="46">
@@ -1723,10 +1723,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C46" t="str">
-        <v>Dashboard avec KPIs</v>
+        <v>Échelles métriques config</v>
       </c>
       <c r="D46" t="str">
-        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
+        <v>Input pour Confidentialité, Intégrité, Disponibilité, Preuve (ex: 1-5)</v>
       </c>
       <c r="E46" t="str">
         <v>P1</v>
@@ -1735,13 +1735,13 @@
         <v>Complété</v>
       </c>
       <c r="G46" t="str">
-        <v>-</v>
+        <v>REQ-027, REQ-028, REQ-037</v>
       </c>
       <c r="H46" t="str">
-        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
+        <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
       </c>
       <c r="I46" t="str">
-        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
+        <v>Format libre permet audit custom (ex: YES/NO ou 0-10)</v>
       </c>
     </row>
     <row r="47">
@@ -1752,10 +1752,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C47" t="str">
-        <v>Gestion entretiens</v>
+        <v>Dashboard avec KPIs</v>
       </c>
       <c r="D47" t="str">
-        <v>Interviewés, notes questions, scoring intégré</v>
+        <v>Affichage cards avec compteurs, matrice conformité, audit log viewer</v>
       </c>
       <c r="E47" t="str">
         <v>P1</v>
@@ -1767,10 +1767,10 @@
         <v>-</v>
       </c>
       <c r="H47" t="str">
-        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
+        <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
       </c>
       <c r="I47" t="str">
-        <v>Chaque note liée criterion + interviewee + score optionnel</v>
+        <v>View mode 'dashboard' toggle TOP (workspace vs dashboard)</v>
       </c>
     </row>
     <row r="48">
@@ -1781,10 +1781,10 @@
         <v>UI/UX</v>
       </c>
       <c r="C48" t="str">
-        <v>Audit log viewer</v>
+        <v>Gestion entretiens</v>
       </c>
       <c r="D48" t="str">
-        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
+        <v>Interviewés, notes questions, scoring intégré</v>
       </c>
       <c r="E48" t="str">
         <v>P1</v>
@@ -1793,13 +1793,13 @@
         <v>Complété</v>
       </c>
       <c r="G48" t="str">
-        <v>REQ-046</v>
+        <v>-</v>
       </c>
       <c r="H48" t="str">
-        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
+        <v>Sections: Ajouter interviewé form. Notes d'entretien table. Scoring form.</v>
       </c>
       <c r="I48" t="str">
-        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
+        <v>Chaque note liée criterion + interviewee + score optionnel</v>
       </c>
     </row>
     <row r="49">
@@ -1810,25 +1810,25 @@
         <v>UI/UX</v>
       </c>
       <c r="C49" t="str">
-        <v>Export buttons</v>
+        <v>Audit log viewer</v>
       </c>
       <c r="D49" t="str">
-        <v>Boutons DOCX et CSV téléchargement</v>
+        <v>Tableau logs avec filtres période (7d/30d/all) et action</v>
       </c>
       <c r="E49" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="F49" t="str">
         <v>Complété</v>
       </c>
       <c r="G49" t="str">
-        <v>-</v>
+        <v>REQ-047</v>
       </c>
       <c r="H49" t="str">
-        <v>POST /export-report et /export-csv. browser Blob download.</v>
+        <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
       </c>
       <c r="I49" t="str">
-        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+        <v>Sync knownActions dynamiquement depuis logs récupérés</v>
       </c>
     </row>
     <row r="50">
@@ -1836,13 +1836,13 @@
         <v>REQ-049</v>
       </c>
       <c r="B50" t="str">
-        <v>Persévérance &amp; Facilité</v>
+        <v>UI/UX</v>
       </c>
       <c r="C50" t="str">
-        <v>Documentation complète</v>
+        <v>Export buttons</v>
       </c>
       <c r="D50" t="str">
-        <v>Setup guides, quickstart, git manual, examples références</v>
+        <v>Boutons DOCX et CSV téléchargement</v>
       </c>
       <c r="E50" t="str">
         <v>P2</v>
@@ -1854,13 +1854,13 @@
         <v>-</v>
       </c>
       <c r="H50" t="str">
-        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
+        <v>POST /export-report et /export-csv. browser Blob download.</v>
       </c>
       <c r="I50" t="str">
-        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
-      </c>
-    </row>
-    <row r="51" xml:space="preserve">
+        <v>Noms fichiers: Rubis_Campaign_[date]_[format]</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" t="str">
         <v>REQ-050</v>
       </c>
@@ -1868,10 +1868,10 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C51" t="str">
-        <v>One-command installation</v>
+        <v>Documentation complète</v>
       </c>
       <c r="D51" t="str">
-        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+        <v>Setup guides, quickstart, git manual, examples références</v>
       </c>
       <c r="E51" t="str">
         <v>P2</v>
@@ -1882,12 +1882,11 @@
       <c r="G51" t="str">
         <v>-</v>
       </c>
-      <c r="H51" t="str" xml:space="preserve">
-        <v xml:space="preserve">.
- install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      <c r="H51" t="str">
+        <v>Fichiers: SETUP_OLLAMA.md, SETUP_OPENAI.md, GETTING_STARTED.md, QUICKSTART.md, README.md, GIT_MANUAL_INSTRUCTIONS.md</v>
       </c>
       <c r="I51" t="str">
-        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+        <v>&gt;1500 lines docs. Français + English mix selon besoin.</v>
       </c>
     </row>
     <row r="52" xml:space="preserve">
@@ -1898,41 +1897,42 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C52" t="str">
+        <v>One-command installation</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Non-tech user peut installer Rubis complet en 1 commande</v>
+      </c>
+      <c r="E52" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Complété</v>
+      </c>
+      <c r="G52" t="str">
+        <v>-</v>
+      </c>
+      <c r="H52" t="str" xml:space="preserve">
+        <v xml:space="preserve">.
+ install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
+      </c>
+      <c r="I52" t="str">
+        <v>~30min première fois (download 2.3GB Mistral). ~5min après.</v>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53" t="str">
+        <v>REQ-052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C53" t="str">
         <v>One-command launch</v>
       </c>
-      <c r="D52" t="str" xml:space="preserve">
+      <c r="D53" t="str" xml:space="preserve">
         <v xml:space="preserve">npm run dev ou .
 start-rubis.ps1 pour lancer tout</v>
       </c>
-      <c r="E52" t="str">
-        <v>P2</v>
-      </c>
-      <c r="F52" t="str">
-        <v>Complété</v>
-      </c>
-      <c r="G52" t="str">
-        <v>-</v>
-      </c>
-      <c r="H52" t="str">
-        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
-      </c>
-      <c r="I52" t="str">
-        <v>Détection auto erreurs, log output lisible</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>REQ-052</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Persévérance &amp; Facilité</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Clear error messages</v>
-      </c>
-      <c r="D53" t="str">
-        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
-      </c>
       <c r="E53" t="str">
         <v>P2</v>
       </c>
@@ -1943,10 +1943,10 @@
         <v>-</v>
       </c>
       <c r="H53" t="str">
-        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+        <v>start-rubis.ps1: verify Ollama, launch Ollama bg terminal, npm run dev. ~30 sec.</v>
       </c>
       <c r="I53" t="str">
-        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+        <v>Détection auto erreurs, log output lisible</v>
       </c>
     </row>
     <row r="54">
@@ -1957,30 +1957,59 @@
         <v>Persévérance &amp; Facilité</v>
       </c>
       <c r="C54" t="str">
-        <v>Roadmap versioning</v>
+        <v>Clear error messages</v>
       </c>
       <c r="D54" t="str">
-        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+        <v>UI affiche erreurs compréhensibles, logs API détaillés</v>
       </c>
       <c r="E54" t="str">
         <v>P2</v>
       </c>
       <c r="F54" t="str">
-        <v>Planifié</v>
+        <v>Complété</v>
       </c>
       <c r="G54" t="str">
         <v>-</v>
       </c>
       <c r="H54" t="str">
+        <v>UI setErrorMessage(). API log.error(). Try-catch tous endpoints.</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Users voient actionable feedback (ex: 'Modèle Ollama non trouvé, essayez gemma3:4b')</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>REQ-054</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Persévérance &amp; Facilité</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Roadmap versioning</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Fichier Excel roadmap dans repo pour futur maintenance/sprints</v>
+      </c>
+      <c r="E55" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G55" t="str">
+        <v>-</v>
+      </c>
+      <c r="H55" t="str">
         <v>Créer ROADMAP.xlsx avec specs, priorités, statuts, directives implémentation.</v>
       </c>
-      <c r="I54" t="str">
+      <c r="I55" t="str">
         <v>À committé dans git, mis à jour post-MVP pour v2 features</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I55"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -911,25 +911,25 @@
         <v>IA &amp; Génération</v>
       </c>
       <c r="C18" t="str">
-        <v>Parsing référentiel multi-format</v>
+        <v>Analyse documentaire pour validation critères</v>
       </c>
       <c r="D18" t="str">
-        <v>Support PDF et Excel avec extraction de texte</v>
+        <v>IA analyse chaque critère d'audit et détermine quels documents fournis répondent/couvrent ce critère. Création d'une matrice critères ↔ documents avec score de pertinence et extraits. Validation et ajustement manuel possible.</v>
       </c>
       <c r="E18" t="str">
         <v>P1</v>
       </c>
       <c r="F18" t="str">
-        <v>Complété</v>
+        <v>Planifié</v>
       </c>
       <c r="G18" t="str">
-        <v>REQ-013</v>
+        <v>REQ-005, REQ-013, REQ-014, REQ-008</v>
       </c>
       <c r="H18" t="str">
-        <v>parseReferentialFile() switch sur mimeType. pdf-parse pour PDF, xlsx pour Excel. Limiter 50KB.</v>
+        <v>Endpoint: POST /analyze-documents-against-criteria (lance analyse complète). Service: analyzeDocumentsAgainstCriteria(criteriaList, referentialDocsList) via LLM. Analyse: pour chaque critère, LLM parcourt docs et identifie ceux qui le couvrent, extrait passages pertinents, calcule score pertinence (0-100%). Output structure: {criterionId, criterionCode, documentMatches: [{documentId, documentName, relevanceScore, extractedText, matchedSections}]}. Stockage db.data.criteriaDocumentMapping: {campaignId, criterionId, linkedDocuments: [{documentId, relevanceScore, extractedText, timestamp, userValidated, userNotes}]}. UI: Affichage type tableau/graph montrant pour chaque critère les docs associés avec score, extraits, justification. Admin module: section 'Vérification couverture documentaire' avec tableau editable, possibilité d'ajouter/retirer liens, ajuster scores, ajouter notes validation. Export: matrice coverage % par critère.</v>
       </c>
       <c r="I18" t="str">
-        <v>Gère encodages UTF-8, caractères spéciaux</v>
+        <v>Visualise couverture documentaire des critères. Score pertinence aide prioriser validation manuelle. Extraction de passages facilite audit trail. LLM prompt: 'Quel critère ce document adresse-t-il et avec quelle pertinence?'</v>
       </c>
     </row>
     <row r="19">
@@ -981,7 +981,7 @@
         <v>Complété</v>
       </c>
       <c r="G20" t="str">
-        <v>REQ-002</v>
+        <v>REQ-013</v>
       </c>
       <c r="H20" t="str">
         <v>db.data.documents: {id, campaignId, name, theme, version, date, sensitivity, summary}</v>
@@ -1039,7 +1039,7 @@
         <v>Complété</v>
       </c>
       <c r="G22" t="str">
-        <v>REQ-005, REQ-020</v>
+        <v>REQ-002</v>
       </c>
       <c r="H22" t="str">
         <v>db.data.interviewNotes: {id, campaignId, criterionId, intervieweeId, content, score}</v>
@@ -1068,7 +1068,7 @@
         <v>Complété</v>
       </c>
       <c r="G23" t="str">
-        <v>REQ-021</v>
+        <v>REQ-005, REQ-021</v>
       </c>
       <c r="H23" t="str">
         <v>Calculée à la volée depuis criterion + interviewNotes. GET /criteria/:campaignId aggregate.</v>
@@ -1097,7 +1097,7 @@
         <v>Complété</v>
       </c>
       <c r="G24" t="str">
-        <v>REQ-002</v>
+        <v>REQ-022</v>
       </c>
       <c r="H24" t="str">
         <v>POST /metric-scales. Stockage db.data.metricScales: {campaignId, confidentiality, integrity, availability, evidence}</v>
@@ -1126,7 +1126,7 @@
         <v>Complété</v>
       </c>
       <c r="G25" t="str">
-        <v>REQ-002, REQ-033</v>
+        <v>REQ-002</v>
       </c>
       <c r="H25" t="str">
         <v>logAction(campaignId, action, details) helper. db.data.auditLogs array (reverse-chrono). Limit 2000 entrées.</v>
@@ -1155,7 +1155,7 @@
         <v>Complété</v>
       </c>
       <c r="G26" t="str">
-        <v>REQ-024</v>
+        <v>REQ-002, REQ-033</v>
       </c>
       <c r="H26" t="str">
         <v>GET /audit-log/:campaignId?period=7d|30d|all. Calcul date range côté backend.</v>
@@ -1184,7 +1184,7 @@
         <v>Complété</v>
       </c>
       <c r="G27" t="str">
-        <v>REQ-024</v>
+        <v>REQ-025</v>
       </c>
       <c r="H27" t="str">
         <v>GET /audit-log/:campaignId?action=all|campaign.created|etc. Sync action list UI.</v>
@@ -1213,7 +1213,7 @@
         <v>Complété</v>
       </c>
       <c r="G28" t="str">
-        <v>REQ-007, REQ-022</v>
+        <v>REQ-025</v>
       </c>
       <c r="H28" t="str">
         <v>POST /export-report. Lib 'docx'. Génère paragraphes formatés + tableaux.</v>
@@ -1242,7 +1242,7 @@
         <v>Complété</v>
       </c>
       <c r="G29" t="str">
-        <v>REQ-022, REQ-024</v>
+        <v>REQ-007, REQ-023</v>
       </c>
       <c r="H29" t="str">
         <v>GET /export-csv/:campaignId. Convert array to CSV format. Headers: code,title,theme,conformity%</v>
@@ -1271,7 +1271,7 @@
         <v>Complété</v>
       </c>
       <c r="G30" t="str">
-        <v>REQ-027, REQ-028</v>
+        <v>REQ-023, REQ-025</v>
       </c>
       <c r="H30" t="str">
         <v>db.data.auditReports: {id, campaignId, title, generatedAt, version, content}</v>
@@ -1300,7 +1300,7 @@
         <v>Complété</v>
       </c>
       <c r="G31" t="str">
-        <v>REQ-019, REQ-020, REQ-021</v>
+        <v>REQ-028, REQ-029</v>
       </c>
       <c r="H31" t="str">
         <v>GET /dashboard-kpis/:campaignId. Aggregate counts depuis db.data.*</v>
@@ -1329,7 +1329,7 @@
         <v>Complété</v>
       </c>
       <c r="G32" t="str">
-        <v>REQ-022</v>
+        <v>REQ-020, REQ-021, REQ-022</v>
       </c>
       <c r="H32" t="str">
         <v>Affichage table React. Données GET /criteria/:campaignId. Tri sur weighting, answeredQuestions.</v>
@@ -1358,7 +1358,7 @@
         <v>Planifié</v>
       </c>
       <c r="G33" t="str">
-        <v>REQ-030</v>
+        <v>REQ-023</v>
       </c>
       <c r="H33" t="str">
         <v>Ajouter recharts ou Chart.js si requis. Endpoints déjà supportent data.</v>
@@ -1387,7 +1387,7 @@
         <v>Complété</v>
       </c>
       <c r="G34" t="str">
-        <v>REQ-033</v>
+        <v>REQ-031</v>
       </c>
       <c r="H34" t="str">
         <v>POST /campaigns body.language enum 'fr'|'en'. Stocké campaign. UI affiche langue active.</v>
@@ -1416,7 +1416,7 @@
         <v>Complété</v>
       </c>
       <c r="G35" t="str">
-        <v>REQ-010</v>
+        <v>-</v>
       </c>
       <c r="H35" t="str">
         <v>GET/POST /config. État currentOllamaModel runtime. Boutons UI permutent.</v>
@@ -1445,7 +1445,7 @@
         <v>Complété</v>
       </c>
       <c r="G36" t="str">
-        <v>REQ-033</v>
+        <v>REQ-010</v>
       </c>
       <c r="H36" t="str">
         <v>OPENAI_API_KEY=... in .env.example. openai.ts check process.env, instantiate si présent.</v>
@@ -1532,7 +1532,7 @@
         <v>Complété</v>
       </c>
       <c r="G39" t="str">
-        <v>REQ-034, REQ-037</v>
+        <v>-</v>
       </c>
       <c r="H39" t="str">
         <v>Fichiers: install-ollama.ps1, start-rubis.ps1, compare-ollama-models.ps1 root repo</v>
@@ -1561,7 +1561,7 @@
         <v>Complété</v>
       </c>
       <c r="G40" t="str">
-        <v>REQ-018, REQ-037</v>
+        <v>REQ-035, REQ-038</v>
       </c>
       <c r="H40" t="str">
         <v>.gitignore configué. Push via SSH Ed25519 key. GitHub repo créé.</v>
@@ -1590,7 +1590,7 @@
         <v>Complété</v>
       </c>
       <c r="G41" t="str">
-        <v>REQ-019, REQ-037</v>
+        <v>REQ-019, REQ-038</v>
       </c>
       <c r="H41" t="str">
         <v>Fastify app.ts. @fastify/cors registered. @fastify/multipart 9.0.1</v>
@@ -1619,7 +1619,7 @@
         <v>Complété</v>
       </c>
       <c r="G42" t="str">
-        <v>REQ-023, REQ-037</v>
+        <v>REQ-020, REQ-038</v>
       </c>
       <c r="H42" t="str">
         <v>Apps/web/src/App.tsx. Vite config. 29 modules bundled.</v>
@@ -1648,7 +1648,7 @@
         <v>Complété</v>
       </c>
       <c r="G43" t="str">
-        <v>REQ-030, REQ-037</v>
+        <v>REQ-024, REQ-038</v>
       </c>
       <c r="H43" t="str">
         <v>Section card en haut App.tsx. Boutons onClick switchOllamaModel(). Vert si actif.</v>
@@ -1677,7 +1677,7 @@
         <v>Complété</v>
       </c>
       <c r="G44" t="str">
-        <v>REQ-020, REQ-021, REQ-037</v>
+        <v>REQ-031, REQ-038</v>
       </c>
       <c r="H44" t="str">
         <v>Form &lt;input type=file accept=.pdf,.xlsx&gt;. Input number 1-10. Submitter disabled si !criterionId</v>
@@ -1706,7 +1706,7 @@
         <v>Complété</v>
       </c>
       <c r="G45" t="str">
-        <v>REQ-025, REQ-026, REQ-037</v>
+        <v>REQ-021, REQ-022, REQ-038</v>
       </c>
       <c r="H45" t="str">
         <v>Form: name, theme, version, date, sensitivity select, summary. POST /documents</v>
@@ -1735,7 +1735,7 @@
         <v>Complété</v>
       </c>
       <c r="G46" t="str">
-        <v>REQ-027, REQ-028, REQ-037</v>
+        <v>REQ-026, REQ-027, REQ-038</v>
       </c>
       <c r="H46" t="str">
         <v>Form 4 inputs texte. POST /metric-scales. Sauvé par campaign.</v>
@@ -1764,7 +1764,7 @@
         <v>Complété</v>
       </c>
       <c r="G47" t="str">
-        <v>-</v>
+        <v>REQ-028, REQ-029, REQ-038</v>
       </c>
       <c r="H47" t="str">
         <v>useState dashboardKpis, matrixDetails. GET /dashboard-kpis. Render grid cards.</v>
@@ -1822,7 +1822,7 @@
         <v>Complété</v>
       </c>
       <c r="G49" t="str">
-        <v>REQ-047</v>
+        <v>-</v>
       </c>
       <c r="H49" t="str">
         <v>Dropdowns: period, action filter. GET /audit-log avec query params. Table affiche action/timestamp/details</v>
@@ -1851,7 +1851,7 @@
         <v>Complété</v>
       </c>
       <c r="G50" t="str">
-        <v>-</v>
+        <v>REQ-048</v>
       </c>
       <c r="H50" t="str">
         <v>POST /export-report et /export-csv. browser Blob download.</v>
@@ -1912,7 +1912,7 @@
         <v>-</v>
       </c>
       <c r="H52" t="str" xml:space="preserve">
-        <v xml:space="preserve">.
+        <v xml:space="preserve">.\
  install-ollama.ps1 détecte, installe Ollama, download Mistral, setup env.</v>
       </c>
       <c r="I52" t="str">
@@ -1930,7 +1930,7 @@
         <v>One-command launch</v>
       </c>
       <c r="D53" t="str" xml:space="preserve">
-        <v xml:space="preserve">npm run dev ou .
+        <v xml:space="preserve">npm run dev ou .\
 start-rubis.ps1 pour lancer tout</v>
       </c>
       <c r="E53" t="str">

--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I58"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2007,9 +2007,96 @@
         <v>À committé dans git, mis à jour post-MVP pour v2 features</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>REQ-055</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Cœur métier</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Plan d'audit</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Document structuré définissant la portée, objectifs, équipe, timeline, ressources, livrables et méthodologie de l'audit. Génération semi-automatique basée sur la campagne et les critères.</v>
+      </c>
+      <c r="E56" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G56" t="str">
+        <v>REQ-001, REQ-013</v>
+      </c>
+      <c r="H56" t="str">
+        <v>POST /audit-plan/generate (basé sur campaignId). Service: generateAuditPlan(campaign, criteria) via LLM. Génère: titre, objectifs, portée, équipe (rôles), planning phases, ressources, livrables, contraintes, approbations. Endpoint: GET /audit-plan/:campaignId (récupère ou réaffiche). UI: section 'Plan d'audit' avec form de finalisation, export PDF/DOCX, signature numérique optionnelle. Admin: validation plan avant approval.</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Facilite formalisation audit. LLM génère brouillon à partir critères. User affine et valide. Export PDF pour archivage et transmission.</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>REQ-056</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Cœur métier</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Note de cadrage</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Document préliminaire établissant contexte, objectifs, conventions de travail, limitations et responsabilités avant le lancement des entretiens. Synthèse des finalités de l'audit.</v>
+      </c>
+      <c r="E57" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G57" t="str">
+        <v>REQ-001, REQ-013</v>
+      </c>
+      <c r="H57" t="str">
+        <v>POST /scope-note/generate (basé sur campaignId, framework). Service: generateScopeNote(campaign, referential, objectives) via LLM. Génère: contexte organisation, objectifs audit, périmètre SI/métiers, limitations, hypothèses, livrables attendus, planning prévisionnel. Stockage db.data.scopeNotes: {id, campaignId, generatedAt, content, userValidated, approvedBy, approvalDate}. UI: section 'Note de cadrage' avec form édition, versioning, commentaires. Export PDF contresigné. Admin: signature électronique et workflow d'approbation.</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Premier document formalisé. Fixe le cadre de l'audit. Généré par IA puis validé par auditeur senior. Versioning permet suivi des modifications. Approuvé par direction avant démarrage entretiens.</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>REQ-057</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Cœur métier</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Convention d'audit</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Accord formalisé entre auditeur(s) et audité(s) définissant conditions, accès, confidentialité, responsabilités de chaque partie, planning détaillé, points de contact et escalade.</v>
+      </c>
+      <c r="E58" t="str">
+        <v>P2</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G58" t="str">
+        <v>REQ-001, REQ-013</v>
+      </c>
+      <c r="H58" t="str">
+        <v>POST /audit-convention/generate (basé sur campaignId, interviewees). Service: generateConvention(campaign, auditors, auditees) via LLM. Génère: parties (auditeur/audité), objectifs rappelés, modalités (durée, jours, horaires), accès SI/locaux, confidentialité/NDA, responsabilités, gestion exceptions, communication, plaintes. Stockage db.data.conventions: {id, campaignId, generatedAt, content, signaturesRequired, signatureStatus}. UI: section 'Convention d'audit' avec affichage, signature électronique, signature collector. Export PDF multi-signatures. Admin: gestion signaturaires, relances signature, archivage final.</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Contrat formel signé par les deux parties. Évite malentendus. IA génère le brouillon standard, user personnalise par contexte. Signatures électroniques (e-sign via DocuSign intégration ultérieurement). À signer avant phase 1.2 (entretiens).</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I58"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -2018,7 +2018,7 @@
         <v>Plan d'audit</v>
       </c>
       <c r="D56" t="str">
-        <v>Document structuré définissant la portée, objectifs, équipe, timeline, ressources, livrables et méthodologie de l'audit. Génération semi-automatique basée sur la campagne et les critères.</v>
+        <v>Document structuré définissant la portée, objectifs, équipe, timeline, ressources, livrables et méthodologie de l'audit. Interface calendrier pour planifier les phases, générer automatiquement les créneaux d'entretien et les exporter dans Outlook. Génération semi-automatique basée sur la campagne et les critères.</v>
       </c>
       <c r="E56" t="str">
         <v>P2</v>
@@ -2030,10 +2030,10 @@
         <v>REQ-001, REQ-013</v>
       </c>
       <c r="H56" t="str">
-        <v>POST /audit-plan/generate (basé sur campaignId). Service: generateAuditPlan(campaign, criteria) via LLM. Génère: titre, objectifs, portée, équipe (rôles), planning phases, ressources, livrables, contraintes, approbations. Endpoint: GET /audit-plan/:campaignId (récupère ou réaffiche). UI: section 'Plan d'audit' avec form de finalisation, export PDF/DOCX, signature numérique optionnelle. Admin: validation plan avant approval.</v>
+        <v>POST /audit-plan/generate (basé sur campaignId). Service: generateAuditPlan(campaign, criteria) via LLM. Génère: titre, objectifs, portée, équipe (rôles), planning phases, ressources, livrables, contraintes, approbations. Interface calendrier: visualisation Gantt des phases, duration drag-drop, auto-calcul dates début/fin. POST /audit-plan/:id/generate-slots (génère créneaux entretiens basé sur interviewees, durée, ressources dispo). Endpoint: GET /audit-plan/:id/export-outlook (export .ics Outlook). UI: section 'Plan d'audit' avec calendrier interactif, form de finalisation, generation slots button, export PDF/DOCX/Outlook. Admin: validation plan avant approval. Integration Outlook: OAuth2 pour envoi direct calendrier, ou téléchargement .ics pour Outlook local.</v>
       </c>
       <c r="I56" t="str">
-        <v>Facilite formalisation audit. LLM génère brouillon à partir critères. User affine et valide. Export PDF pour archivage et transmission.</v>
+        <v>Facilite formalisation audit avec visualisation temporelle. Calendrier permet allocation ressources, évite conflicts. Export Outlook synchronise planning avec outils secteur. LLM génère brouillon. User affine, génère slots. Créneaux exportés aux participants.</v>
       </c>
     </row>
     <row r="57">

--- a/ROADMAP.xlsx
+++ b/ROADMAP.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2094,9 +2094,38 @@
         <v>Contrat formel signé par les deux parties. Évite malentendus. IA génère le brouillon standard, user personnalise par contexte. Signatures électroniques (e-sign via DocuSign intégration ultérieurement). À signer avant phase 1.2 (entretiens).</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>REQ-058</v>
+      </c>
+      <c r="B59" t="str">
+        <v>UI/UX</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Navigation multi-campagnes par onglets</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Système d'onglets permettant d'ouvrir plusieurs campagnes d'audit simultanément dans l'interface. L'utilisateur peut basculer entre différentes instances de campagnes, créer de nouvelles campagnes depuis un onglet dédié, et fermer des onglets. Affichage partie par partie au lieu d'une vue globale unique.</v>
+      </c>
+      <c r="E59" t="str">
+        <v>P1</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="G59" t="str">
+        <v>REQ-002, REQ-038</v>
+      </c>
+      <c r="H59" t="str">
+        <v>UI: Composant TabSystem avec state managé [openTabs: {id, campaignId, title, isActive}]. Barre d'onglets horizontal en haut de l'app avec (+) pour nouvelle campagne. Chaque onglet affiche nom campagne + bouton fermeture (×). Click sur onglet active la campagne correspondante. État activeCampaignId contrôle quelle campagne est chargée. localStorage persistance des onglets ouverts entre sessions. GET /campaigns récupère liste complète pour modal sélection. Workflow: User click '+' → Modal liste campagnes existantes + bouton 'Créer nouvelle' → Sélection ouvre nouvel onglet. Component isolation: chaque onglet charge son propre contexte (documents, critères, interviewés, etc.). Max 5 onglets ouverts simultanément pour perf. Fermer onglet = cleanup state + localStorage update. Navigation keyboard: Ctrl+Tab pour basculer entre onglets.</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Améliore UX multi-audit. Permet comparaison side-by-side (futur: split view). Persistance localStorage évite perte état après refresh. Limite 5 onglets empêche surcharge mémoire. Chaque campagne isolée = évite cross-contamination données. icône badge sur onglet si actions pending (ex: docs à transmettre).</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I59"/>
   </ignoredErrors>
 </worksheet>
 </file>